--- a/output/opodesh-test/book-output.xlsx
+++ b/output/opodesh-test/book-output.xlsx
@@ -534,7 +534,7 @@
 وَيَسْتُرُهُ فَيَقُولُ أَتَعْرِفُ ذَنْبَ كَذَا أَتَعْرِفُ ذَنْبَ كَذَا فَيَقُولُ نَعَمْ أَيْ رَبِّ . حَتَّى إِذَا
 قَرَّرَهُ بِذُنُوبِهِ وَرَأَى فِي نَفْسِهِ أَنَّهُ هَلَكَ قَالَ سَتَرْتُهَا عَلَيْكَ فِي الدُّنْيَا، وَأَنَا أَغْفِرُهَا
 لَكَ الْيَوْمَ ، فَيُعْطَى كِتَابَ حَسَنَاتِهِ، وَأَمَّا الْكَافِرُ وَالْمُنَافِقُونَ فَيَقُولُ الْأَشْهَادُ هَؤُلَاءِ
-الَّذِينَ كَذَبُوا عَلَى رَبِّهِمْ، أَلَا لَعْنَةُ اللَّهِ عَلَى الظَّالِمِينَ » .&lt;/p&gt;
+الَّذِينَ كَذَبُوا عَلَى رَبِّهِمْ، أَلَا لَعْنَةُ اللَّهِ عَلَى الظَّالِمِينَ » .&lt;/ar&gt;
 &lt;p&gt;
 ইবনু উমার (রাঃ) বলেন, রাসূলুল্লাহ (ﷺ) বলেছেন, '(কিয়ামতের দিন) আল্লাহ তাআলা মুমিনদের নিজের নিকটবর্তী করবেন এবং আল্লাহ
 তাআলা নিজ বাজু তার উপরে রেখে তাকে ঢেকে নিবেন। অতঃপর আল্লাহ সেই বান্দাকে বলবেন, আচ্ছা! বলো দেখি, এই গুনাহটি তুমি করেছ কি?

--- a/output/opodesh-test/book-output.xlsx
+++ b/output/opodesh-test/book-output.xlsx
@@ -499,180 +499,35 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>&lt;div class="page-text"&gt;&lt;p&gt;(কুরআন ও ছহীহ হাদীছের আলোকে উপদেশ)&lt;/p&gt;
-&lt;p&gt;
-অবিচ্ছেদ্য সাক্ষী এমন সাক্ষীকে বলা হয়, যা ব্যক্তি হতে পৃথক হয় না। কিয়ামতের মাঠে আল্লাহ অবিচ্ছেদ্য সাক্ষীর মাধ্যমে
-মানুষকে অপরাধী প্রমাণ করবেন। আর তা হবে মানুষের হাত, পা, শরীর ইত্যাদি। যেমন: মহান আল্লাহ বলেন,
-&lt;/p&gt;
-&lt;ar&gt;
-الْيَوْمَ نَخْتِمُ عَلَى أَفْوَاهِهِمْ وَتُكَلِّمُنَا أَيْدِيهِمْ وَتَشْهَدُ أَرْجُلُهُمْ بِمَا كَانُوا يَكْسِبُونَ
-&lt;/ar&gt;
-&lt;p&gt;
-'আমি আজ এদের মুখে মোহর লাগিয়ে দিব, এদের হাত কথা বলবে আমার সাথে এবং এদের পা সাক্ষ্য দিবে এদের কৃতকর্মের' (ইয়াসীন, ৩৬/৬৫)।
-&lt;/p&gt;
+          <t>&lt;div class="page-text"&gt;&lt;p&gt;অবিচ্ছেদ্য সাক্ষী এমন সাক্ষীকে বলা হয়, যা ব্যক্তি হতে পৃথক হয় না।&lt;/p&gt;
+&lt;p&gt;কিয়ামতের মাঠে আল্লাহ অবিচ্ছেদ্য সাক্ষীর মাধ্যমে মানুষকে অপরাধী প্রমাণ করবেন। আর তা হবে মানুষের হাত, পা, শরীর ইত্যাদি।&lt;/p&gt;
+&lt;p&gt;যেমন: মহান আল্লাহ বলেন,&lt;/p&gt;
+&lt;ar&gt;الْيَوْمَ نَخْتِمُ عَلَى أَفْوَاهِهِمْ وَتُكَلِّمُنَا أَيْدِيهِمْ وَتَشْهَدُ أَرْجُلُهُمْ بِمَا كَانُوا يَكْسِبُونَ&lt;/ar&gt;
+&lt;p&gt;'আমি আজ এদের মুখে মোহর লাগিয়ে দিব, এদের হাত কথা বলবে আমার সাথে এবং এদের পা সাক্ষ্য দিবে এদের কৃতকর্মের' (ইয়াসীন, ৩৬/৬৫)।&lt;/p&gt;
 &lt;ar&gt;يَوْمَ تَشْهَدُ عَلَيْهِمْ أَلْسِنَتُهُمْ وَأَيْدِيهِمْ وَأَرْجُلُهُمْ بِمَا كَانُوا يَعْمَلُوْনَ&lt;/ar&gt;
 &lt;p&gt;'যেদিন তাদের বিরুদ্ধে সাক্ষ্য দিবে তাদের যবান, তাদের হাত ও তাদের পা তাদের কৃতকর্ম সম্বন্ধে' (আন-নূর, ২৪/২৪)।&lt;/p&gt;
-&lt;ar&gt;
-وَيَوْمَ يُحْشَرُ أَعْدَاءُ اللهِ إِلَى النَّارِ فَهُمْ يُوزَعُوْنَ إِذَا مَا جَاءُوهَا شَهِدَ عَلَيْهِمْ سَمْعُهمْ
-وَأَبْصَارُهُمْ وَجُلُودُهُمْ بِمَا كَانُوا يَعْمَلُوْنَ وَقَالُوا لِجُلُوْدِهِمْ لِمَ شَهِدْتُمْ عَلَيْنَا قَالُوْا
-أَنْطَقَنَا اللَّهُ الَّذِي أَنْطَقَ كُلَّ شَيْءٍ وَهُوَ خَلَقَكُمْ أَوَّلَ مَرَّةٍ وَإِلَيْهِ تُرْجَعُوْنَ وَمَا
-كُنْتُمْ تَسْتَتِرُوْنَ أَنْ يَشْهَدَ عَلَيْكُمْ سَمْعُكُمْ وَلَا أَبْصَارُكُمْ وَلَا جُلُودُكُمْ وَلَكِنْ ظَنَنْتُمْ
-أَنَّ اللَّهَ لَا يَعْلَمُ كَثِيرًا مِمَّا تَعْمَلُوْনَ
-&lt;/ar&gt;
-&lt;p&gt;
-'যেদিন আল্লাহর শত্রুদের জাহান্নাম অভিমুখে সমবেত করা হবে, সেদিন তাদের তাড়িয়ে নিয়ে যাওয়া হবে বিভিন্ন দলে। পরিশেষে যখন তারা
-জাহান্নামের সন্নিকটে পৌঁছবে তখন তাদের কর্ণ, চক্ষু ও ত্বক (চামড়া) তাদের কৃতকর্ম সম্বন্ধে সাক্ষ্য দিবে। জাহান্নামীরা তাদের
-ত্বককে জিজ্ঞাসা করবে, তোমরা আমাদের বিরুদ্ধে সাক্ষ্য দিচ্ছ কেন? উত্তরে তারা বলবে, আল্লাহ যিনি সবকিছুকে বাকশক্তি
-&lt;/p&gt;
-&lt;p&gt;
-দিয়েছেন তিনি আমাদেরও বাকশক্তি দিয়েছেন। তিনি তোমাদের সৃষ্টি করেছেন প্রথম বার এবং তাঁরই নিকট তোমরা প্রত্যাবর্তিত হবে।
-তোমরা কিছু গোপন করতে না এই বিশ্বাসে যে, তোমাদের কর্ণ, চক্ষু এবং ত্বক তোমাদের বিরুদ্ধে সাক্ষ্য দিবে না। উপরন্তু তোমরা মনে
-করতে যে, তোমরা যা করতে তার অনেক কিছুই আল্লাহ জানেন না' (ফুছছিলাত, ৪১/১৯-২২)।
-&lt;/p&gt;
+&lt;ar&gt;وَيَوْمَ يُحْশَرُ أَعْدَاءُ اللهِ إِلَى النَّارِ فَهُمْ يُوزَعُوْنَ إِذَا مَا جَاءُوهَا شَهِدَ عَلَيْهِمْ سَمْعُكُمْ وَأَبْصَارُكُمْ وَجُلُودُكُمْ بِمَا كَانُوا يَعْمَلُوْনَ وَقَالُوا لِجُلُوْدِهِمْ لِمَ شَهِدْتُمْ عَلَيْنَا قَالُوْا أَنْطَقَنَا اللَّهُ الَّذِي أَنْطَقَ كُلَّ شَيْءٍ وَهُوَ خَلَقَكُمْ أَوَّلَ مَرَّةٍ وَإِلَيْهِ تُرْجَعُوْنَ وَمَا كُنْتُمْ تَسْتَتِرُوْنَ أَنْ يَشْهَدَ عَلَيْكُمْ سَمْعُكُمْ وَلَا أَبْصَارُكُمْ وَلَا جُلُودُكُمْ وَلَكِنْ ظَنَنْتُمْ أَنَّ اللَّهَ لَا يَعْلَمُ كَثِيرًا مِمَّا تَعْمَلُوْনَ&lt;/ar&gt;
+&lt;p&gt;'যেদিন আল্লাহর শত্রুদের জাহান্নাম অভিমুখে সমবেত করা হবে, সেদিন তাদের তাড়িয়ে নিয়ে যাওয়া হবে বিভিন্ন দলে। পরিশেষে যখন তারা জাহান্নামের সন্নিকটে পৌঁছবে তখন তাদের কর্ণ, চক্ষু ও ত্বক (চামড়া) তাদের কৃতকর্ম সম্বন্ধে সাক্ষ্য দিবে। জাহান্নামীরা তাদের ত্বককে জিজ্ঞাসা করবে, তোমরা আমাদের বিরুদ্ধে সাক্ষ্য দিচ্ছ কেন? উত্তরে তারা বলবে, আল্লাহ যিনি সবকিছুকে বাকশক্তি&lt;/p&gt;
+&lt;p&gt;দিয়েছেন তিনি আমাদেরও বাকশক্তি দিয়েছেন। তিনি তোমাদের সৃষ্টি করেছেন প্রথম বার এবং তাঁরই নিকট তোমরা প্রত্যাবর্তিত হবে। তোমরা কিছু গোপন করতে না এই বিশ্বাসে যে, তোমাদের কর্ণ, চক্ষু এবং ত্বক তোমাদের বিরুদ্ধে সাক্ষ্য দিবে না। উপরন্তু তোমরা মনে করতে যে, তোমরা যা করতে তার অনেক কিছুই আল্লাহ জানেন না' (ফুছছিলাত, ৪১/১৯-২২)।&lt;/p&gt;
 &lt;p&gt;হাদীছে এসেছে,&lt;/p&gt;
-&lt;ar&gt;عَنِ ابْنِ عُمَرَ قَالَ قَالَ رَسُولُ اللهِ ﷺ إِنَّ اللهَ يُدْنِي الْمُؤْمِنَ فَيَضَعُ عَلَيْهِ كَنَفَهُ،
-وَيَسْتُرُهُ فَيَقُولُ أَتَعْرِفُ ذَنْبَ كَذَا أَتَعْرِفُ ذَنْبَ كَذَا فَيَقُولُ نَعَمْ أَيْ رَبِّ . حَتَّى إِذَا
-قَرَّرَهُ بِذُنُوبِهِ وَرَأَى فِي نَفْسِهِ أَنَّهُ هَلَكَ قَالَ سَتَرْتُهَا عَلَيْكَ فِي الدُّنْيَا، وَأَنَا أَغْفِرُهَا
-لَكَ الْيَوْمَ ، فَيُعْطَى كِتَابَ حَسَنَاتِهِ، وَأَمَّا الْكَافِرُ وَالْمُنَافِقُونَ فَيَقُولُ الْأَشْهَادُ هَؤُلَاءِ
-الَّذِينَ كَذَبُوا عَلَى رَبِّهِمْ، أَلَا لَعْنَةُ اللَّهِ عَلَى الظَّالِمِينَ » .&lt;/ar&gt;
-&lt;p&gt;
-ইবনু উমার (রাঃ) বলেন, রাসূলুল্লাহ (ﷺ) বলেছেন, '(কিয়ামতের দিন) আল্লাহ তাআলা মুমিনদের নিজের নিকটবর্তী করবেন এবং আল্লাহ
-তাআলা নিজ বাজু তার উপরে রেখে তাকে ঢেকে নিবেন। অতঃপর আল্লাহ সেই বান্দাকে বলবেন, আচ্ছা! বলো দেখি, এই গুনাহটি তুমি করেছ কি?
-এই গুনাহটি সম্পর্কে তুমি অবগত আছ কি? সে বলবে হ্যাঁ, হে আমার রব! আমি অবগত আছি। শেষ পর্যন্ত এক একটি করে তার কৃত সমস্ত
-গুনাহের স্বীকৃতি আদায় করবেন। এদিকে সে ৰান্দা মনে মনে এই ধারণা করবে যে, সে এই সমস্ত অপরাধের কারণে নিশ্চিত ধ্বংস হবে। তখন
-আল্লাহ তাআলা বলবেন, দুনিয়াতে আমি তোমার এই সমস্ত অপরাধ ঢেকে রেখেছিলাম। আর আজ আমি তা মাফ করে দিব। অতঃপর তাকে নেকীর আমলনামা
-দেওয়া হবে। আর কাফের ও মুনাফেকদের সমস্ত সৃষ্টির সম্মুখে আনয়ন করা হবে এবং উচ্চৈস্বরে এই ঘোষণা দেওয়া হবে- এরা তারা, যারা
-স্বীয় পরওয়ারদিগারের বিরুদ্ধে মিথ্যারোপ করত। জেনে রাখ, এই সমস্ত জালেমদের উপর আজ আল্লাহর লানত' (ছহীহ বুখারী, হা/২৪৪১; ছহীহ
-মুসলিম, হা/২৭৬৮; মিশকাত, হা/৫৫৫১)।
-&lt;/p&gt;
-&lt;ar&gt;
-عَنْ أَنَسِ بْنِ مَالِكٍ قَالَ كُنَّا عِنْدَ رَسُولِ اللهِ ﷺ فَضَحِكَ فَقَالَ « هَلْ تَدْرُونَ مِمَّ أَضْحَكُ ». قَالَ
-قُلْنَا اللهُ وَرَسُولُهُ أَعْلَمُ . قَالَ « مِنْ مُخَاطَبَةِ الْعَبْدِ رَبَّهُ يَقُولُ يَا رَبِّ أَلَمْ تُجِرْنِي مِنَ
-الظُّلْمِ قَالَ يَقُولُ بَلَى قَالَ فَيَقُولُ فَإِنِّي لا أُجِيرُ عَلَى نَفْسِي إِلَّا شَاهِدًا مِنِّي قَالَ فَيَقُولُ
-كَفَى بِنَفْسِكَ الْيَوْمَ عَلَيْكَ شَهِيدًا وَبِالْكِرَامِ الْكَاتِبِينَ شُهُودًا - قَالَ - نَيُحْتَمَ عَلَى فِيهِ
-فَيُقَالُ لأَرْكَانِهِ انْطِقِي. قَالَ فَتَنْطِقُ بِأَعْمَالِهِ - قَالَ - ثُمَّ يُخَلَّى بَيْنَهُ وَبَيْنَ الْكَلَامِ -
-قَالَ - فَيَقُولُ بُعْدًا لَكُنَّ وَসُحْقًا. فَعَنْكُنَّ كُنْتُ أُنَاضِلُ ».
-&lt;/ar&gt;
-&lt;p&gt;
-আনাস (রাঃ) হতে বর্ণিত, তিনি বলেন, আমরা রাসূলুল্লাহ (ﷺ)-এর কাছে ছিলাম, হঠাৎ তিনি হাসলেন। অতঃপর জিজ্ঞাসা করলেন, তোমরা কি
-জান আমি কেন হাসছি? আমরা বললাম, আল্লাহ এবং তাঁর রাসূলই ভালো জানেন। তিনি বললেন, কিয়ামতের দিন বান্দা যে তার রবের সাথে
-সরাসরি কথা বলবে, সেই কথাটি স্মরণ করে হাসছি। বান্দা বলবে, হে রব! তুমি কি আমাকে জুলুম হতে নিরাপত্তা দান করনি? আল্লাহ
-বলবেন, হ্যাঁ, তখন বান্দা বলবে, আজ আমি আমার সম্পর্কে আপনজন ব্যতীত আমার বিরুদ্ধে অন্য কারো সাক্ষ্য গ্রহণ করব না। তখন
-আল্লাহ বলবেন, আজ তুমি নিজেই তোমার সাক্ষী হিসাবে এবং কিরামান-কাতেবীনের সাক্ষ্যই তোমার জন্য যথেষ্ট। অতঃপর আল্লাহ তাআলা তার
-মুখের উপর মোহর লাগিয়ে দিবেন এবং অঙ্গ-প্রত্যঙ্গকে বলা হবে, তোমরা কে কখন কী কী কাজ করেছ বলো। তখন অঙ্গ-প্রত্যঙ্গসমূহ তাদের
-কৃতকর্মসমূহ প্রকাশ করে দিবে। এরপর তার মুখকে স্বাভাবিক অবস্থায় খুলে দেওয়া হবে। তখন সে স্বীয় অঙ্গসমূহকে লক্ষ্য করে
-আক্ষেপের সাথে বলবে, হে দুর্ভাগা অঙ্গসমূহ! তোরা দূর হ! তোদের ধ্বংস হৌক! তোদের জন্যই তো আমি আমার রবের সাথে ঝগড়া করেছিলাম'
-(ছহীহ মুসলিম, হা/২৯৬৯; মিশকাত, হা/৫৫৫৪)।
-&lt;/p&gt;
-&lt;ar&gt;عَنْ أَبِي هُرَيْرَةَ قَالَ: قَالُوا : يَا রَسُولَ اللهِ! هَلْ نَرَى رَبَّنَا يَوْمَ الْقِيَامَةِ؟ قَالَ: هَلْ
-تُضَارُّونَ فِي رُؤْيَةِ الشَّمْسِ فِي الظَّهِيرَةِ لَيْسَتْ فِي سَحَابَةٍ؟ قَالُوا: لَا ، قَالَ: فَهَلْ تُضَارُّونَ فِي
-رُؤْيَةِ الْقَمَرِ لَيْلَةَ الْبَدْرِ لَيْسَتْ فِي سَحَابَةٍ؟ قَالُوا : لَا. قَالَ: فَوَالَّذِي نَفْسِي بِيَدِهِ لَا
-تُضَارُّونَ فِي رُؤْيَةِ رَبِّكُمْ إِلَّا كَمَا تُضَارُّونَ فِي رُؤْيَةِ أَحَدِهِمَا. قَالَ: فَيَلْقَى الْعَبْدَ
-فَيَقُولُ: أَيْ قُلْ: أَلَمْ أُكْرِمْكَ وَأُسَوَّدْكَ وَأَزَوَّجْكَ، وَأُسَخَّرْ لَكَ الْخَيْلَ وَالْإِبِلَ ، وَأَذَرْكَ
-تَرْأَسُ وَتَرْبَعُ؟ فَيَقُولُ: بَلَى. قَالَ: فَيَقُولُ: أَفَظَنَنْتَ أَنَّكَ مُلَاقِي؟ فَيَقُولُ لَا فَيَقُولُ:
-فَإِنِّي قَدْ أَنْسَاكَ كَمَا نَسِيتَنِي. ثُمَّ يَلْقَى الثَّاني فَذَكَرَ مِثْلَهُ ، ثُمَّ يَلْقَى الثَّالِثَ فَيَقُولُ
-لَهُ مِثْلَ ذَلِكَ، فَيَقُولُ: يَا رَبِّ آمَنْتُ بِكَ، وَبِكِتَابِكَ وَبِرُسُلِكَ، وَصَلَّيْتُ وَصُمْتُ، وَتَصَدَّقْتُ،
-وَيُثْنِي بِخَيْرٍ مَا اسْتَطَاعَ، يَقُولُ: هَاهُنَا إِذًا، ثُمَّ يُقَالُ: الْآنَ نَبْعَثُ شَاهِدًا عَلَيْكَ،
-وَيَتَفَكَّرُ فِي نَفْسِهِ: مَنْ ذَا الَّذِي يَشْهَدُ عَلَيَّ؟ فَيُخْتَمُ عَلَى فِيهِ وَيُقَالُ لِفَخِذِهِ: انْطِقِي؛
-فَتَنْطِقُ فَخِذُهُ وَلَحْمُهُ وَعِظَامُهُ بِعَمَلِهِ، وَذَلِكَ لِيُعْذِرَ مِنْ نَفْسِهِ، وَذَلِكَ الْمُنَافِقُ،
-وَذَلِكَ الَّذِي سَخِطَ اللهُ عَلَيْهِ» .&lt;/p&gt;
-&lt;p&gt;
-আবূ হুরায়রা (রাঃ) হতে বর্ণিত, তিনি বলেন, ছাহাবীগণ বললেন, হে আল্লাহর রাসূল! কিয়ামতের দিন কী আমরা আমাদের রবকে দেখতে পাব?
-তিনি বললেন, দ্বিপ্রহরে মেঘমুক্ত আকাশে সূর্য দেখতে কি তোমাদের মধ্যে পরস্পরে বাধা সৃষ্টি হয়? তারা বললেন, না। তিনি আরও
-বললেন, মেঘমুক্ত আকাশে পূর্ণিমার রাত্রে পূর্ণ চাঁদ দেখতে কি তোমাদের কোনো প্রকারের অসুবিধা হয়? তারা বললেন, না। অতঃপর তিনি
-বললেন, সেই মহান সত্তার কসম, যাঁর হাতে
-&lt;/p&gt;
-&lt;p&gt;
-আমার প্রাণ! এই দুটির কোনো একটিকে দেখতে তোমাদের যেই পরিমাণ অসুবিধা হয়, সেই দিন তোমাদের রবকে দেখতে সেই পরিমাণ অসুবিধাও হবে
-না। এরপর রাসূল (ﷺ) বললেন, তখন আল্লাহ তাআলা কোনো এক বান্দাকে লক্ষ্য করে বলবেন, হে অমুক! আমি কি তোমাকে মর্যাদা দান করিনি?
-আমি কি তোমাকে সর্দারী দান করিনি? আমি কি তোমাকে বিবি দান করিনি? আমি কি তোমার জন্য ঘোড়া ও উটকে অনুগত করে দেয়নি? আমি কি
-তোমাকে এই সুযোগ দেয়নি যে, তুমি নিজ সম্প্রদায়ের নেতৃত্ব দিবে এবং তাদের নিকট হতে এক-চতুর্থাংশ মাল ভোগ করবে? জবাবে বান্দা
-বলবে, হ্যাঁ, (হে আমার প্রতিপালক!)। অতঃপর রাসূল (ﷺ) বলেন, তখন আল্লাহ তাআলা বান্দাকে বলবেন, আচ্ছা বলো দেখি, তোমার কি এই
-ধারণা ছিল যে, তুমি আমার সাক্ষাৎ লাভ করবে? বান্দা বলবে, না। এইবার আল্লাহ বলবেন, (দুনিয়াতে) তুমি যেভাবে আমাকে ভুলে
-গিয়েছিলে আজ আমিও (আখেরাতে) অনুরূপভাবে তোমাকে ভুলে থাকব। (অর্থাৎ তোমাকে আযাবে লিপ্ত রাখব)। অতঃপর আল্লাহ তাআলা দ্বিতীয় এক
-ব্যক্তিকে জিজ্ঞাসা করবেন, সেও অনুরূপ বলবে। তারপর তৃতীয় এক ব্যক্তির সাথে সাক্ষাৎ করবেন এবং তাকেও অনুরূপ কথা জিজ্ঞাসা করলে
-সে বলবে, হে আমার প্রতিপালক! আমি তোমার প্রতি, তোমার কিতাবের প্রতি এবং তোমার সমস্ত নবীগণের প্রতি ঈমান এনেছি, ছালাত আদায়
-করেছি, ছিয়াম পালন করেছি এবং দান-ছাদাকা করেছি। মোটকথা, সে সাধ্য পরিমাণ নিজের নেক কার্যসমূহের একটি তালিকা আল্লাহর সম্মুখে
-তুলে ধরবে। তখন আল্লাহ তাআলা বলবেন, আচ্ছা! তুমি তো তোমার কথা বললে, এখন এখানেই দাঁড়াও, এক্ষুণি তোমার ব্যাপারে সাক্ষী
-উপস্থিত করছি। এই কথা শুনে বান্দা মনে মনে চিন্তা করবে, এমন কে আছে যে, এখানে আমার বিরুদ্ধে সাক্ষ্য দিবে? অতঃপর তার মুখে
-মোহর লাগিয়ে দেওয়া হবে এবং তার রানকে বলা হবে, তুমি বলো, তখন তার রান, হাড়, মাংস প্রভৃতি এক একটি করে বলে ফেলবে, এরা যা যা
-করেছিল। তার মুখে মোহর লাগিয়ে অঙ্গ-প্রত্যঙ্গ হতে এই জন্য সাক্ষী গ্রহণ করা হবে, যেন সেই বান্দা কোনো ওযর-আপত্তি পেশ করতে না
-পারে। বস্তুত যেই বান্দার কথা আলোচনা করা হয়েছে, সে হলো মুনাফেক এবং এই কারণেই আল্লাহ তার প্রতি অত্যন্ত ক্ষুব্ধ হবেন (ছহীহ
-মুসলিম, হা/২৯৬৮; মিশকাত, হা/৫৫৫৫)।
-&lt;/p&gt;
-&lt;ar&gt;
-عَنْ عَبْدِ اللَّهِ بْنِ عَمْرٍو قَالَ: قَالَ رَسُولُ اللهِ ﷺ : «إِنَّ اللَّهَ سَيُخَلَّصُ رَجُلًا مِنْ أُمَّتِي عَلَى
-رُءُوسِ الْخَلَائِقِ يَوْمَ الْقِيَامَةِ، فَيَنْشُرُ عَلَيْهِ تِسْعَةً وَتِسْعِينَ سِجِلًا، كُلُّ سِجِلٌ مِثْلَ مَدَّ
-الْبَصَرِ ، ثُمَّ يَقُولُ أَتُنْكِرُ مِنْ هَذَا شَيْئًا أَظْلَمَكَ كَتَبَتِي الْحَافِظُونَ؟ فَيَقُولُ: لَا يَا رَبِّ
-فَيَقُولُ: أَفَلَكَ عُذْرُ؟ قَالَ: لَا يَا رَبِّ فَيَقُولُ : بَلَى؛ إِنَّ لَكَ عِنْدَنَا حَسَنَةً، وَإِنَّهُ لَا ظُلْمَ
-عَلَيْكَ الْيَوْمَ، فَتُخْرَجُ بِطَاقَةٌ فِيهَا: أَشْهَدُ أَنْ لَا إِلَهَ إِلَّا اللهُ، وَأَنَّ مُحَمَّدًا عَبْدُهُ
-وَرَسُولُهُ، فَيَقُولُ: احْضُرْ
-&lt;/ar&gt;
-&lt;ar&gt;
-وَزْنَكَ، فَيَقُولُ: يَا رَبِّ مَا هَذِهِ الْبِطَاقَةُ مَعَ هَذِهِ السِّجِلَّاتِ؟ فَيَقُولُ: إِنَّكَ لَا تُظْلَمُ،
-قَالَ: فَتُوضَعُ السِّجِلَّاتُ فِي كِفَّةٍ، وَالْبِطَاقَةُ فِي كِفَّةٍ، فَطَاشَتِ السِّجِلَّاتُ وَثَقُلَتِ الْبِطَاقَةُ؛
-فَلَا يَثْقُلُ مَعَ اسْمِ اللهِ شَيْءٌ .
-&lt;/ar&gt;
-&lt;p&gt;
-আব্দুল্লাহ ইবনু আমর (রাঃ) বলেন, রাসূলুল্লাহ (ﷺ) বলেছেন, 'কিয়ামতের দিন এমন এক ব্যক্তিকে জনসম্মুখে উপস্থিত করা হবে, যার
-আমলনামা খোলা হবে নিরানব্বই ভলিয়মে এবং প্রতি ভলিয়ম বিস্তীর্ণ হবে দৃষ্টিসীমা পর্যন্ত। অতঃপর আল্লাহ তাআলা তাকে জিজ্ঞাসা
-করবেন, আচ্ছা বলো দেখি, তুমি এর কোনো একটিকে অস্বীকার করতে পারবে? অথবা আমার লিখক ফেরেশতাগণ কি তোমার প্রতি জুলুম করেছে? সে
-বলবে, না। হে আমার রব! আল্লাহ তাআলা জিজ্ঞাসা করবেন, তবে কি তোমার পক্ষ হতে কোনো ওযর পেশ করার আছে? সে বলবে, না; হে আমার রব!
-তখন আল্লাহ বলবেন, হ্যাঁ, তোমার একটি নেকী আমার নিকট রক্ষিত আছে। তুমি নিশ্চিত জেনে রাখ, আজ তোমার প্রতি কোনো জুলুম বা
-অবিচার করা হবে না। এরপর এক টুকরা কাগজ বের করা হবে, যাতে লিখা আছে,
-&lt;/p&gt;
-&lt;ar&gt;أَشْهَدُ أَنْ لَا إِلَهَ إِلَّا اللَّهُ وَأَنَّ مُحَمَّدًا رَّسُوْلُ اللَّهِ&lt;/ar&gt;
-&lt;p&gt;
-[অর্থাৎ আমি সাক্ষ্য দিচ্ছি যে, আল্লাহ ছাড়া কোনো ইলাহ, (মা'বুদ) নেই এবং মুহাম্মাদ (ﷺ) তাঁর বান্দা ও রাসূল]। অতঃপর আল্লাহ
-তাকে বলবেন, তোমার আমলের ওজন দেখার জন্য উপস্থিত হও। তখন সে বলবে, হে আমার রব! ঐ সমস্ত বিরাট বিরাট দফতরের মুকাবিলায় এই এক
-টুকরা কাগজের মূল্যই বা কী আছে? তখন আল্লাহ বলবেন, তোমার উপর কোনো অবিচার করা হবে না। নবী করীম (ﷺ) বলেন, অতঃপর ঐ সমস্ত
-দফতরগুলো এক পাল্লায় এবং এই কাগজের টুকরাখানি আরেক পাল্লায় থাকবে। কাগজের টুকরা যে পাল্লায় থাকবে তা ভারী হয়ে নিচের দিকে
-ঝুঁকে থাকবে। মোটকথা, আল্লাহর নামের সাথে অন্য কোনো জিনিস ওজনই হতে পারবে না' (তিরমিযী, হা/২৬৩৯; ইবনু হিব্বান, হা/২২৫;
-মিশকাত, হা/৫৫৫৯)।
-&lt;/p&gt;
-&lt;ar&gt;
-عَنْ عَدِيِّ بْنِ حَاتِمٍ قَالَ : قَالَ رَسُولُ اللهِ ﷺ : «مَا مِنْكُمْ مِنْ أَحَدٍ إِلَّا سَيُكَلِّمُهُ رَبُّهُ، لَيْسَ
-بَيْنَهُ وَبَيْنَهُ تُرْجُمَانُ وَلَا حِجَابٌ يَحْجُبُهُ، فَيَنْظُرُ أَيْمَنَ مِنْهُ، فَلَا يَرَى إِلَّا مَا قَدَّمَ
-مِنْ عَمَلِهِ، وَيَنْظُرُ أَشْأَمَ مِنْهُ فَلَا يَرَى إِلَّا مَا قَدَّمَ، وَيَنْظُرُ بَيْنَ يَدَيْهِ فَلَا يَرَى إِلَّا
-النَّارَ تِلْقَاءَ وَجْهِهِ، فَاتَّقُوا النَّارَ وَلَوْ بِشِقِّ تَمْرَةٍ».
-&lt;/ar&gt;
-&lt;p&gt;
-আদী ইবনু হাতেম (রাঃ) হতে বর্ণিত, তিনি বলেন, রাসূলুল্লাহ (ﷺ) বলেছেন, তোমাদের মধ্যে এমন কেউ নেই, যার সাথে তার রব কথাবার্তা
-&lt;/p&gt;
-&lt;p&gt;
-বলবেন না। তার ও তার রবের মধ্যে কোনো দোভাষী এবং এমন কোনো পর্দা থাকবে না, যা তাকে আড়াল করে রাখবে। সে তার ডানে তাকাবে, তখনও
-পূর্বে প্রেরিত আমল ছাড়া আর কিছুই দেখতে পাবে না। আবার বামে তাকাবে, তখনও পূর্ব প্রেরিত আমল ছাড়া আর কিছুই দেখতে পাবে না। আর
-সম্মুখের দিকে তাকালে জাহান্নাম ছাড়া আর কিছুই দেখতে পাবে না। যা একেবারে চেহারার সম্মুখে অবস্থিত। সুতরাং খেজুর ছালের
-বিনিময়ে হলেও জাহান্নাম হতে বাঁচতে চেষ্টা করো' (ছহীহ বুখারী, হা/৭৫১২; মিশকাত, হা/৫৫৫০)।
-&lt;/p&gt;
-&lt;ar&gt;
-عَنْ أَبِي سَعِيدٍ الْخُدْرِي قَالَ قَالَ رَسُولُ اللهِ ( وَالَّذِي نَفْسِي بِيَدِهِ لَا تَقُومُ السَّاعَةُ حَتَّى
-تُكَلِّمَ السَّاعَةُ الإِنْسَ وَحَتَّى تُكَلِّمَ الرَّجُلَ عَذَبَةُ سَوْطِهِ وَشِرَاكُ نَعْلِهِ وَتُخْبِرَهُ فَخِذْهُ
-بِمَا أَحْدَثَ أَهْلُهُ مِنْ بَعْدِهِ ».
-&lt;/ar&gt;
-&lt;p&gt;
-আবু সাঈদ খুদরী (রাঃ) বলেন, রাসূলুল্লাহ (ﷺ) বলেছেন, সেই মহান সত্তার কসম, যার হাতে আমার প্রাণ! সেই সময় পর্যন্ত কিয়ামত
-কায়েম হবে না যে পর্যন্ত না হিংস্র পশু মানুষের সাথে কথা বলবে এবং যে পর্যন্ত না কারও চাবুক তার সাথে কথা বলবে, তার জুতার
-ফিতা তার সাথে কথা বলবে। আর তার উরু তাকে জানিয়ে দিবে যে, তার অনুপস্থিতিতে তার স্ত্রী কী করেছে' (তিরমিযী, হা/২১৮১; মিশকাত,
-হা/৫৪৫৯)।
-&lt;/p&gt;
-&lt;ar&gt;
-عَنْ بَهِزِ بْنِ حَكِيمٍ عَنْ أَبِيْهِ عَنْ جَدِّهِ عَنِ النَّبِيِّ ﷺ قَالَ: «إِنَّكُمْ تُدْعَوْنَ مُقَدَّمُ عَلَى
-أَفْوَاهِكُمْ بِالْقِدَامِ، فَأَوَّلُ مَا يُسْأَلُ عَنْ أَحَدِكُمْ فَخِدْهُ وَكَفُهُ».
-&lt;/ar&gt;
-&lt;p&gt;
-বাহয ইবনু হাকীম তাঁর পিতার মধ্যস্থতায় বর্ণনা করেন, তাঁর দাদা বলেন, নবী কারীম (ﷺ) বলেছেন, 'নিশ্চয়ই তোমাদের মুখ বন্ধ করে
-ডাকা হবে। সেদিন তোমাদের মুখ বন্ধ থাকবে। সর্বপ্রথম তোমাদের উরু এবং কব্জিকে জিজ্ঞাসা করা হবে' ('শারহুস-সুন্নাহ লিল বাগাবী,
-হা/৭/৪৩৪; আল মুজামুল কাবীর, হা/৯৬৯)।
-&lt;/p&gt;
-&lt;ar&gt;
-عَنْ عُقْبَةَ بْنِ عَامِرٍ أَنَّهُ سَمِعَ النَّبِيَّ ﷺ يَقُولُ « إِنَّ أَوَّلَ عَظْمٍ مِنَ الْإِنْسَانِ يَتَكَلَّمُ
-يَوْمَ يُخْتَمُ عَلَى الأَفْوَاهِ فَخِذُهُ مِنَ الرِّجْلِ الشِّمَالِ ».
-&lt;/ar&gt;
-&lt;p&gt;
-উক্ববা ইবনু আমের (রাঃ) হতে বর্ণিত, তিনি রাসূলুল্লাহ (ﷺ)-কে বলতে শুনেছেন, 'কিয়ামতের দিন মানুষের যখন মুখ বন্ধ থাকবে, তখন
-তার বাম উরুর হাড় সর্বপ্রথম কথা বলবে' (মুসনাদে আহমাদ, হা/১৭৪১২; সিলসিলা ছহীহা, হা/২৭১৩)।
-&lt;/p&gt;&lt;/div&gt;</t>
+&lt;ar&gt;عَنِ ابْنِ عُمَرَ قَالَ قَالَ رَسُولُ اللهِ ﷺ إِنَّ اللهَ يُدْنِي الْمُؤْمِنَ فَيَضَعُ عَلَيْهِ كَنَفَهُ، وَيَسْتُرُهُ فَيَقُولُ أَتَعْرِفُ ذَنْبَ كَذَا أَتَعْرِفُ ذَنْبَ كَذَا فَيَقُولُ نَعَمْ أَيْ رَبِّ . حَتَّى إِذَا قَرَّرَهُ بِذُنُوبِهِ وَرَأَى فِي نَفْسِهِ أَنَّهُ هَلَكَ قَالَ سَتَرْتُهَا عَلَيْكَ فِي الدُّنْيَا، وَأَنَا أَغْفِرُهَا لَكَ الْيَوْمَ ، فَيُعْطَى كِتَابَ حَسَنَاتِهِ، وَأَمَّا الْكَافِرُ وَالْمُنَافিقُونَ فَيَقُولُ الْأَشْهَادُ هَؤُلَاءِ الَّذِينَ كَذَبُوا عَلَى رَبِّهِمْ، أَلَا لَعْنَةُ اللَّهِ عَلَى الظَّالِمِينَ » .&lt;/ar&gt;
+&lt;p&gt;ইবনু উমার (রাঃ) বলেন, রাসূলুল্লাহ (ﷺ) বলেছেন, '(কিয়ামতের দিন) আল্লাহ তাআলা মুমিনদের নিজের নিকটবর্তী করবেন এবং আল্লাহ তাআলা নিজ বাজু তার উপরে রেখে তাকে ঢেকে নিবেন। অতঃপর আল্লাহ সেই বান্দাকে বলবেন, আচ্ছা! বলো দেখি, এই গুনাহটি তুমি করেছ কি? এই গুনাহটি সম্পর্কে তুমি অবগত আছ কি? সে বলবে হ্যাঁ, হে আমার রব! আমি অবগত আছি। শেষ পর্যন্ত এক একটি করে তার কৃত সমস্ত গুনাহের স্বীকৃতি আদায় করবেন। এদিকে সে বান্দা মনে মনে এই ধারণা করবে যে, সে এই সমস্ত অপরাধের কারণে নিশ্চিত ধ্বংস হবে। তখন আল্লাহ তাআলা বলবেন, দুনিয়াতে আমি তোমার এই সমস্ত অপরাধ ঢেকে রেখেছিলাম। আর আজ আমি তা মাফ করে দিব। অতঃপর তাকে নেকীর আমলনামা দেওয়া হবে। আর কাফের ও মুনাফেকদের সমস্ত সৃষ্টির সম্মুখে আনয়ন করা হবে এবং উচ্চৈস্বরে এই ঘোষণা দেওয়া হবে- এরা তারা, যারা স্বীয় পরওয়ারদিগারের বিরুদ্ধে মিথ্যারোপ করত। জেনে রাখ, এই সমস্ত জালেমদের উপর আজ আল্লাহর লানত' (ছহীহ বুখারী, হা/২৪৪১; ছহীহ মুসলিম, হা/২৭৬৮; মিশকাত, হা/৫৫৫১)।&lt;/p&gt;
+&lt;ar&gt;عَنْ أَنَسِ بْنِ مَالِكٍ قَالَ كُنَّا عِنْدَ رَسُولُ اللهِ ﷺ فَضَحِكَ فَقَالَ « هَلْ تَدْرُونَ مِمَّ أَضْحَكُ ». قَالَ قُلْنَا اللهُ وَرَسُولُهُ أَعْلَمُ . قَالَ « مِنْ مُخَاطَبَةِ الْعَبْدِ رَبَّهُ يَقُولُ يَا رَبِّ أَلَمْ تُجِرْنِي مِنَ الظُّلْمِ قَالَ يَقُولُ بَلَى قَالَ فَيَقُولُ فَإِنِّي لا أُجِيرُ عَلَى نَفْسِي إِلَّا شَاهِدًا مِنِّي قَالَ فَيَقُولُ كَفَى بِنَفْسِكَ الْيَوْمَ عَلَيْكَ شَهِيدًا وَبِالْكِرَامِ الْكَاتِبِينَ شُهُودًا - قَالَ - فَيُحْتَمَ عَلَى فِيهِ فَيُقَالُ لأَرْكَانِهِ انْطِقِي. قَالَ فَتَنْطِقُ بِأَعْمَالِهِ - قَالَ - ثُمَّ يُخَلَّى بَيْنَهُ وَبَيْنَ الْكَلَامِ - قَالَ - فَيَقُولُ بُعْدًا لَكُنَّ وَسُحْقًا. فَعَنْكُنَّ كُنْتُ أُنَاضِلُ ».&lt;/ar&gt;
+&lt;p&gt;আনাস (রাঃ) হতে বর্ণিত, তিনি বলেন, আমরা রাসূলুল্লাহ (ﷺ)-এর কাছে ছিলাম, হঠাৎ তিনি হাসলেন। অতঃপর জিজ্ঞাসা করলেন, তোমরা কি জান আমি কেন হাসছি? আমরা বললাম, আল্লাহ এবং তাঁর রাসূলই ভালো জানেন। তিনি বললেন, কিয়ামতের দিন বান্দা যে তার রবের সাথে সরাসরি কথা বলবে, সেই কথাটি স্মরণ করে হাসছি। বান্দা বলবে, হে রব! তুমি কি আমাকে জুলুম হতে নিরাপত্তা দান করনি? আল্লাহ বলবেন, হ্যাঁ, তখন বান্দা বলবে, আজ আমি আমার সম্পর্কে আপনজন ব্যতীত আমার বিরুদ্ধে অন্য কারো সাক্ষ্য গ্রহণ করব না। তখন আল্লাহ বলবেন, আজ তুমি নিজেই তোমার সাক্ষী হিসাবে এবং কিরামান-কাতেবীনের সাক্ষ্যই তোমার জন্য যথেষ্ট। অতঃপর আল্লাহ তাআলা তার মুখের উপর মোহর লাগিয়ে দিবেন এবং অঙ্গ-প্রত্যঙ্গকে বলা হবে, তোমরা কে কখন কী কী কাজ করেছ বলো। তখন অঙ্গ-প্রত্যঙ্গসমূহ তাদের কৃতকর্মসমূহ প্রকাশ করে দিবে। এরপর তার মুখকে স্বাভাবিক অবস্থায় খুলে দেওয়া হবে। তখন সে স্বীয় অঙ্গসমূহকে লক্ষ্য করে আক্ষেপের সাথে বলবে, হে দুর্ভাগা অঙ্গসমূহ! তোরা দূর হ! তোদের ধ্বংস হৌক! তোদের জন্যই তো আমি আমার রবের সাথে ঝগড়া করেছিলাম' (ছহীহ মুসলিম, হা/২৯৬৯; মিশকাত, হা/৫৫৫৪)।&lt;/p&gt;
+&lt;ar&gt;عَنْ أَبِي هُرَيْرَةَ قَالَ: قَالُوا : يَا رَسُولَ اللهِ! هَلْ نَرَى رَبَّنَا يَوْمَ الْقِيَامَةِ؟ قَالَ: هَلْ تُضَارُّونَ فِي رؤْيَةِ الشَّمْسِ فِي الظَّهِيرَةِ لَيْسَتْ فِي سَحَابَةٍ؟ قَالُوا: لَا ، قَالَ: فَهَلْ تُضَارُّونَ فِي رُؤْيَةِ الْقَمَرِ لَيْلَةَ الْبَدْرِ لَيْسَتْ فِي سَحَابَةٍ؟ قَالُوا : لَا. قَالَ: فَوَالَّذِي نَفْسِي بِيَدِهِ لَا تُضَارُّونَ فِي رُؤْيَةِ رَبِّكُمْ إِلَّا كَمَا تُضَارُّونَ فِي رُؤْيَةِ أَحَدِهِمَا. قَالَ: فَيَلْقَى الْعَبْدَ فَيَقُولُ: أَيْ قُلْ: أَلَمْ أُكْرِمْكَ وَأُسَوَّدْكَ وَأَزَوَّجْكَ، وَأُسَخَّرْ لَكَ الْخَيْلَ وَالْإِبِلَ ، وَأَذَرْكَ تَرْأَسُ وَتَرْبَعُ؟ فَيَقُولُ: بَلَى. قَالَ: فَيَقُولُ: أَفَظَنَنْتَ أَنَّكَ مُلَاقِي؟ فَيَقُولُ لَا فَيَقُولُ: فَإِنِّي قَدْ أَنْسَاكَ كَمَا نَسِيتَنِي. ثُمَّ يَلْقَى الثَّانِي فَذَكَرَ مِثْلَهُ ، ثُمَّ يَلْقَى الثَّالِثَ فَيَقُولُ لَهُ مِثْلَ ذَلِكَ، فَيَقُولُ: يَا رَبِّ آمَنْتُ بِكَ، وَبِكِতَابِكَ وَبِرُسُلِكَ، وَصَلَّيْتُ وَصُمْتُ، وَتَصَدَّقْتُ، وَيُثْنِي بِخَيْرٍ مَا اسْتَطَاعَ، يَقُولُ: هَاهُنَا إِذًا، ثُمَّ يُقَالُ: الْآنَ نَبْعَثُ شَاهِدًا عَلَيْكَ، وَيَتَفَكَّرُ فِي نَفْسِهِ: مَنْ ذَا الَّذِي يَشْهَدُ عَلَيَّ? فَيُخْتَمُ عَلَى فِيهِ وَيُقَالُ لِفَخِذِهِ: انْطِقِي؛ فَتَنْطِقُ فَخِذُهُ وَلَحْمُهُ وَعِظَامُهُ بِعَمَلِهِ، وَذَلِكَ لِيُعْذِرَ مِنْ نَفْسِهِ، وَذَلِكَ الْمُنَافِقُ، وَذَلِكَ الَّذِي سَخِطَ اللهُ عَلَيْهِ» .&lt;/ar&gt;
+&lt;p&gt;আবূ হুরায়রা (রাঃ) হতে বর্ণিত, তিনি বলেন, ছাহাবীগণ (রাঃ) বললেন, হে আল্লাহর রাসূল (ﷺ)! কিয়ামতের দিন কী আমরা আমাদের রবকে দেখতে পাব? তিনি বললেন, দ্বিপ্রহরে মেঘমুক্ত আকাশে সূর্য দেখতে কি তোমাদের মধ্যে পরস্পরে বাধা সৃষ্টি হয়? তারা বললেন, না। তিনি আরও বললেন, মেঘমুক্ত আকাশে পূর্ণিমার রাত্রে পূর্ণ চাঁদ দেখতে কি তোমাদের কোনো প্রকারের অসুবিধা হয়? তারা বললেন, না। অতঃপর তিনি বললেন, সেই মহান সত্তার কসম, যাঁর হাতে আমার প্রাণ! এই দুটির কোনো একটিকে দেখতে তোমাদের যেই পরিমাণ অসুবিধা হয়, সেই দিন তোমাদের রবকে দেখতে সেই পরিমাণ অসুবিধাও হবে না। এরপর রাসূল (ﷺ) বললেন, তখন আল্লাহ তাআলা কোনো এক বান্দাকে লক্ষ্য করে বলবেন, হে অমুক! আমি কি তোমাকে মর্যাদা দান করিনি? আমি কি তোমাকে সর্দারী দান করিনি? আমি কি তোমাকে বিবি দান করিনি? আমি কি তোমার জন্য ঘোড়া ও উটকে অনুগত করে দেয়নি? আমি কি তোমাকে এই সুযোগ দেয়নি যে, তুমি নিজ সম্প্রদায়ের নেতৃত্ব দিবে এবং তাদের নিকট হতে এক-চতুর্থাংশ মাল ভোগ করবে? জবাবে বান্দা বলবে, হ্যাঁ, (হে আমার প্রতিপালক!)। অতঃপর রাসূল (ﷺ) বলেন, তখন আল্লাহ তাআলা বান্দাকে বলবেন, আচ্ছা বলো দেখি, তোমার কি এই ধারণা ছিল যে, তুমি আমার সাক্ষাৎ লাভ করবে? বান্দা বলবে, না। এইবার আল্লাহ বলবেন, (দুনিয়াতে) তুমি যেভাবে আমাকে ভুলে গিয়েছিলে আজ আমিও (আখেরাতে) অনুরূপভাবে তোমাকে ভুলে থাকব। (অর্থাৎ তোমাকে আযাবে লিপ্ত রাখব)। অতঃপর আল্লাহ তাআলা দ্বিতীয় এক ব্যক্তিকে জিজ্ঞাসা করবেন, সেও অনুরূপ বলবে। তারপর তৃতীয় এক ব্যক্তির সাথে সাক্ষাৎ করবেন এবং তাকেও অনুরূপ কথা জিজ্ঞাসা করলে সে বলবে, হে আমার প্রতিপালক! আমি তোমার প্রতি, তোমার কিতাবের প্রতি এবং তোমার সমস্ত নবীগণের প্রতি ঈমান এনেছি, ছালাত আদায় করেছি, ছিয়াম পালন করেছি এবং দান-ছাদাকা করেছি। মোটকথা, সে সাধ্য পরিমাণ নিজের নেক কার্যসমূহের একটি তালিকা আল্লাহর সম্মুখে তুলে ধরবে। তখন আল্লাহ তাআলা বলবেন, আচ্ছা! তুমি তো তোমার কথা বললে, এখন এখানেই দাঁড়াও, এক্ষুণি তোমার ব্যাপারে সাক্ষী উপস্থিত করছি। এই কথা শুনে বান্দা মনে মনে চিন্তা করবে, এমন কে আছে যে, এখানে আমার বিরুদ্ধে সাক্ষ্য দিবে? অতঃপর তার মুখে মোহর লাগিয়ে দেওয়া হবে এবং তার রানকে বলা হবে, তুমি বলো, তখন তার রান, হাড়, মাংস প্রভৃতি এক একটি করে বলে ফেলবে, এরা যা যা করেছিল। তার মুখে মোহর লাগিয়ে অঙ্গ-প্রত্যঙ্গ হতে এই জন্য সাক্ষী গ্রহণ করা হবে, যেন সেই বান্দা কোনো ওযর-আপত্তি পেশ করতে না পারে। বস্তুত যেই বান্দার কথা আলোচনা করা হয়েছে, সে হলো মুনাফেক এবং এই কারণেই আল্লাহ তার প্রতি অত্যন্ত ক্ষুব্ধ হবেন (ছহীহ মুসলিম, হা/২৯৬৮; মিশকাত, হা/৫৫৫৫)।&lt;/p&gt;
+&lt;ar&gt;عَنْ عَبْدِ اللَّهِ بْنِ عَمْرٍو قَالَ: قَالَ رَسُولُ اللهِ ﷺ : «إِنَّ اللَّهَ سَيُخَلَّصُ رَجُلًا مِنْ أُمَّتِي عَلَى رُءُوسِ الْخَلَائِقِ يَوْمَ الْقِيَامَةِ، فَيَنْشُرُ عَلَيْهِ تِسْعَةً وَتِسْعِينَ سِجِلًا، كُلُّ سِجِلٌ مِثْلَ مَدَّ الْبَصَرِ ، ثُمَّ يَقُولُ أَتُنْكِرُ مِنْ هَذَا شَيْئًا أَظْلَمَكَ كَتَبَتِي الْحَافِظُونَ؟ فَيَقُولُ: لَا يَا رَبِّ فَيَقُولُ: أَفَلَكَ عُذْرُ؟ قَالَ: لَا يَا رَبِّ فَيَقُولُ : بَلَى؛ إِنَّ لَكَ عِنْدَنَا حَسَنَةً، وَإِنَّهُ لَا ظُلْمَ عَلَيْكَ الْيَوْمَ، فَتُخْرَجُ بِطَاقَةٌ فِيهَا: أَشْهَدُ أَنْ لَا إِلَهَ إِلَّا اللهُ، وَأَنَّ مُحَمَّدًا عَبْدُهُ وَرَسُولُهُ، فَيَقُولُ: احْضُرْ&lt;/ar&gt;
+&lt;ar&gt;وَزْنَكَ، فَيَقُولُ: يَا رَبِّ مَا هَذِهِ الْبِطَاقَةُ مَعَ هَذِهِ السِّجِلَّاتِ؟ فَيَقُولُ: إِنَّكَ لَا تُظْلَمُ، قَالَ: فَتُوضَعُ السِّجِلَّاتُ فِي كِفَّةٍ، وَالْبِطَاقَةُ فِي كِفَّةٍ، فَطَاشَتِ السِّجِلَّاتُ وَثَقُلَتِ الْبِطَاقَةُ؛ فَلَا يَثْقُلُ مَعَ اسْمِ اللهِ شَيْءٌ .&lt;/ar&gt;
+&lt;p&gt;আব্দুল্লাহ ইবনু আমর (রাঃ) বলেন, রাসূলুল্লাহ (ﷺ) বলেছেন, 'কিয়ামতের দিন এমন এক ব্যক্তিকে জনসম্মুখে উপস্থিত করা হবে, যার আমলনামা খোলা হবে নিরানব্বই ভলিয়মে এবং প্রতি ভলিয়ম বিস্তীর্ণ হবে দৃষ্টিসীমা পর্যন্ত। অতঃপর আল্লাহ তাআলা তাকে জিজ্ঞাসা করবেন, আচ্ছা বলো দেখি, তুমি এর কোনো একটিকে অস্বীকার করতে পারবে? অথবা আমার লিখক ফেরেশতাগণ কি তোমার প্রতি জুলুম করেছে? সে বলবে, না। হে আমার রব! আল্লাহ তাআলা জিজ্ঞাসা করবেন, তবে কি তোমার পক্ষ হতে কোনো ওযর পেশ করার আছে? সে বলবে, না; হে আমার রব! তখন আল্লাহ বলবেন, হ্যাঁ, তোমার একটি নেকী আমার নিকট রক্ষিত আছে। তুমি নিশ্চিত জেনে রাখ, আজ তোমার প্রতি কোনো জুলুম বা অবিচার করা হবে না। এরপর এক টুকরা কাগজ বের করা হবে, যাতে লিখা আছে, &lt;ar&gt;أَشْهَدُ أَنْ لَا إِلَهَ إِلَّا اللَّهُ وَأَنَّ مُحَمَّدًا رَّسُوْلُ اللَّهِ&lt;/ar&gt; [অর্থাৎ আমি সাক্ষ্য দিচ্ছি যে, আল্লাহ ছাড়া কোনো ইলাহ, (মা'বুদ) নেই এবং মুহাম্মাদ (ﷺ) তাঁর বান্দা ও রাসূল]। অতঃপর আল্লাহ তাকে বলবেন, তোমার আমলের ওজন দেখার জন্য উপস্থিত হও। তখন সে বলবে, হে আমার রব! ঐ সমস্ত বিরাট বিরাট দফতরের মুকাবিলায় এই এক টুকরা কাগজের মূল্যই বা কী আছে? তখন আল্লাহ বলবেন, তোমার উপর কোনো অবিচার করা হবে না। নবী করীম (ﷺ) বলেন, অতঃপর ঐ সমস্ত দফতরগুলো এক পাল্লায় এবং এই কাগজের টুকরাখানি আরেক পাল্লায় থাকবে। কাগজের টুকরা যে পাল্লায় থাকবে তা ভারী হয়ে নিচের দিকে ঝুঁকে থাকবে। মোটকথা, আল্লাহর নামের সাথে অন্য কোনো জিনিস ওজনই হতে পারবে না' (তিরমিযী, হা/২৬৩৯; ইবনু হিব্বান, হা/২২৫; মিশকাত, হা/৫৫৫৯)।&lt;/p&gt;
+&lt;ar&gt;عَنْ عَدِيِّ بْنِ حَاتِمٍ قَالَ : قَالَ رَسُولُ اللهِ ﷺ : «مَا مِنْكُمْ مِنْ أَحَدٍ إِلَّا سَيُكَلِّمُهُ رَبُّهُ، لَيْسَ بَيْنَهُ وَبَيْنَهُ تُرْجُمَانُ وَلَا حِجَابٌ يَحْجُبُهُ، فَيَنْظُرُ أَيْمَنَ مِنْهُ، فَلَا يَرَى إِلَّا مَا قَدَّمَ مِنْ عَمَلِهِ، وَيَنْظُرُ أَشْأَمَ مِنْهُ فَلَا يَرَى إِلَّا مَا قَدَّمَ، وَيَنْظُرُ بَيْنَ يَدَيْهِ فَلَا يَرَى إِلَّا النَّارَ تِلْقَاءَ وَجْهِهِ، فَاتَّقُوا النَّارَ وَلَوْ بِشِقِّ تَمْرَةٍ».&lt;/ar&gt;
+&lt;p&gt;আদী ইবনু হাতেম (রাঃ) হতে বর্ণিত, তিনি বলেন, রাসূলুল্লাহ (ﷺ) বলেছেন, তোমাদের মধ্যে এমন কেউ নেই, যার সাথে তার রব কথাবার্তা&lt;/p&gt;
+&lt;p&gt;বলবেন না। তার ও তার রবের মধ্যে কোনো দোভাষী এবং এমন কোনো পর্দা থাকবে না, যা তাকে আড়াল করে রাখবে। সে তার ডানে তাকাবে, তখনও পূর্বে প্রেরিত আমল ছাড়া আর কিছুই দেখতে পাবে না। আবার বামে তাকাবে, তখনও পূর্ব প্রেরিত আমল ছাড়া আর কিছুই দেখতে পাবে না। আর সম্মুখের দিকে তাকালে জাহান্নাম ছাড়া আর কিছুই দেখতে পাবে না। যা একেবারে চেহারার সম্মুখে অবস্থিত। সুতরাং খেজুর ছালের বিনিময়ে হলেও জাহান্নাম হতে বাঁচতে চেষ্টা করো' (ছহীহ বুখারী, হা/৭৫১২; মিশকাত, হা/৫৫৫০)।&lt;/p&gt;
+&lt;ar&gt;عَنْ أَبِي سَعِيدٍ الْخُدْرِي  قَالَ قَالَ رَسُولُ اللهِ   ( وَالَّذِي نَفْسِي بِيَدِهِ لَا تَقُومُ السَّاعَةُ حَتَّى تُكَلِّمَ السَّاعَةُ حَتَّى تُكَلِّمَ السَّبَاعُ الإِنْسَ وَحَتَّى تُكَلِّمَ الرَّجُلَ عَذَبَةُ سَوْطِهِ وَشِرَاكُ نَعْلِهِ وَتُخْبِرَهُ فَخِذْهُ بِمَا أَحْدَثَ أَهْلُهُ مِنْ بَعْدِهِ ».&lt;/ar&gt;
+&lt;p&gt;আবু সাঈদ খুদরী (রাঃ) বলেন, রাসূলুল্লাহ (ﷺ) বলেছেন, 'সেই মহান সত্তার কসম, যার হাতে আমার প্রাণ! সেই সময় পর্যন্ত কিয়ামত কায়েম হবে না যে পর্যন্ত না হিংস্র পশু মানুষের সাথে কথা বলবে এবং যে পর্যন্ত না কারও চাবুক তার সাথে কথা বলবে, তার জুতার ফিতা তার সাথে কথা বলবে। আর তার উরু তাকে জানিয়ে দিবে যে, তার অনুপস্থিতিতে তার স্ত্রী কী করেছে' (তিরমিযী, হা/২১৮১; মিশকাত, হা/৫৪৫৯)।&lt;/p&gt;
+&lt;ar&gt;عَنْ بَهِزِ بْنِ حَكِيمٍ عَنْ أَبِيْهِ عَنْ جَدِّهِ عَنِ النَّبِيِّ ﷺ قَالَ: «إِنَّكُمْ تُدْعَوْنَ مُقَدَّمُ عَلَى أَفْوَاهِكُمْ بِالْقِدَامِ، فَأَوَّلُ مَا يُسْأَلُ عَنْ أَحَدِكُمْ فَخِدْهُ وَكَفُهُ».&lt;/ar&gt;
+&lt;p&gt;বাহয ইবনু হাকীম তার পিতার মধ্যস্থতায় বর্ণনা করেন, তার দাদা বলেন, নবী কারীম (ﷺ) বলেছেন, 'নিশ্চয়ই তোমাদের মুখ বন্ধ করে ডাকা হবে। সেদিন তোমাদের মুখ বন্ধ থাকবে। সর্বপ্রথম তোমাদের উরু এবং কব্জিকে জিজ্ঞাসা করা হবে' ('শারহুস-সুন্নাহ লিল বাগাবী, হা/৭/৪৩৪; আল মুজামুল কাবীর, হা/৯৬৯)।&lt;/p&gt;
+&lt;ar&gt;عَنْ عُقْبَةَ بْنِ عَامِرٍ أَنَّهُ سَمِعَ النَّبِيَّ ﷺ يَقُولُ « إِنَّ أَوَّلَ عَظْمٍ مِنَ الْإِنْسَانِ يَتَكَلَّمُ يَوْمَ يُخْتَمُ عَلَى الأَفْوَاهِ فَخِذُهُ مِنَ الرِّجْلِ الشِّمَالِ ».&lt;/ar&gt;
+&lt;p&gt;উক্ববা ইবনু আমের (রাঃ) হতে বর্ণিত, তিনি রাসূলুল্লাহ (ﷺ)-কে বলতে শুনেছেন, 'কিয়ামতের দিন মানুষের যখন মুখ বন্ধ থাকবে, তখন তার বাম উরুর হাড় সর্বপ্রথম কথা বলবে' (মুসনাদে আহমাদ, হা/১৭৪১২; সিলসিলা ছহীহা, হা/২৭১৩)।&lt;/p&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr"/>
@@ -697,229 +552,50 @@
       <c r="E3" s="3" t="inlineStr">
         <is>
           <t>&lt;div class="page-text"&gt;&lt;p&gt;কারো কোনো সম্পদ আত্মসাৎ করা বড় গুনাহ। এর পরিণতি ভয়াবহ। যেমন আল্লাহ তাআলা বলেন,&lt;/p&gt;
-&lt;ar&gt;
-وَمَا كَانَ لِنَبِيَّ أَنْ يَغُلَّ وَمَنْ يَغْلُلْ يَأْتِ بِمَا غَلَّ يَوْمَ الْقِيَامَةِ ثُمَّ تُوَفَّى كُلُّ نَفْسٍ
-مَا كَسَبَتْ وَهُمْ لَا يُظْلَمُوْنَ
-&lt;/ar&gt;
-&lt;p&gt;
-'আর কোনো নবীর পক্ষে আত্মসাৎ করা শোভনীয় নয় এবং কেউ আত্মসাৎ করলে, যা সে আত্মসাৎ করেছে তা উত্থান দিবসে নিয়ে আসবে। অনন্তর
-প্রত্যেক ব্যক্তি যা অর্জন করেছে তা পূর্ণরূপে দেওয়া হবে এবং তারা অত্যাচারিত হবে না' (আলে ইমরান, ৩/১৬১)। তিনি অন্যত্র
-বলেন,
-&lt;/p&gt;
-&lt;ar&gt;
-وَإِمَّا تَخَافَنَّ مِنْ قَوْمٍ خِيَانَةً فَانْبِذْ إِلَيْهِمْ عَلَى سَواءِ إِنَّ اللَّهَ لَا يُحِبُّ الْخَائِنِينَ
-&lt;/ar&gt;
-&lt;p&gt;
-'(হে নবী!) তুমি যদি কোনো সম্প্রদায়ের বিশ্বাস ভঙ্গের (খেয়ানতের) আশঙ্কা কর, তবে তোমার চুক্তিকেও প্রকাশ্যভাবে তাদের সামনে
-নিক্ষেপ করো (বাতিল করবে)। নিশ্চয়ই আল্লাহ বিশ্বাস ভঙ্গকারীদের পছন্দ করেন না' (আল-আনফাল, ৮/৫৮)। তিনি অন্যত্র আরো বলেন,
-&lt;/p&gt;
+&lt;ar&gt;وَمَا كَانَ لِنَبِيَّ أَنْ يَয়ُلَّ وَمَنْ يَয়ْلُلْ يَأْتِ بِمَا غَلَّ يَوْمَ الْقِيَامَةِ ثُمَّ تُوَفَّى كُلُّ نَفْسٍ مَا كَسَبَتْ وَهُمْ لَا يُظْلَمُوْنَ&lt;/ar&gt;
+&lt;p&gt;'আর কোনো নবীর পক্ষে আত্মসাৎ করা শোভনীয় নয় এবং কেউ আত্মসাৎ করলে, যা সে আত্মসাৎ করেছে তা উত্থান দিবসে নিয়ে আসবে। অনন্তর প্রত্যেক ব্যক্তি যা অর্জন করেছে তা পূর্ণরূপে দেওয়া হবে এবং তারা অত্যাচারিত হবে না' (আলে ইমরান, ৩/১৬১)।&lt;br&gt;&lt;br&gt;তিনি অন্যত্র বলেন,&lt;/p&gt;
+&lt;ar&gt;وَإِمَّا تَخَافَنَّ مِنْ قَوْمٍ خِيَانَةً فَانْبِذْ إِلَيْهِمْ عَلَى سَواءٍ إِنَّ اللَّهَ لَا يُحِبُّ الْخَائِنِينَ&lt;/ar&gt;
+&lt;p&gt;'(হে নবী!) তুমি যদি কোনো সম্প্রদায়ের বিশ্বাস ভঙ্গের (খেয়ানতের) আশঙ্কা কর, তবে তোমার চুক্তিকেও প্রকাশ্যভাবে তাদের সামনে নিক্ষেপ করো (বাতিল করবে)। নিশ্চয়ই আল্লাহ বিশ্বাস ভঙ্গকারীদের পছন্দ করেন না' (আল-আনফাল, ৮/৫৮)।&lt;br&gt;&lt;br&gt;তিনি অন্যত্র আরো বলেন,&lt;/p&gt;
 &lt;ar&gt;ذَلِكَ لِيَعْلَمَ أَنِّي لَمْ أَخُنْهُ بِالْغَيْبِ وَأَنَّ اللَّهَ لَا يَهْدِي كَيْدَ الْخَائِنِين&lt;/ar&gt;
-&lt;p&gt;
-'ইউসুফ বললেন, এটা এজন্য যে, যাতে তিনি জানতে পারেন যে, তার অনুপস্থিতিতে আমি তার প্রতি বিশ্বাসঘাতকতা করিনি এবং আল্লাহ
-বিশ্বাসঘাতকদের ষড়যন্ত্র সফল করেন না' (ইউসুফ, ১২/৫২)। আয়াত দ্বারা প্রতীয়মান হয় যে, ইউসুফ বাদশার স্ত্রীর সাথে অন্যায় কর্মে
-লিপ্ত হননি। হলে তা হতো বিশ্বাসঘাতকতা। আল্লাহ অন্যত্র বলেন, তিনি অন্যত্র বলেন,
-&lt;/p&gt;
-&lt;ar&gt;
-يَا أَيُّهَا الَّذِينَ آمَنُوا لَا تَخُوْنُوْا اللهَ وَالرَسُوْلَ وَتَخَوْنُوْا أَمَانَاتِكُمْ وَأَنْتُمْ تَعْلَمُوْنَ
-&lt;/ar&gt;
-&lt;p&gt;
-'হে মুমিনগণ! তোমরা জেনে শুনে আল্লাহ ও তাঁর রাসূল-এর সাথে খিয়ানত করবে না, আর তোমাদের পরস্পরের আমানতসমূহেরও (গচ্ছিত
-দ্রব্যের সম্পর্কেও) খিয়ানত করবে না' (আল-আনফাল, ৮/২৭)।
-&lt;/p&gt;
-&lt;ar&gt;
-عَنْ أَبِي هُرَيْرَةَ إِنَّ النَّبِيَّ ﷺ قَالَ : " لَا يَزْنِي الزَّانِي حِيْنَ يَزْنِي وَهُوَ مُؤْمِنٌ، وَلَا يَشْرَبُ
-الْخَمْرَ حِينَ يَشْرَبُهَا وَهُوَ مُؤْمِنٌ ، وَلَا يَسْرِقُ السَّارِقُ حِيْنَ يَسْرِقُ وَهُوَ مُؤْمِنٌ، وَلَا
-يَنْتَهِبُ نُهْبَةً ذَاتَ شَرَفٍ يَرْفَعُ النَّاسُ إِلَيْهِ فِيهَا أَبْصَارَهُمْ حِيْنَ يَنْتَهِبُهَا وَهُوَ مُؤْمِنٌ،
-وَلَا يَغُلُّ أَحَدُكُمْ حِيْنَ يَغُلُّ وَهُوَ مُؤْمِنٌ فَإِيَّاكُمْ إِيَّاكُمْ».
-&lt;/ar&gt;
-&lt;p&gt;
-আবু হুরায়রা (রাঃ) বলেন, রাসূলুল্লাহ (ﷺ) এরশাদ করেন, ১. কোনো যেনাকার যেনা করতে পারে না যখন সে যেনা করে, মুমিন থাকা
-অবস্থায়। ২. কোনো মদখোর মদপান করতে পারে না যখন সে মদ্যপান করে, মুমিন থাকা অবস্থায়। ৩. কোনো চোর চুরি করতে পারে না যখন সে
-চুরি করে, মুমিন থাকা অবস্থায়। ৪. কোনো ডাকাত এরূপে ডাকাতি বা ছিনতাই করতে পারে না যে লোক তার প্রতি নযর উঠিয়ে দেখে (অর্থাৎ
-প্রকাশ্যে) যখন সে ডাকাতি করে, মুমিন থাকা অবস্থায়। ৫. তোমাদের কেউ গনীমতের মালে (বা কোনো মালে) খেয়ানত করতে পারে না যখন সে
-খেয়ানত করে, মুমিন থাকা অবস্থায়। অতএব তোমরা সাবধান হও? তোমরা সাবধান হও' (ছহীহ মুসলিম, হা/৫৭; ছহীহ বুখারী, হা/৬৭৭২;
-মিশকাত, হা/৫৩)। এই হাদীছ দ্বারা বুঝা যায় যে, মানুষ যখন খিয়ানত করে তখন মুমিন থাকে না। মুমিন হওয়ার জন্য তওবা করতে হবে।
-&lt;/p&gt;
-&lt;ar&gt;
-عَنْ أَبِي هُرَيْرَةَ قَالَ: قَالَ رَسُولُ اللهِ ﷺ: «آيَةُ الْمُنَافِقِ ثَلَاثُ إِذَا حَدَّثَ كَذَبَ، وَإِذَا وَعَدَ
-أَخْلَفَ، وَإِذَا اؤْتُمِنَ خَانَ».
-&lt;/ar&gt;
-&lt;p&gt;
-আবূ হুরায়রা (রাঃ) বলেন, রাসূলুল্লাহ (ﷺ) বলেছেন, 'মুনাফিকের আলামত হচ্ছে তিনটা- যখন সে কথা বলে, মিথ্যা বলে, যখন ওয়াদা করে,
-ভঙ্গ করে এবং যখন তার নিকট কোনো কিছু আমানত রাখা হয়, তা সে খিয়ানত করে' (ছহীহ বুখারী, হা/২৭৪৯; ছহীহ মুসলিম, হা/৬৯; মিশকাত,
-হা/৫৫)।
-&lt;/p&gt;
-&lt;ar&gt;
-عَنْ أَنَسٍ قَالَ قَلَّمَا خَطَبَنَا رَسُولُ اللهِ ﷺ إِلَّا قَالَ : «لَا إِيمَانَ لِمَنْ لَا أَمَانَةَ لَهُ، وَلَا دِينَ
-لِمَنْ لَا عَهْدَ لَهُ».
-&lt;/ar&gt;
-&lt;p&gt;
-আনাস (রাঃ) হতে বর্ণিত, তিনি বলেন, রাসূলুল্লাহ (ﷺ) আমাদের এরূপ উপদেশ খুব কমই দিয়েছেন যাতে একথাগুলো বলেননি যে, 'যার
-আমানতদারী নেই তার ঈমান নেই এবং যার অঙ্গীকারের মূল্য নেই তার দ্বীন-ধর্ম নেই' (মুসনাদে আহমাদ, হা/১২৪০৬; মিশকাত, হা/৩৫)।
-&lt;/p&gt;
+&lt;p&gt;'ইউসুফ বললেন, এটা এজন্য যে, যাতে তিনি জানতে পারেন যে, তার অনুপস্থিতিতে আমি তার প্রতি বিশ্বাসঘাতকতা করিনি এবং আল্লাহ বিশ্বাসঘাতকদের ষড়যন্ত্র সফল করেন না' (ইউসুফ, ১২/৫২)।&lt;br&gt;&lt;br&gt;আয়াত দ্বারা প্রতীয়মান হয় যে, ইউসুফ বাদশার স্ত্রীর সাথে অন্যায় কর্মে লিপ্ত হননি। হলে তা হতো বিশ্বাসঘাতকতা। আল্লাহ অন্যত্র বলেন, তিনি অন্যত্র বলেন,&lt;/p&gt;
+&lt;ar&gt;يَا أَيُّهَا الَّذِينَ آمَنُوا لَا تَخُوْنُوْا اللهَ وَالرَسُوْلَ وَتَخَوْنُوْا أَمَانَاتِكُمْ وَأَنْتُمْ تَعْلَمُوْনَ&lt;/ar&gt;
+&lt;p&gt;'হে মুমিনগণ! তোমরা জেনে শুনে আল্লাহ ও তাঁর রাসূল-এর সাথে খিয়ানত করবে না, আর তোমাদের পরস্পরের আমানতসমূহেরও (গচ্ছিত দ্রব্যের সম্পর্কেও) খিয়ানত করবে না' (আল-আনফাল, ৮/২৭)।&lt;/p&gt;
+&lt;ar&gt;عَنْ أَبِي هُرَيْرَةَ  إِنَّ النَّبِيَّ ﷺ قَالَ : " لَا يَزْنِي الزَّانِي حِيْنَ يَزْنِي وَهُوَ مُؤْمِنٌ، وَلَا يَشْرَبُ الْخَمْرَ حِينَ يَشْرَبُهَا وَهُوَ مُؤْمِنٌ ، وَلَا يَسْرِقُ السَّارِقُ حِيْنَ يَسْرِقُ وَهُوَ مُؤْمِنٌ، وَلَا يَنْتَهِبُ نُهْبَةً ذَاتَ شَرَفٍ يَرْفَعُ النَّاسُ إِلَيْهِ فِيهَا أَبْصَارَهُمْ حِيْنَ يَنْتَهِبُهَا وَهُوَ مُؤْمِنٌ، وَلَا يَغُلُّ أَحَدُكُمْ حِيْنَ يَغُلُّ وَهُوَ مُؤْمِنٌ فَإِيَّاكُمْ إِيَّاكُمْ».&lt;/ar&gt;
+&lt;p&gt;আবু হুরায়রা (রাঃ) বলেন, রাসূলুল্লাহ (ﷺ) এরশাদ করেন, ১. কোনো যেনাকার যেনা করতে পারে না যখন সে যেনা করে, মুমিন থাকা অবস্থায়। ২. কোনো মদখোর মদপান করতে পারে না যখন সে মদ্যপান করে, মুমিন থাকা অবস্থায়। ৩. কোনো চোর চুরি করতে পারে না যখন সে চুরি করে, মুমিন থাকা অবস্থায়। ৪. কোনো ডাকাত এরূপে ডাকাতি বা ছিনতাই করতে পারে না যে লোক তার প্রতি নযর উঠিয়ে দেখে (অর্থাৎ প্রকাশ্যে) যখন সে ডাকাতি করে, মুমিন থাকা অবস্থায়। ৫. তোমাদের কেউ গনীমতের মালে (বা কোনো মালে) খেয়ানত করতে পারে না যখন সে খেয়ানত করে, মুমিন থাকা অবস্থায়। অতএব তোমরা সাবধান হও! তোমরা সাবধান হও' (ছহীহ মুসলিম, হা/৫৭; ছহীহ বুখারী, হা/৬৭৭২; মিশকাত, হা/৫৩)।&lt;br&gt;&lt;br&gt;এই হাদীছ দ্বারা বুঝা যায় যে, মানুষ যখন খিয়ানত করে তখন মুমিন থাকে না। মুমিন হওয়ার জন্য তওবা করতে হবে।&lt;/p&gt;
+&lt;ar&gt;عَنْ أَبِي هُرَيْرَةَ قَالَ: قَالَ رَسُولُ اللهِ ﷺ: «آيَةُ الْمُنَافِقِ ثَلَاثُ إِذَا حَدَّثَ كَذَبَ، وَإِذَا وَعَدَ أَخْلَفَ، وَإِذَا اؤْتُمِنَ خَانَ».&lt;/ar&gt;
+&lt;p&gt;আবূ হুরায়রা (রাঃ) বলেন, রাসূলুল্লাহ (ﷺ) বলেছেন, 'মুনাফিকের আলামত হচ্ছে তিনটা- যখন সে কথা বলে, মিথ্যা বলে, যখন ওয়াদা করে, ভঙ্গ করে এবং যখন তার নিকট কোনো কিছু আমানত রাখা হয়, তা সে খিয়ানত করে' (ছহীহ বুখারী, হা/২৭৪৯; ছহীহ মুসলিম, হা/৬৯; মিশকাত, হা/৫৫)।&lt;/p&gt;
+&lt;ar&gt;عَنْ أَنَسٍ قَالَ قَلَّمَا خَطَبَنَا رَسُولُ اللهِ ﷺ إِلَّا قَالَ : «لَا إِيمَانَ لِمَنْ لَا أَمَانَةَ لَهُ، وَلَا دِينَ لِمَنْ لَا عَهْدَ لَهُ».&lt;/ar&gt;
+&lt;p&gt;আনাস (রাঃ) বলেন, রাসূলুল্লাহ (ﷺ) আমাদের এরূপ উপদেশ খুব কমই দিয়েছেন, যাতে একথাগুলো বলেননি যে, 'যার আমানতদারী নেই তার ঈমান নেই এবং যার অঙ্গীকারের মূল্য নেই তার দ্বীন-ধর্ম নেই' (মুসনাদে আহমাদ, হা/১২৪০৬; মিশকাত, হা/৩৫)।&lt;/p&gt;
 &lt;p&gt;এই হাদীছ দ্বারা প্রতীয়মান হয় যে, আমানত রক্ষা করা এবং অঙ্গীকার পূরণ করা পূর্ণ মুমিন হওয়ার অন্যতম বৈশিষ্ট্য।&lt;/p&gt;
-&lt;ar&gt;
-عَنْ أَبِي هُرَيْرَةَ قَالَ قَالَ رَسُولُ اللهِ ﷺ : « أَدَّ الأَمَانَةَ إِلَى مَنِ ائْتَمَنَكَ وَلَا تَحْنُ مَنْ
-خَانَكَ».
-&lt;/ar&gt;
-&lt;p&gt;
-আবু হুরায়রা (রাঃ) হতে বর্ণিত, তিনি বলেন, রাসূলুল্লাহ (ﷺ) বলেছেন, 'যে ব্যক্তি তোমার কাছে আমানত রেখেছে তাকে সময় মত আমানত
-বুঝিয়ে দাও। আর যে তোমার সাথে খিয়ানত করে তার খিয়ানত করো না' (তিরমিযী, হা/১২৬৪; আবু দাউদ, হা/৩৫৩৫; দারেমী, হা/২৬৫২;
-মিশকাত, হা/২৯৩৪)।
-&lt;/p&gt;
-&lt;ar&gt;
-عَنْ سَعِيدِ بْنِ زَيْدٍ قَالَ: قَالَ رَسُولُ اللهِ ﷺ : «مَنْ أَخَذَ شِبْرًا مِنَ الْأَرْضِ ظُلْمًا، فَإِنَّهُ
-يُطَوَّقُهُ يَوْمَ الْقِيَامَةِ مِنْ سَبْعِ أَرَضِينَ».
-&lt;/ar&gt;
-&lt;p&gt;
-সাঈদ ইবনু যায়েদ (রাঃ) হতে বর্ণিত, তিনি বলেন, রাসূলুল্লাহ (ﷺ) বলেছেন, 'যে ব্যক্তি অত্যাচার করে অর্ধহাত জমিন দখল করেছে,
-নিশ্চয়ই কিয়ামতের দিন অনুরূপ সাতটি জমিন তার কাঁধে ঝুলিয়ে দেওয়া হবে' (ছহীহ বুখারী, হা/৩১৯৮; ছহীহ মুসলিম, হা/১৬১০; মিশকাত,
-হা/২৯৩৮)।
-&lt;/p&gt;
-&lt;ar&gt;
-عَنْ سَالِمٍ عَنْ أَبِيهِ قَالَ: قَالَ رَسُولُ اللهِ ﷺ: «مَنْ أَخَذَ مِنَ الْأَرْضِ شَيْئًا بِغَيْرِ حَقَّهِ، خُسِفَ
-بِهِ يَوْমَ الْقِيَامَةِ إِلَى سَبْعِ أَرَضِينَ».
-&lt;/ar&gt;
-&lt;p&gt;
-তাবেঈ সালেম তাঁর পিতা আব্দুল্লাহ ইবনু উমর (রাঃ) হতে বর্ণনা করেন, তিনি বলেছেন, রাসূলুল্লাহ (ﷺ) বলেছেন, 'যে অনধিকারে কারো
-কিছু জমিন নিয়েছে, কিয়ামতের দিন তাকে সাত তবক জমিন পর্যন্ত ধসিয়ে দেওয়া হবে' (ছহীহ বুখারী, হা/২৪৫৪; মিশকাত, হা/২৯৫৮)।
-&lt;/p&gt;
-&lt;ar&gt;
-عَنْ يَعْلَى بْنِ مُرَّةَ قَالَ : سَمِعْتُ رَسُولُ اللهِ ﷺ يَقُولُ : «أَيُّمَا رَجُلٍ ظَلَمَ شِبْرًا مِنَ الْأَرْضِ
-كَلَّفَهُ اللهُ - عَزَّ وَجَلَّ أَنْ يَحْفিরেরُ حَتَّى يَبْلُغَ آخِرَ سَبْعِ أَرَضِينَ، ثُمَّ يُطَوَّقَهُ إِلَى يَوْمِ
-الْقِيَامَةِ حَتَّى يُقْضَى بَيْنَ النَّاسِ».
-&lt;/ar&gt;
-&lt;p&gt;
-ইয়া'লা ইবনু মুররা (রাঃ) হতে বর্ণিত, তিনি বলেন, আমি রাসূলুল্লাহ (ﷺ)-কে বলতে শুনেছি, 'যে কোন ব্যক্তি অন্যায়ভাবে কারো এক
-বিগত জমি দখল করে তাকে আল্লাহ তা সাত তবকের শেষ পর্যন্ত খুঁড়তে বাধ্য করবেন। অতঃপর তার গলায় তা শিকলরূপে পরিয়ে দেওয়া হবে,
-যাবৎ না মানুষের বিচার শেষ করা হয়' (মুসনাদে আহমাদ, হা/১৭৬০৭; মিশকাত, হা/২৯৬০)।
-&lt;/p&gt;
-&lt;ar&gt;
-عَنْ عَبْدِ اللَّهِ بْنِ عَمْرِو قَالَ: قِيلَ لِرَسُولِ اللهِ ﷺ : «أَيُّ النَّاسِ أَفْضَلُ؟ قَالَ : كُلُّ مَحْمُومٍ
-الْقَلْبِ صَدُوقِ اللِّسَانِ. قَالُوا : صَدُوقُ اللِّسَانِ نَعْرِفُهُ، فَمَا مَحْمُومُ الْقَلْبِ؟ قَالَ : هُوَ
-النَّقِيُّ، التَّقِيُّ، لَا إِثْمَ عَلَيْهِ، وَلَا بَغْيَ، وَلَا غِلَّ، وَلَا حَسَدَ».
-&lt;/ar&gt;
-&lt;p&gt;
-আব্দুল্লাহ ইবনু আমর (রাঃ) বলেন, রাসূলুল্লাহ (ﷺ)-কে জিজ্ঞাসা করা হলো, মানুষের মধ্যে উত্তম কে? তিনি বললেন, 'প্রত্যেক
-নিষ্কলুষ অন্তঃকরণ সত্যভাষী'। ছাহাবীগণ আরয করলেন, 'সুদূকুল লিসান' তো আমরা বুঝি, তবে 'মাখমুমুল কালব' কী? তিনি বললেন,
-'নির্মল ও পবিত্র অন্তঃকরণ, যা পাপ করেনি, জুলুম করেনি, যা খিয়ানত করেনি ও যা হিংসা-বিদ্বেষ হতে মুক্ত' (ইবনু মাজাহ,
-হা/৪২১৬; বায়হাক্বী শু'আবুল ঈমান, হা/৪৮০০; মিশকাত, হা/৫২২১)।
-&lt;/p&gt;
-&lt;ar&gt;
-عَنْ عَبْدِ اللَّهِ بْنِ عَمْرِو أَنَّ رَسُولُ اللهِ ﷺ قَالَ: «أَرْبَعُ إِذَا كُنَّ فِيكَ فَلَا عَلَيْكَ مَا فَاتَكَ
-مِنَ الدُّنْيَا: حِفْظُ أَمَانَةٍ، وَصِدْقُ حَدِيثٍ، وَحُسْنُ خَلِيقَةٍ، وَعِفَّةُ فِي طُعْمَةِ».
-&lt;/ar&gt;
-&lt;p&gt;
-আব্দুল্লাহ ইবনু আমর (রাঃ) হতে বর্ণিত, রাসূলুল্লাহ (ﷺ) বলেছেন, 'যখন তোমার মধ্যে চারটি বস্তু বিদ্যমান থাকে, তখন দুনিয়ার যা
-কিছুই তোমার থেকে চলে যায় তাতে তোমার কোনো ক্ষতি নেই। আমানত রক্ষা করা, সত্য কথা বলা, উত্তম চরিত্র হওয়া এবং খানা-পিনাতে
-সতর্কতা অবলম্বন করা' (মুসনাদে আহমাদ, হা/৬৩৬৫; শু'আবুল ঈমান, হা/৪৮০১; মিশকাত, হা/৫২২২)।
-&lt;/p&gt;
-&lt;ar&gt;
-عَنْ عَبْدِ اللَّهِ بْنِ عَمْرٍو قَالَ: كَانَ رَسُولُ اللهِ ﷺ إِذَا أَصَابَ غَنِيمَةً، أَمَرَ بِلَالًا فَنَادَى في
-النَّاسِ، فَيَجِيتُونَ بِغَنَائِمِهِمْ، فَيُخَمِّسُهُ وَيُقَسِّمُهُ ، فَجَاءَ رَجُلٌ يَوْمًا بَعْدَ ذَلِكَ بِزِمَامٍ
-مِنْ شَعَرٍ، فَقَالَ: يَا رَسُولُ اللَّهِ! هَذَا فِيمَا كُنَّا أَصَبْنَاهُ مِنَ الْغَنِيمَةِ، قَالَ: أَسْمَعْتَ بِلَالًا
-نَادَى ثَلَاثًا؟ قَالَ: نَعَمْ، قَالَ: فَمَا মَنَعَكَ أَنْ تَجِيءَ بِهِ؟ فَاعْتَذَرَ قَالَ: كُنْ أَنْتَ تَجِيءُ بِهِ
-يَوْمَ الْقِيَامَةِ، فَلَنْ أَقْبَلَهُ مِنْكَ .
-&lt;/ar&gt;
-&lt;p&gt;
-আব্দুল্লাহ ইবনু আমর (রাঃ) বলেন, যখনই গনীমতের মাল লাভ করতেন, তখন বেলালকে আদেশ করতেন। (তিনি যেন লোকদের যার কাছে যা কিছু
-আছে তা উপস্থিত করার জন্য ঘোষণা করেন)। তিনি জনগণের মধ্যে ঘোষণা করতেন, তখন লোকেরা তাদের স্ব স্ব গনীমত নিয়ে আসত। অতঃপর
-সমস্ত মাল হতে (বায়তুল মালের) এক-পঞ্চমাংশ বের করতেন এবং অবশিষ্টগুলো লোকদের মধ্যে বণ্টন করে দিতেন। একদা এক ব্যক্তি এর
-(খুমুস বের করা এবং সমস্ত মাল বিতরণ করে দেওয়ার) পর একখানা পশমের লাগাম নিয়ে আসল এবং বলল, হে আল্লাহর রাসূল! এটা গনীমতের
-মাল, যা আমি পেয়েছিলাম। তার কথা শুনে রাসূলুল্লাহ (ﷺ) জিজ্ঞাসা করলেন, বেলাল যে তিন (ﷺ)
-&lt;/p&gt;
-&lt;p&gt;
-তিনবার ঘোষণা করেছিল, তুমি কি তা শুনেছ? সে বলল, হ্যাঁ, (শুনেছি)। তিনি জিজ্ঞাসা করলেন, সেই সময় তা আনতে তোমাকে কে বাধা
-দিয়েছিল? তখন সে বিভিন্ন ওযর পেশ করল। রাসূল (ﷺ) বললেন, যাও, তুমি কিয়ামতের দিন এই রশি নিয়েই উপস্থিত হবে। আমি তোমার নিকট
-হতে এটা গ্রহণ করব না (আবু দাউদ, হা/১৭২১; মিশকাত, হা/৪০১২)।
-&lt;/p&gt;
-&lt;ar&gt;
-عَنْ خَوْلَةَ بِنْتِ قَيْسٍ له قَالَتْ: سَمِعْتُ رَسُولَ اللهِ ﷺ يَقُولُ: «إِنَّ هَذِهِ الْمَالَ خَضِرَةٌ حُلْوَةٌ،
-فَمَنْ أَصَابَهُ بِحَقِّهِ بُورِكَ لَهُ فِيهِ، وَرُبَّ مُتَخَوِّضٍ فِيمَا شَاءَتْ بِهِ نَفْسُهُ مِنْ مَالِ اللَّهِ
-وَرَسُولِهِ لَيْسَ لَهُ يَوْمَ الْقِيَامَةِ إِلَّا النَّارُ».
-&lt;/ar&gt;
-&lt;p&gt;
-খাওলা বিনতে কায়সা (রাঃ) হতে বর্ণিত, তিনি বলেন, আমি রাসূল (ﷺ)-কে বলতে শুনেছি, তিনি বলেন, 'নিশ্চয়ই এই পার্থিব সম্পদ শ্যামল
-ও সুমিষ্ট (অর্থাৎ আকর্ষণীয়) তবে যেই ব্যক্তি ন্যায়ভাবে প্রাপ্ত হয় তাতে তার বরকত হয়। আবার বহু লোক এমনও আছে, যে আল্লাহ ও
-তাঁর রাসূলের সম্পদে (অর্থাৎ গনীমতের মালে) যথেচ্ছা তসরূপ করে, তার জন্য কিয়ামতের দিন জাহান্নামের আগুন ব্যতীত আর কিছুই না'
-(তিরমিযী, হা/২৩৭৭; মিশকাত, হা/৪০১৭)।
-&lt;/p&gt;
-&lt;ar&gt;
-عَنْ أَبِي هُرَيْرَةَ هُ قَالَ: قَامَ فِينَا رَسُولُ اللهِ ﷺ ذاتَ يَوْمٍ، فَذَكَرَ الْغُلُولَ، فَعَظَّمَهُ وَعَظَّمَ
-أَمْرَهُ، ثُمَّ قَالَ: «لَا أُلْفِيَنَّ أَحَدَكُمْ يَجِيءُ يَوْمَ الْقِيَامَةِ عَلَى رَقَبَتِهِ بَعِيرٌ لَهُ رُغَاءُ
-يَقُولُ: يَا رَسُولَ اللَّهِ! أَغِثْنِي، فَأَقُولُ لَا أَمْلِكُ لَكَ شَيْئًا، قَدْ أَبْلَغْتُكَ. لَا أُلْفِيَنَّ
-أَحَدَكُمْ يَجِيءُ يَوْمَ الْقِيَامَةِ عَلَى رَقَبَتِهِ فُرْسُ لَهُ حَمْحَمَةٌ، فَيَقُولُ: يَا رَسُولَ اللهِ أَغِثْنِي،
-فَأَقُولُ: لَا أَمْلِكُ لَكَ شَيْئًا، قَدْ أَبْلَغْتُكَ، لَا أُلْفِيَنَّ أَحَدَكُمْ يَجِيءُ يَوْمَ الْقِيَامَةِ عَلَى
-رَقَبَتِهِ شَاةٌ لَهَا ثُغَاءُ يَقُولُ: يَا رَسُولَ اللَّهِ أَغِثْنِي، فَأَقُولُ: لَا أَمْلِكُ لَكَ شَيْئًا قَدْ
-أَبْلَغْتُكَ. لَا أُلْفِيَنَّ أَحَدَكُمْ يَجِيءُ الْقِيَامَةِ عَلَى رَقَبَتِهِ نَفْسٌ لَهَا صِيَاحٌ، فَيَقُولُ : يَا
-رَسُولَ اللهِ أَغِثْنِي، فَأَقُولُ: لَا أَمْلِكُ لَكَ شَيْئًا، قَدْ أَبْلَغْتُكَ. لَا أُلْفِيَنَّ أَحَدَكُمْ يَجِيءُ
-يَوْমَ الْقِيَامَةِ عَلَى رَقَبَتِهِ رِقَاعٌ تَخْفُقُ، فَيَقُولُ: يَا رَسُولَ اللَّهِ أَغِثْنِي، فَأَقُولُ : لَا
-أَمْلِكُ لَكَ شَيْئًا، قَدْ أَبْلَغْتُكَ. لَا أُلْفِيَنَّ أَحَدَكُمْ يَجِيءُ يَوْمَ الْقِيَامَةِ عَلَى رَقَبَتِهِ
-صَامِتُ، فَيَقُولُ: يَا رَسُولَ اللهِ أَغِثْنِي، فَأَقُولُ: لَا أَمْلِكُ لَكَ شَيْئًا، قَدْ أَبْلَغْتُكَ»
-&lt;/ar&gt;
-&lt;p&gt;
-আবূ হুরায়রা (রাঃ) হতে বর্ণিত, তিনি বলেন, একদা নবী (ﷺ) আমাদের মাঝে বক্তব্য দেওয়ার জন্য দাঁড়ালেন, তিনি খিয়ানত সম্পর্ককে
-বক্তব্য দিলেন এবং খিয়ানতের বিষয়টি খুব বড় করে পেশ করলেন। তারপর তিনি বললেন, 'কিয়ামতের দিন তোমাদের কাউকে আমি এমন অবস্থায়
-পাব যে, তার কাঁধের উপর উট চিৎকার করতে থাকবে। সে বলবে, হে আল্লাহর রাসূল! আমাকে রক্ষা করুন।
-&lt;/p&gt;
-&lt;p&gt;
-আমি বলব, আজ আল্লাহর সামনে তোমার জন্য সামান্য কিছু করার ক্ষমতা আমি রাখি না, যা পূর্বেই বলেছি। কিয়ামতের দিন আমি তোমাদের
-কাউকে এমন অবস্থায় পাব যে, তার কাঁধের উপর ঘোড়া চিৎকার করতে থাকবে। সে বলবে, হে আল্লাহর রাসূল! আমাকে রক্ষা করুন, আমি বলব,
-আজ আল্লাহর সামনে তোমার জন্য সামান্য কিছু করার ক্ষমতা আমার নেই, যা আমি পূর্বেই বলেছি। কিয়ামতের দিন আমি যেন তোমাদের কাউকে
-এই অবস্থায় দেখতে না পাই যে, সে কাঁধের উপর একটি ছাগল বহন করছে এবং আমাকে বলবে, আল্লাহর রাসূল আমাকে সাহায্য করুন। আর আমি
-বলব, আমি কিছুই করতে পারব না। আমি তো তোমাকে আল্লাহর বিধান পূর্বেই জানিয়ে দিয়েছি। কিয়ামতের দিন আমি যেন তোমাদের কাউকে এমন
-অবস্থায় দেখতে না পাই যে, সে নিজের কাঁধের উপর চিৎকাররত একটি মানুষ বহন করে নিয়ে আসবে আর আমাকে বলবে, হে আল্লাহর রাসূল!
-আমাকে সাহায্য করুন। আর আমি বলব, আজ আমি তোমার জন্য কিছুই করতে পারব না। আমি আল্লাহর বিধান তোমাকে পূর্বেই জানিয়ে দিয়েছি।
-কিয়ামতের দিন আমি যেন তোমাদের কাউকে এ অবস্থায় দেখতে না পাই যে, সে নিজের কাঁধের উপর কাপড় ইত্যাদির এক খণ্ড বহন করে নিয়ে
-আসছে। আর তা ভীষণভাবে তার কাঁধের উপর দুলছে, তখন সে আমাকে বলবে, হে আল্লাহর রাসূল! আমাকে সাহায্য করুন, আর আমি বলব, আমি
-তোমার জন্য কিছুই করতে পারব না। কিয়ামতে আমি যেন তোমাদের কাউকে এমন অবস্থায় না দেখতে পাই যে, সে নিজের কাঁধের উপর অচেতন
-সম্পদ (সোনা-চাঁদি) বহন করে নিয়ে আসছে। আর আমাকে বলবে, হে আল্লাহর রাসূল! আমাকে সাহায্য করুন। আর আমি বলব, আজ আমি তোমাকে
-কোনো সাহায্য করতে পারব না। আমি তো তোমাকে আল্লাহর বিধান পূর্বেই জানিয়ে দিয়েছি' (ছহীহ মুসলিম, হা/১৮৩১; মিশকাত, হা/৩৯৯৬)।
-&lt;/p&gt;
-&lt;ar&gt;
-عَنْ أَبِي هُرَيْرَةَ قَالَ: «أَهْدَى رَجُلٌ لِرَسُولِ اللهِ ﷺ غُلَامًا يُقَالُ لَهُ: مِدْعَمُ فَبَيْنَمَا مِدْعَمُ
-يَحُطُّ رَحْلًا لِرَسُولِ اللهِ ﷺ إِذْ أَصَابَهُ سَهْمُ عَائِرٌ فَقَتَلَهُ، فَقَالَ النَّاسُ: هَنِيئًا لَهُ الْجَنَّةُ،
-فَقَالَ رَسُولُ اللهِ ﷺ : كَلَّا ، وَالَّذِي نَفْسِي بِيَدِهِ إِنَّ الشَّمْلَةَ الَّتِي أَخَذَهَا يَوْمَ خَيْبَرَ مِنَ
-الْمَغَانِمِ لَمْ تُصِبْهَا الْمَقَاسِمُ، لَتَشْتَعِلُ عَلَيْهِ نَارًا فَلَمَّا سَمِعَ ذَلِكَ النَّاسُ جَاءَ رَجُلٌ
-بِشِرَاكٍ، أَوْ شِرَاكَيْنِ إِلَى النَّبِيِّ ﷺ فَقَالَ: شِرَاكَ مِنْ نَارٍ، أَوْ شِرَاكَانِ مِنْ نَارٍ» .
-&lt;/ar&gt;
-&lt;p&gt;
-আবূ হুরায়রা (রাঃ) বলেন, মিদআম নামে একটি গোলাম রাসূল (ﷺ)-কে হাদিয়া দিয়েছিল। মিদআম এক সময় রাসূল (ﷺ)-এর উটের পিঠের হাওদা
-নামাচ্ছিল এমতাবস্থায় একটি তীর এসে তাকে লাগে এবং সে মারা যায়। ছাহাবীগণ বলেন, তার জন্য জান্নাত। রাসূল (ﷺ) বললেন, কখনই নয়।
-&lt;/p&gt;
-&lt;p&gt;
-আল্লাহর কসম, নিশ্চয়ই ঐ চাদরটি যেটি সে 'খায়বার'-এর গনীমত বণ্টন করার পূর্বে আত্মসাৎ করেছিল সে চাদরটি জাহান্নামের আগুন তার
-উপর উত্তেজিত করছে। এ কথা শুনে একজন লোক একটি জুতার ফিতা বা দুটি জুতার ফিতা রাসূল (ﷺ)-এর নিকট নিয়ে আসল। রাসূল (ﷺ) বললেন,
-একটি বা দুটি জুতার ফিতা আত্মসাৎ করলেও জাহান্নামে যাবে (ছহীহ বুখারী, হা/৬৭০৭; ছহীহ মুসলিম, হা/১১৫; মিশকাত, হা/৩৯৯৭)।
-&lt;/p&gt;
-&lt;p&gt;এই হাদীছসমূহ দ্বারা প্রমাণিত হয় যে, আত্মসাৎকৃত বস্তু ক্ষুদ্র হলেও তার পরিণাম জাহান্নাম।&lt;/p&gt;
-&lt;ar&gt;
-عَنْ عَبْدِ اللَّهِ بْنِ عَمْرٍو قَالَ: «كَانَ عَلَى ثَقَلِ النَّبِيِّ ﷺ رَجُلٌ يُقَالُ لَهُ كَرْكَرَةُ، فَمَاتَ،
-فَقَالَ رَسُولُ اللهِ ﷺ : هُوَ فِي النَّارِ فَذَهَبُوا يَنْظُرُونَ فَوَجَدُوا عَبَاءَةٌ قَدْ غَلَّهَا .
-&lt;/ar&gt;
-&lt;p&gt;
-আব্দুল্লাহ ইবনু আমর (রাঃ) বলেন, রাসূল (ﷺ)-এর গনীমতের মালের এক ব্যক্তি দায়িত্বশীল ছিল, যে কারকারা নামে পরিচিত। সে মারা
-গেলে রাসূল (ﷺ) তাকে জাহান্নামী বলে ঘোষণা করেন। ছাহাবীগণ তার নিকট গিয়ে দেখলেন সে একটি চাদর আত্মসাৎ করেছিল (ছহীহ বুখারী,
-হা/৩০৭৪; ইবনু মাজাহ, হা/২৮৪৯, মিশকাত, হা/৩৯৯৮)।
-&lt;/p&gt;
-&lt;ar&gt;
-عَنِ ابْنِ عَبَّاسٍ قَالَ: حَدَّثَنِي عُمَرُ الله قَالَ: لَمَّا كَانَ يَوْمَ خَيْبَرَ أَقْبَلَ نَفَرُ مِنْ صَحَابَةِ
-النَّبِيِّ ﷺ فَقَالُوا: فُلَانٌ شَهِيدٌ، وَفُلَانٌ شَهِيدٌ، حَتَّى مَرُّوا عَلَى رَجُلٍ، فَقَالُوا: فُلَانٌ شَهِيدٌ.
-فَقَالَ رَسُولُ اللهِ ﷺ: كَلَّا إِنِّي رَأَيْتُهُ فِي النَّارِ فِي بُرْدَةٍ غَلَّهَا .....
-&lt;/ar&gt;
-&lt;p&gt;
-ইবনু আব্বাস (রাঃ) বলেন, উমার (রাঃ) আমাকে বললেন, 'খায়বার'-এর যুদ্ধের দিন ছাহাবীগণের একটি দল বাড়ি ফিরে আসছিলেন। ঐ সময়
-ছাহাবীগণ বললেন, অমুক অমুক শহীদ, শেষ পর্যন্ত এমন এক ব্যক্তিকে ছাহাবীগণ শহীদ বললেন, যার ব্যাপারে রাসূল (ﷺ) বললেন, কখনো নয়,
-আমি তাকে জাহান্নামে দেখছি সে একটি চাদর আত্মসাৎ করেছে' (ছহীহ মুসলিম, হা/১১৪; মিশকাত, হা/৪০৩৪; মুসনাদে আহমাদ, হা/২০৩)।
-&lt;/p&gt;
-&lt;ar&gt;
-عَنْ خَوْلَةَ الْأَنْصَارِيَّةِ قَالَتْ: قَالَ رَسُولُ اللهِ ﷺ : «إِنَّ رِجَالًا يَتَخَوَّضُونَ فِي مَالِ اللَّهِ
-بِغَيْرِ حَقٌّ؛ فَلَهُمُ النَّارُ يَوْمَ الْقِيَامَةِ».
-&lt;/ar&gt;
-&lt;p&gt;
-খাওলা আনছারী (রাঃ) হতে বর্ণিত, তিনি বলেন, আমি রাসূল (ﷺ)-কে বলতে শুনেছি, 'নিশ্চয়ই যে ব্যক্তি অন্যায়ভাবে সম্পদ দখল করবে।
-কিয়ামতের দিন তার জন্য জাহান্নাম রয়েছে' (ছহীহ বুখারী, হা/৩১১৮; মিশকাত, হা/৩৯৯৫)।
-&lt;/p&gt;&lt;/div&gt;</t>
+&lt;ar&gt;عَنْ أَبِي هُرَيْرَةَ قَالَ قَالَ رَسُولُ اللهِ ﷺ : « أَدَّ الأَمَانَةَ إِلَى مَنِ ائْتَمَنَكَ وَلَا تَخُنْ مَنْ خَانَكَ».&lt;/ar&gt;
+&lt;p&gt;আবু হুরায়রা (রাঃ) হতে বর্ণিত, তিনি বলেন, রাসূলুল্লাহ (ﷺ) বলেছেন, 'যে ব্যক্তি তোমার কাছে আমানত রেখেছে তাকে সময় মত আমানত বুঝিয়ে দাও। আর যে তোমার সাথে খিয়ানত করে তার খিয়ানত করো না' (তিরমিযী, হা/১২৬৪; আবু দাউদ, হা/৩৫৩৫; দারেমী, হা/২৬৫২; মিশকাত, হা/২৯৩৪)।&lt;/p&gt;
+&lt;ar&gt;عَنْ سَعِيدِ بْنِ زَيْدٍ قَالَ: قَالَ رَسُولُ اللهِ ﷺ : «مَنْ أَخَذَ شِبْرًا مِنَ الْأَرْضِ ظُلْمًا، فَإِنَّهُ يُطَوَّقُهُ يَوْمَ الْقِيَامَةِ مِنْ سَبْعِ أَرَضِينَ».&lt;/ar&gt;
+&lt;p&gt;সাঈদ ইবনু যায়দ (রাঃ) হতে বর্ণিত, তিনি বলেন, রাসূলুল্লাহ (ﷺ) বলেছেন, 'যে ব্যক্তি অত্যাচার করে অর্ধহাত জমিন দখল করেছে, নিশ্চয়ই কিয়ামতের দিন অনুরূপ সাতটি জমিন তার কাঁধে ঝুলিয়ে দেওয়া হবে' (ছহীহ বুখারী, হা/৩১৯৮; ছহীহ মুসলিম, হা/১৬১০; মিশকাত, হা/২৯৩৮)।&lt;/p&gt;
+&lt;ar&gt;عَنْ سَالِمٍ عَنْ أَبِيهِ قَالَ: قَالَ رَسُولُ اللهِ ﷺ: «مَنْ أَخَذَ مِنَ الْأَرْضِ شَيْئًا بِغَيْرِ حَقَّهِ، خُسِفَ بِهِ يَوْমَ الْقِيَامَةِ إِلَى سَبْعِ أَرَضِينَ».&lt;/ar&gt;
+&lt;p&gt;তাবেঈ সালেম তাঁর পিতা আব্দুল্লাহ ইবনু উমার (রাঃ) হতে বর্ণনা করেন, তিনি বলেছেন, রাসূলুল্লাহ (ﷺ) বলেছেন, 'যে অনধিকারে কারো কিছু জমিন নিয়েছে, কিয়ামতের দিন তাকে সাত তবক জমিন পর্যন্ত ধসিয়ে দেওয়া হবে' (ছহীহ বুখারী, হা/২৪৫৪; মিশকাত, হা/২৯৫৮)।&lt;/p&gt;
+&lt;ar&gt;عَنْ يَعْلَى بْنِ مُرَّةَ قَالَ : سَمِعْتُ رَسُولُ اللهِ ﷺ يَقُولُ : «أَيُّمَا رَجُلٍ ظَلَمَ شِبْرًا مِنَ الْأَرْضِ كَلَّفَهُ اللهُ - عَزَّ وَجَلَّ أَنْ يَحْفِرَهُ حَتَّى يَبْلُغَ آخِرَ سَبْعِ أَرَضِينَ، ثُمَّ يُطَوَّقَهُ إِلَى يَوْমِ الْقِيَامَةِ حَتَّى يُقْضَى بَيْنَ النَّاسِ».&lt;/ar&gt;
+&lt;p&gt;ইয়া'লা ইবনু মুররা (রাঃ) হতে বর্ণিত, তিনি বলেন, আমি রাসূলুল্লাহ (ﷺ)-কে বলতে শুনেছি, 'যে কোন ব্যক্তি অন্যায়ভাবে কারো এক বিগত জমি দখল করে তাকে আল্লাহ তা সাত তবকের শেষ পর্যন্ত খুঁড়তে বাধ্য করবেন। অতঃপর তার গলায় তা শিকলরূপে পরিয়ে দেওয়া হবে, যাবৎ না মানুষের বিচার শেষ করা হয়' (মুসনাদে আহমাদ, হা/১৭৬০৭; মিশকাত, হা/২৯৬০)।&lt;/p&gt;
+&lt;ar&gt;عَنْ عَبْدِ اللَّهِ بْنِ عَمْرِو قَالَ: قِيلَ لِرَسُولِ اللهِ ﷺ : «أَيُّ النَّاسِ أَفْضَلُ؟ قَالَ : كُلُّ مَحْمُومٍ الْقَلْبِ صَدُوقِ اللِّسَانِ. قَالُوا : صَدُوقُ اللِّسَانِ نَعْرِفُهُ، فَمَا مَحْمُومُ الْقَلْبِ؟ قَالَ : هُوَ النَّقِيُّ، التَّقِيُّ، لَا إِثْمَ عَلَيْهِ، وَلَا بَغْيَ، وَلَا غِلَّ، وَلَا حَسَدَ».&lt;/ar&gt;
+&lt;p&gt;আব্দুল্লাহ ইবনু আমর (রাঃ) বলেন, রাসূলুল্লাহ (ﷺ)-কে জিজ্ঞাসা করা হলো, মানুষের মধ্যে উত্তম কে? তিনি বললেন, 'প্রত্যেক নিষ্কলুষ অন্তঃকরণ সত্যভাষী'। ছাহাবীগণ আরয করলেন, 'সুদূকুল লিসান' তো আমরা বুঝি, তবে 'মাখমুমুল কালব' কী? তিনি বললেন, 'নির্মল ও পবিত্র অন্তঃকরণ, যা পাপ করেনি, জুলুম করেনি, যা খিয়ানত করেনি ও যা হিংসা-বিদ্বেষ হতে মুক্ত' (ইবনু মাজাহ, হা/৪২১৬; বায়হাক্বী শু'আবুল ঈমান, হা/৪৮০০; মিশকাত, হা/৫২২১)।&lt;/p&gt;
+&lt;ar&gt;عَنْ عَبْدِ اللَّهِ بْنِ عَمْرِو أَنَّ رَسُولَ اللهِ ﷺ قَالَ: «أَرْبَعُ إِذَا كُنَّ فِيكَ فَلَا عَلَيْكَ مَا فَاتَكَ مِنَ الدُّنْيَا: حِفْظُ أَمَانَةٍ، وَصِدْقُ حَدِيثٍ، وَحُسْنُ خَلِيقَةٍ، وَعِفَّةُ فِي طُعْمَةِ».&lt;/ar&gt;
+&lt;p&gt;আব্দুল্লাহ ইবনু আমর (রাঃ) হতে বর্ণিত, রাসূলুল্লাহ (ﷺ) বলেছেন, 'যখন তোমার মধ্যে চারটি বস্তু বিদ্যমান থাকে, তখন দুনিয়ার যা কিছুই তোমার থেকে চলে যায় তাতে তোমার কোনো ক্ষতি নেই। আমানত রক্ষা করা, সত্য কথা বলা, উত্তম চরিত্র হওয়া এবং খানা-পিনাতে সতর্কতা অবলম্বন করা' (মুসনাদে আহমাদ, হা/৬৩৬৫; শু'আবুল ঈমান, হা/৪৮০১; মিশকাত, হা/৫২২২)।&lt;/p&gt;
+&lt;ar&gt;عَنْ عَبْدِ اللَّهِ بْنِ عَمْرٍو قَالَ: كَانَ رَسُولُ اللهِ ﷺ إِذَا أَصَابَ غَنِيمَةً، أَمَرَ بِلَالًا فَنَادَى في النَّاسِ، فَيَجِيتُونَ بِغَنَائِمِهِمْ، فَيُخَمِّسُهُ وَيُقَسِّمُهُ ، فَجَاءَ رَجُلٌ يَوْمًا بَعْدَ ذَلِكَ بِزِمَامٍ مِنْ شَعَرٍ، فَقَالَ: يَا رَسُولَ اللَّهِ! هَذَا فِيمَا كُنَّا أَصَبْنَاهُ مِنَ الْغَنِيمَةِ، قَالَ: أَسْمَعْتَ بِلَالًا نَادَى ثَلَاثًا؟ قَالَ: نَعَمْ، قَالَ: فَمَا مَنَعَكَ أَنْ تَجِيءَ بِهِ؟ فَاعْتَذَرَ قَالَ: كُنْ أَنْتَ تَجِيءُ بِهِ يَوْمَ الْقِيَامَةِ، فَلَنْ أَقْبَلَهُ مِنْكَ .&lt;/ar&gt;
+&lt;p&gt;আব্দুল্লাহ ইবনু আমর (রাঃ) বলেন, যখনই গনীমতের মাল লাভ করতেন, তখন বেলালকে আদেশ করতেন। (তিনি যেন লোকদের যার কাছে যা কিছু আছে তা উপস্থিত করার জন্য ঘোষণা করেন)। তিনি জনগণের মধ্যে ঘোষণা করতেন, তখন লোকেরা তাদের স্ব স্ব গনীমত নিয়ে আসত। অতঃপর সমস্ত মাল হতে (বায়তুল মালের) এক-পঞ্চমাংশ বের করতেন এবং অবশিষ্টগুলো লোকদের মধ্যে বণ্টন করে দিতেন। একদা এক ব্যক্তি এর (খুমুস বের করা এবং সমস্ত মাল বিতরণ করে দেওয়ার) পর একখানা পশমের লাগাম নিয়ে আসল এবং বলল, হে আল্লাহর রাসূল! এটা গনীমতের মাল, যা আমি পেয়েছিলাম। তার কথা শুনে রাসূলুল্লাহ (ﷺ) জিজ্ঞাসা করলেন, বেলাল যে তিনবার ঘোষণা করেছে তা কি তুমি শুনেছো? সে বলল, হ্যাঁ। তিনি বললেন, তবে তা নিয়ে আসতে তোমাকে কিসে বাধা দিল? সে ওজর পেশ করল। রাসূলুল্লাহ (ﷺ) বললেন, তুমি কিয়ামতের দিন তা নিয়ে উপস্থিত হয়ো, আমি এখন তা গ্রহণ করব না।&lt;/p&gt;
+&lt;p&gt;তিনবার ঘোষণা করেছিল, তুমি কি তা শুনেছ? সে বলল, হ্যাঁ, (শুনেছি)। তিনি জিজ্ঞাসা করলেন, সেই সময় তা আনতে তোমাকে কে বাধা দিয়েছিল? তখন সে বিভিন্ন ওযর পেশ করল। রাসূল (ﷺ) বললেন, যাও, তুমি কিয়ামতের দিন এই রশি নিয়েই উপস্থিত হবে। আমি তোমার নিকট হতে এটা গ্রহণ করব না' (আবু দাউদ, হা/১৭২১; মিশকাত, হা/৪০১২)।&lt;/p&gt;
+&lt;ar&gt;عَنْ خَوْلَةَ بِنْتِ قَيْسٍ له قَالَتْ: سَمِعْتُ رَسُولَ اللهِ ﷺ يَقُولُ: «إِنَّ هَذِهِ الْمَالَ خَضِرَةٌ حُلْوَةٌ، فَمَنْ أَصَابَهُ بِحَقِّهِ بُورِكَ لَهُ فِيهِ، وَرُبَّ مُتَخَوِّضٍ فِيمَا شَاءَتْ بِهِ نَفْسُهُ مِنْ مَالِ اللَّهِ وَرَسُولِهِ لَيْسَ لَهُ يَوْمَ الْقِيَامَةِ إِلَّا النَّارُ».&lt;/ar&gt;
+&lt;p&gt;খাওলা বিনতে কায়স (রাঃ) হতে বর্ণিত, তিনি বলেন, আমি রাসূল (ﷺ)-কে বলতে শুনেছি, তিনি বলেন, 'নিশ্চয়ই এই পার্থিব সম্পদ শ্যামল ও সুমিষ্ট (অর্থাৎ আকর্ষণীয়) তবে যেই ব্যক্তি ন্যায়ভাবে প্রাপ্ত হয় তাতে তার বরকত হয়। আবার বহু লোক এমনও আছে, যে আল্লাহ ও তাঁর রাসূলের সম্পদে (অর্থাৎ গনীমতের মালে) যথেচ্ছা তসরূপ করে, তার জন্য কিয়ামতের দিন জাহান্নামের আগুন ব্যতীত আর কিছুই না' (তিরমিযী, হা/২৩৭৭; মিশকাত, হা/৪০১৭)।&lt;/p&gt;
+&lt;ar&gt;عَنْ أَبِي هُرَيْرَةَ هُ قَالَ: قَامَ فِينَا رَسُولُ اللهِ ﷺ ذَاتَ يَوْمٍ، فَذَكَرَ الْغُلُولَ، فَعَظَّمَهُ وَعَظَّمَ أَمْرَهُ، ثُمَّ قَالَ: «لَا أُلْفِيَنَّ أَحَدَكُمْ يَجِيءُ يَوْمَ الْقِيَامَةِ عَلَى رَقَبَتِهِ بَعِيرٌ لَهُ رُغَاءُ يَقُولُ: يَا رَسُولَ اللَّهِ! أَغِثْنِي، فَأَقُولُ لَا أَمْلِكُ لَكَ شَيْئًا، قَدْ أَبْلَغْتُكَ. لَا أُلْفِيَنَّ أَحَدَكُمْ يَجِيءُ يَوْমَ الْقِيَامَةِ عَلَى رَقَبَتِهِ فُرْسُ لَهُ حَمْحَمَةٌ، فَيَقُولُ: يَا رَسُولَ اللهِ أَغِثْنِي، فَأَقُولُ: لَا أَمْلِكُ لَكَ شَيْئًا، قَدْ أَبْلَغْتُكَ، لَا أُلْفِيَنَّ أَحَدَكُمْ يَجِيءُ يَوْমَ الْقِيَامَةِ عَلَى رَقَبَتِهِ شَاةٌ لَهَا ثُغَاءُ يَقُولُ: يَا رَسُولَ اللَّهِ أَغِثْنِي، فَأَقُولُ: لَا أَمْلِكُ لَكَ شَيْئًا قَدْ أَبْلَগْتُكَ. لَا أُلْفِيَنَّ أَحَدَكُمْ يَجِيءُ الْقِيَامَةِ عَلَى رَقَبَتِهِ نَفْسٌ لَهَا صِيَاحٌ، فَيَقُولُ : يَا رَسُولَ اللهِ أَغِثْنِي، فَأَقُولُ: لَا أَمْلِكُ لَكَ شَيْئًا، قَدْ أَبْلَغْتُكَ. لَا أُلْفِيَنَّ أَحَدَكُمْ يَجِيءُ يَوْমَ الْقِيَامَةِ عَلَى رَقَبَتِهِ رِقَاعٌ تَخْفُقُ، فَيَقُولُ: يَا رَسُولَ اللَّهِ أَغِثْنِي، فَأَقُولُ : لَا أَمْلِكُ لَكَ شَيْئًا، قَدْ أَبْلَغْتُكَ. لَا أُلْفِيَنَّ أَحَدَكُمْ يَجِيءُ يَوْمَ الْقِيَامَةِ عَلَى رَقَبَتِهِ صَامِتُ، فَيَقُولُ: يَا رَسُولَ اللهِ أَغِثْنِي، فَأَقُولُ: لَا أَمْلِكُ لَكَ شَيْئًا، قَدْ أَبْلَغْتُكَ»&lt;/ar&gt;
+&lt;p&gt;আবূ হুরায়রা (রাঃ) হতে বর্ণিত, তিনি বলেন, একদা নবী (ﷺ) আমাদের মাঝে বক্তব্য দেওয়ার জন্য দাঁড়ালেন, তিনি খিয়ানত সম্পর্কে বক্তব্য দিলেন এবং খিয়ানতের বিষয়টি খুব বড় করে পেশ করলেন। তারপর তিনি বললেন, 'কিয়ামতের দিন তোমাদের কাউকে আমি এমন অবস্থায় পাব যে, তার কাঁধের উপর উট চিৎকার করতে থাকবে। সে বলবে, হে আল্লাহর রাসূল! আমাকে রক্ষা&lt;/p&gt;
+&lt;p&gt;করুন। আমি বলব, আজ আল্লাহর সামনে তোমার জন্য সামান্য কিছু করার ক্ষমতা আমি রাখি না, যা পূর্বেই বলেছি। কিয়ামতের দিন আমি তোমাদের কাউকে এমন অবস্থায় পাব যে, তার কাঁধের উপর ঘোড়া চিৎকার করতে থাকবে। সে বলবে, হে আল্লাহর রাসূল! আমাকে রক্ষা করুন, আমি বলব, আজ আল্লাহর সামনে তোমার জন্য সামান্য কিছু করার ক্ষমতা আমার নেই, যা আমি পূর্বেই বলেছি। কিয়ামতের দিন আমি যেন তোমাদের কাউকে এই অবস্থায় দেখতে না পাই যে, সে কাঁধের উপর একটি ছাগল বহন করছে এবং আমাকে বলবে, আল্লাহর রাসূল আমাকে সাহায্য করুন। আর আমি বলব, আমি কিছুই করতে পারব না। আমি তো তোমাকে আল্লাহর বিধান পূর্বেই জানিয়ে দিয়েছি। কিয়ামতের দিন আমি যেন তোমাদের কাউকে এমন অবস্থায় দেখতে না পাই যে, সে নিজের কাঁধের উপর চিৎকাররত একটি মানুষ বহন করে নিয়ে আসবে আর আমাকে বলবে, হে আল্লাহর রাসূল! আমাকে সাহায্য করুন। আর আমি বলব, আজ আমি তোমার জন্য কিছুই করতে পারব না। আমি আল্লাহর বিধান তোমাকে পূর্বেই জানিয়ে দিয়েছি। কিয়ামতের দিন আমি যেন তোমাদের কাউকে এ অবস্থায় দেখতে না পাই যে, সে নিজের কাঁধের উপর কাপড় ইত্যাদির এক খণ্ড বহন করে নিয়ে আসছে। আর তা ভীষণভাবে তার কাঁধের উপর দুলছে, তখন সে আমাকে বলবে, হে আল্লাহর রাসূল! আমাকে সাহায্য করুন, আর আমি বলব, আমি তোমার জন্য কিছুই করতে পারব না। কিয়ামতে আমি যেন তোমাদের কাউকে এমন অবস্থায় না দেখতে পাই যে, সে নিজের কাঁধের উপর অচেতন সম্পদ (সোনা-চাঁদি) বহন করে নিয়ে আসছে। আর আমাকে বলবে, হে আল্লাহর রাসূল! আমাকে সাহায্য করুন। আর আমি বলব, আজ আমি তোমাকে কোনো সাহায্য করতে পারব না। আমি তো তোমাকে আল্লাহর বিধান পূর্বেই জানিয়ে দিয়েছি' (ছহীহ মুসলিম, হা/১৮৩১; মিশকাত, হা/৩৯৯৬)।&lt;/p&gt;
+&lt;ar&gt;عَنْ أَبِي هُرَيْرَةَ قَالَ: «أَهْدَى رَجُلٌ لِرَسُولِ اللهِ ﷺ غُلَامًا يُقَالُ لَهُ: مِدْعَمُ فَبَيْنَمَا مِدْعَمُ يَحُطُّ رَحْلًا لِرَسُولِ اللهِ ﷺ إِذْ أَصَابَهُ سَهْمُ عَائِرٌ فَقَتَلَهُ، فَقَالَ النَّاسُ: هَنِيئًا لَهُ الْجَنَّةُ، فَقَالَ رَسُولُ اللهِ ﷺ : كَلَّا ، وَالَّذِي نَفْسِي بِيَدِهِ إِنَّ الشَّمْلَةَ الَّتِي أَخَذَهَا يَوْمَ خَيْبَرَ مِنَ الْمَغَانِمِ لَمْ تُصِبْهَا الْمَقَاسِمُ، لَتَشْتَعِلُ عَلَيْهِ نَارًا فَلَمَّا سَمِعَ ذَلِكَ النَّاسُ جَاءَ رَجُلٌ بِشِرَاكٍ، أَوْ شِرَاكَيْنِ إِلَى النَّبِيِّ ﷺ فَقَالَ: شِرَاكَ مِنْ نَارٍ، أَوْ شِرَاكَانِ مِنْ نَارٍ» .&lt;/ar&gt;
+&lt;p&gt;আবূ হুরায়রা (রাঃ) বলেন, মিদআম নামে একটি গোলাম রাসূল (ﷺ)-কে হাদিয়া দিয়েছিল। মিদআম এক সময় রাসূল (ﷺ)-এর উটের পিঠের হাওদা নামাচ্ছিল এমতাবস্থায় একটি তীর এসে তাকে লাগে এবং সে মারা যায়। ছাহাবীগণ বলেন, তার জন্য জান্নাত। রাসূল (ﷺ) বললেন, কখনই নয়।&lt;/p&gt;
+&lt;p&gt;আল্লাহর কসম, নিশ্চয়ই ঐ চাদরটি যেটি সে 'খায়বার'-এর গনীমত বণ্টন করার পূর্বে আত্মসাৎ করেছিল সে চাদরটি জাহান্নামের আগুন তার উপর উত্তেজিত করছে। এ কথা শুনে একজন লোক একটি জুতার ফিতা বা দুটি জুতার ফিতা রাসূল (ﷺ)-এর নিকট নিয়ে আসল। রাসূল (ﷺ) বললেন, একটি বা দুটি জুতার ফিতা আত্মসাৎ করলেও জাহান্নামে যাবে (ছহীহ বুখারী, হা/৬৭০৭; ছহীহ মুসলিম, হা/১১৫; মিশকাত, হা/৩৯৯৭)।&lt;br&gt;&lt;br&gt;এই হাদীছসমূহ দ্বারা প্রমাণিত হয় যে, আত্মসাৎকৃত বস্তু ক্ষুদ্র হলেও তার পরিণাম জাহান্নাম।&lt;/p&gt;
+&lt;ar&gt;عَنْ عَبْدِ اللَّهِ بْنِ عَمْرٍو قَالَ: «كَانَ عَلَى ثَقَلِ النَّبِيِّ ﷺ رَجُلٌ يُقَالُ لَهُ كَرْكَرَةُ، فَمَاتَ، فَقَالَ رَسُولُ اللهِ ﷺ : هُوَ فِي النَّارِ فَذَهَبُوا يَنْظُرُونَ فَوَجَدُوا عَبَاءَةٌ قَدْ غَلَّهَا .&lt;/ar&gt;
+&lt;p&gt;আব্দুল্লাহ ইবনু আমর (রাঃ) বলেন, রাসূল (ﷺ)-এর গনীমতের মালের এক ব্যক্তি দায়িত্বশীল ছিল, যে কারকারা নামে পরিচিত। সে মারা গেলে রাসূল (ﷺ) তাকে জাহান্নামী বলে ঘোষণা করেন। ছাহাবীগণ তার নিকট গিয়ে দেখলেন সে একটি চাদর আত্মসাৎ করেছিল (ছহীহ বুখারী, হা/৩০৭৪; ইবনু মাজাহ, হা/২৮৪৯, মিশকাত, হা/৩৯৯৮)।&lt;/p&gt;
+&lt;ar&gt;عَنِ ابْنِ عَبَّاسٍ قَالَ: حَدَّثَنِي عُمَرُ الله قَالَ: لَمَّا كَانَ يَوْمَ خَيْبَرَ أَقْبَلَ نَفَرُ مِنْ صَحَابَةِ النَّبِيِّ ﷺ فَقَالُوا: فُلَانٌ شَهِيدٌ، وَفُلَانٌ شَهِيدٌ, حَتَّى مَرُّوا عَلَى رَجُلٍ، فَقَالُوا: فُلَانٌ شَهِيدٌ. فَقَالَ رَسُولُ اللهِ ﷺ: كَلَّا إِنِّي رَأَيْتُهُ فِي النَّارِ فِي بُرْدَةٍ غَلَّهَا .....&lt;/ar&gt;
+&lt;p&gt;ইবনু আব্বাস (রাঃ) বলেন, উমার (রাঃ) আমাকে বললেন, ''খায়বার'-এর যুদ্ধের দিন ছাহাবীগণের একটি দল বাড়ি ফিরে আসছিলেন। ঐ সময় ছাহাবীগণ বললেন, অমুক অমুক শহীদ, শেষ পর্যন্ত এমন এক ব্যক্তিকে ছাহাবীগণ শহীদ বললেন, যার ব্যাপারে রাসূল (ﷺ) বললেন, কখনো নয়, আমি তাকে জাহান্নামে দেখছি সে একটি চাদর আত্মসাৎ করেছে' (ছহীহ মুসলিম, হা/১১৪; মিশকাত, হা/৪০৩৪; মুসনাদে আহমাদ, হা/২০৩)।&lt;/p&gt;
+&lt;ar&gt;عَنْ خَوْلَةَ الْأَنْصَارِيَّةِ قَالَتْ: قَالَ رَسُولُ اللهِ ﷺ : «إِنَّ رِجَالًا يَتَخَوَّضُونَ فِي مَالِ اللَّهِ بِغَيْرِ حَقٌّ؛ فَلَهُمُ النَّارُ يَوْمَ الْقِيَامَةِ».&lt;/ar&gt;
+&lt;p&gt;খাওলা আনছারী (রাঃ) হতে বর্ণিত, তিনি বলেন, আমি রাসূল (ﷺ)-কে বলতে শুনেছি, 'নিশ্চয়ই যে ব্যক্তি অন্যায়ভাবে সম্পদ দখল করবে। কিয়ামতের দিন তার জন্য জাহান্নাম রয়েছে' (ছহীহ বুখারী, হা/৩১১৮; মিশকাত, হা/৩৯৯৫)।&lt;/p&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr"/>
@@ -943,70 +619,53 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>&lt;div class="page-text"&gt;&lt;ar&gt;
-يَا أَيُّهَا النَّاسُ كُلُوا مِمَّا فِي الْأَرْضِ حَلَالًا طَيِّبًا وَلَا تَتَّبِعُوا خُطُوَاتِ الشَّيْطَانِ إِنَّهُ
-لَكُمْ عَدُوٌّ مُبِينٌ
-&lt;/ar&gt;
-&lt;p&gt;
-'হে মানবগণ! পৃথিবীর মধ্যে যা বৈধ-পবিত্র, তা হতে ভক্ষণ করো এবং শয়তানের পদঙ্ক অনুসরণ করো না, নিশ্চয়ই সে তোমাদের প্রকাশ্য
-শত্রু' (আল-বাকারা, ২/১৬৮)।
-&lt;/p&gt;
-&lt;ar&gt;
-يَا أَيُّهَا الَّذِينَ آمَنُوا كُلُوا مِنْ طَيِّبَاتِ مَا رَزَقْنَاكُمْ وَاشْكُرُوا لِلَّهِ إِنْ كُنْتُمْ إِيَّاهُ
-تَعْبُدُونَ
-&lt;/ar&gt;
-&lt;p&gt;
-'হে ঈমানদারগণ! আমি তোমাদের যা জীবিকা স্বরূপ দান করেছি তা হতে পবিত্র বস্তুসমূহ ভক্ষণ করো এবং আল্লাহর নিকট কৃতজ্ঞতা প্রকাশ
-করো যদি তোমরা তারই ইবাদত করে থাকো' (আল-বাকারা, ২/১৭২)।
-&lt;/p&gt;
-&lt;ar&gt;يَا أَيُّهَا الرُّسُلُ كُلُوا مِنَ الطَّيِّبَاتِ وَاعْمَلُوا صَالِحًا إِنِّي بِمَا تَعْمَلُوْنَ عَلِيمٌ&lt;/ar&gt;
+          <t>&lt;div class="page-text"&gt;&lt;ar&gt;يَا أَيُّهَا النَّاسُ كُلُوا مِمَّا فِي الْأَرْضِ حَلَالًا طَيِّبًا وَلَا تَتَّبِعُوا خُطُوَاتِ الشَّيْطَانِ إِنَّهُ لَكُمْ عَدُوٌّ مُبِينٌ)&lt;/ar&gt;
+&lt;p&gt;'হে মানবগণ! পৃথিবীর মধ্যে যা বৈধ-পবিত্র, তা হতে ভক্ষণ করো এবং শয়তানের পদঙ্ক অনুসরণ করো না, নিশ্চয়ই সে তোমাদের প্রকাশ্য শত্রু' (আল-বাকারা, ২/১৬৮)।&lt;/p&gt;
+&lt;ar&gt;يَا أَيُّهَا الَّذِينَ آمَنُوا كُلُوا مِنْ طَيِّبَاتِ مَا رَزَقْنَاكُمْ وَاشْكُرُوا لِلَّهِ إِنْ كُنْتُمْ إِيَّاهُ تَعْبُدُونَ)&lt;/ar&gt;
+&lt;p&gt;'হে ঈমানদারগণ! আমি তোমাদের যা জীবিকা স্বরূপ দান করেছি তা হতে পবিত্র বস্তুসমূহ ভক্ষণ করো এবং আল্লাহর নিকট কৃতজ্ঞতা প্রকাশ করো যদি তোমরা তারই ইবাদত করে থাকো' (আল-বাকারা, ২/১৭২)।&lt;/p&gt;
+&lt;ar&gt;يَا أَيُّهَا الرُّسُلُ كُلُوا مِنَ الطَّيِّبَاتِ وَاعْمَلُوا صَالِحًا إِنِّي بِمَا تَعْمَلُوْنَ عَلِيمٌ)&lt;/ar&gt;
 &lt;p&gt;'হে রাসূলগণ! তোমরা পবিত্র বস্তু হতে আহার করো ও সৎকর্ম করো; তোমরা যা কর সে সম্বন্ধে আমি অবগত' (আল-মুমিনূন, ২৩/৫১)।&lt;/p&gt;
-&lt;ar&gt;
-عَنْ أَبِي هُرَيْرَةَ هُ قَالَ: «قَالَ رَسُولُ اللهِ اللهِ : إِنَّ اللهَ طَيِّبُ لَا يَقْبَلُ إِلَّا طَيِّبًا، وَأَنَّ
-اللَّهَ أَمَرَ الْمُؤْمِنِينَ بِمَا أَمَرَ بِهِ الْمُرْسَلِينَ ثُمَّ ذَكَرَ الرَّجُلَ يُطِيلُ السَّفَرَ، أَشْعَثَ،
-أَغْبَرَ، يَمُدُّ يَدَيْهِ إِلَى السَّمَاءِ: يَا رَبِّ يَا رَبِّ وَمَطْعَمُهُ حَرَامٌ ، وَمَشْرَبُهُ حَرَامٌ ،
-وَمَلْبَسُهُ حَرَامٌ، وَغُذَّيَ بِالْحَرَامِ، فَأَنَّى يُسْتَجَابُ لِذَلِكَ؟».
-&lt;/ar&gt;
-&lt;p&gt;
-আবু হুরায়রা (রাঃ) বলেন, রাসূল (ﷺ) বলেছেন, 'নিশ্চয়ই আল্লাহ পবিত্র, তিনি পবিত্র ছাড়া গ্রহণ করেন না। (এবং সর্বক্ষেত্রে
-পাক-পবিত্রতার আদেশই তিনি করেছেন। সেই সম্পর্কে) আল্লাহ রাসূলগণকে যে আদেশ করছেন, মুমিনগণকেও সেই আদেশই করেছেন। অতঃপর রাসূল
-(ﷺ) উল্লেখ করলেন, এক ব্যক্তি দূর-দূরান্তের সফর করছে। তার মাথার চুল এলোমেলো, শরীরে ধূলা-বালি। এমতাবস্থায় ঐ ব্যক্তি উভয়
-হস্ত আসমানের দিকে উঠিয়ে কাতর
-&lt;/p&gt;
-&lt;p&gt;
-স্বরে হে প্রভু! হে প্রভু! বলে ডাকছে। কিন্তু তার খাদ্য হারাম, তার পানীয় হারাম, তার পোশাক হারাম, তার জীবিকা নির্বাহ হারাম,
-কীভাবে তার দু'আ কবুল হবে' (ছহীহ মুসলিম, হা/১০১৫; তিরমিযী, হা/ক২৯৮৯; মিশকাত হা/২৭৬০)।
-&lt;/p&gt;
-&lt;ar&gt;
-عَنْ أَبِي هُرَيْرَةَ الله قَالَ: قَالَ رَسُولُ اللهِ ﷺ : يَأْتِي عَلَى الْمَرْءِ زَمَانٌ لَا يُبَالِي الْمَرْءُ مَا
-أَخَذَ مِنْهُ، أَمِنَ الْحَلَالِ أَمْ مِنَ الْحَرَامِ».
-&lt;/ar&gt;
-&lt;p&gt;
-আবু হুরায়রা (রাঃ) বলেন, রাসূল (ﷺ) বলেছেন, 'মানুষের সম্মুখে এমন এক যুগ আসবে যে, কেউ পরওয়া করবে না কী উপায়ে মাল অর্জন করল;
-হারাম না হালাল উপায়ে' (ছহীহ বুখারী, হা/২০৫৯; মিশকাত, হা/২৭৬১)।
-&lt;/p&gt;
-&lt;ar&gt;
-وَعَنِ النُّعْمَانِ بْنِ بَشِيرٍ قَالَ: قَالَ رَسُولُ اللهِ ﷺ : الْحَلَالُ بَيِّنُ وَالْحَرَامُ بَيِّنٌ، وَبَيْنَهُمَا
-مُشْتَبِهَاتٌ لَا يَعْلَمُهُنَّ كَثِيرٌ مِنَ النَّاسِ، فَمَنِ اتَّقَى الشُّبَهَاتِ اسْتَبْرَأَ لِدِينِهِ وَعِرْضِهِ،
-وَمَنْ وَقَعَ فِي الْحَرَامِ كَالرَّاعِي يَرْعَى حَوْلَ الْحِمَى يُوشِكُ أَنْ يَرْتَعَ فِيهِ، أَلَا وَإِنَّ لِكُلِّ
-مَلِكٍ حِمّى أَلَا وَإِنَّ حِمَى اللَّهِ مَحَارِمُهُ، أَلَا وَإِنَّ فِي الْجَسَدِ مُضْغَةً إِذَا صَلُحَتْ صَلَحَ
-الْجُسَدُ كُلُّهُ، وَإِذَا فَسَدَتْ فَسَدَ الْجَسَدُ كُلُّهُ، أَلَا وَهِيَ الْقَلْبُ».
-&lt;/ar&gt;
-&lt;p&gt;
-নু'মান ইবনু বাশীর (রাঃ) হতে বর্ণিত, তিনি বলেন, রাসূলুল্লাহ (ﷺ) বলেছেন, 'হালাল এবং হারাম সুস্পষ্ট, আর উভয়ের মধ্যে অনেক
-সন্দেহজনক বিষয় বা বস্তু আছে। যেগুলো (হালালের অন্তর্ভুক্ত না হারামের অন্তর্ভুক্ত,) সে সম্পর্কে অনেকেই সিদ্ধান্ত নিতে পারে
-না। এরূপ ক্ষেত্রে যেই ব্যক্তি সন্দেহের বস্তুকে পরিহার করে চলবে, তার দ্বীন এবং আবরু-ইজ্জত, মান-সম্মান পাক-পবিত্র থাকবে।
-পক্ষান্তরে, যেই ব্যক্তি সন্দেহের কাজে লিপ্ত হবে, সে অচিরেই হারামেও লিপ্ত হয়ে পড়বে। (ফলে তার দ্বীন এবং মান-সম্মান কলুষিত
-হবে।) যেমন যেই রাখাল তার পশুপালকে নিষিদ্ধ এলাকার সীমার ধারে চরাবে, খুব সম্ভব তার পশু নিষিদ্ধ এলাকার ভিতরেও মুখ ঢুকিয়ে
-দিবে। তোমরা স্মরণ রেখো প্রত্যেক বাদশাহরই নিজ পশুপালের চারণভূমি (নিষিদ্ধ এলাকা) বানিয়ে রাখেন। তদ্রুপ (সকল বাদশাহর বাদশাহ)
-আল্লাহ তাআলার চারণভূমি তাঁর হারাম বস্তুসমূহকে নির্ধারিত করে রেখেছেন। 'মনে রেখো মানুষের দেহের ভিতরে একটি গোশতের টুকরা
-রয়েছে, যা সঠিক থাকলে সমস্ত দেহই সঠিক থাকে। আর সেই অংশের বিকৃতি ঘটলে সম্পূর্ণ দেহেরই বিকৃতি ঘটে। সেই গোশতের টুকরাটি হলো
-অন্তর' (ছহীহ বুখারী, হা/৫২; ছহীহ মুসলিম, হা/১৫৯৯; মিশকাত, হা/২৭৬২)।
-&lt;/p&gt;
-&lt;ar&gt;
-عَنْ رَافِعِ بْنِ خَدِيجٍ قَالَ : قَالَ رَسُولُ اللهِ : ثَمَنُ الْكَلْبِ خَبِيثُ، وَمَهْرُ الْبَغِيِّ خَبِيتٌ، وَكَسْبُ
-الْحَجَّامِ خَبِيتٌ .
-&lt;/ar&gt;&lt;/div&gt;</t>
+&lt;ar&gt;عَنْ أَبِي هُرَيْرَةَ هُ قَالَ: «قَالَ رَسُولُ اللهِ اللهِ : إِنَّ اللهَ طَيِّبُ لَا يَقْبَلُ إِلَّا طَيِّبًا، وَأَنَّ اللَّهَ أَمَرَ الْمُؤْمِنِينَ بِمَا أَمَرَ بِهِ الْمُرْسَلِينَ ثُمَّ ذَكَرَ الرَّجُلَ يُطِيلُ السَّفَرَ، أَشْعَثَ، أَغْبَرَ، يَمُدُّ يَدَيْهِ إِلَى السَّمَاءِ: يَا رَبِّ يَا رَبِّ وَمَطْعَمُهُ حَرَامٌ ، وَمَشْرَبُهُ حَرَامٌ ، وَمَلْبَسُهُ حَرَামٌ، وَغُذَّيَ بِالْحَرَامِ، فَأَنَّى يُسْتَجَابُ لِذَلِكَ؟».&lt;/ar&gt;
+&lt;p&gt;আবু হুরায়রা (রাঃ) বলেন, রাসূল (ﷺ) বলেছেন, 'নিশ্চয়ই আল্লাহ পবিত্র, তিনি পবিত্র ছাড়া গ্রহণ করেন না। (এবং সর্বক্ষেত্রে পাক-পবিত্রতার আদেশই তিনি করেছেন। সেই সম্পর্কে) আল্লাহ রাসূলগণকে যে আদেশ করেছেন, মুমিনগণকেও সেই আদেশই করেছেন। অতঃপর রাসূল (ﷺ) উল্লেখ করলেন, এক ব্যক্তি দূর-দূরান্তের সফর করছে। তার মাথার চুল এলোমেলো, শরীরে ধূলা-বালি। এমতাবস্থায় ঐ ব্যক্তি উভয় হস্ত আসমানের দিকে উঠিয়ে কাতর&lt;/p&gt;
+&lt;p&gt;স্বরে হে প্রভু! হে প্রভু! বলে ডাকছে। কিন্তু তার খাদ্য হারাম, তার পানীয় হারাম, তার পোশাক হারাম, তার জীবিকা নির্বাহ হারাম, কীভাবে তার দু'আ কবুল হবে' (ছহীহ মুসলিম, হা/১০১৫; তিরমিযী, হা/২৯৮৯; মিশকাত হা/২৭৬০)।&lt;/p&gt;
+&lt;ar&gt;عَنْ أَبِي هُرَيْرَةَ الله قَالَ: قَالَ رَسُولُ اللهِ ﷺ : يَأْتِي عَلَى الْمَرْءِ زَمَانٌ لَا يُبَالِي الْمَرْءُ مَا أَخَذَ مِنْهُ، أَمِنَ الْحَلَالِ أَمْ مِنَ الْحَرَامِ».&lt;/ar&gt;
+&lt;p&gt;আবু হুরায়রা (রাঃ) বলেন, রাসূল (ﷺ) বলেছেন, 'মানুষের সম্মুখে এমন এক যুগ আসবে যে, কেউ পরওয়া করবে না কী উপায়ে মাল অর্জন করল; হারাম না হালাল উপায়ে' (ছহীহ বুখারী, হা/২০৫৯; মিশকাত, হা/২৭৬১)।&lt;/p&gt;
+&lt;ar&gt;وَعَنِ النُّعْمَانِ بْنِ بَشِيرٍ قَالَ: قَالَ رَسُولُ اللهِ ﷺ : الْحَلَالُ بَيِّنُ وَالْحَرَامُ بَيِّنٌ، وَبَيْنَهُمَا مُشْتَبِهَاتٌ لَا يَعْلَمُهُنَّ كَثِيرٌ مِنَ النَّاسِ، فَمَنِ اتَّقَى الشُّبَهَاتِ اسْتَبْرَأَ لِدِينِهِ وَعِرْضِهِ، وَمَنْ وَقَعَ فِي الْحَرَامِ كَالرَّاعِي يَرْعَى حَوْلَ الْحِمَى يُوشِكُ أَنْ يَرْتَعَ فِيهِ، أَلَا وَإِنَّ لِكُلِّ مَلِكٍ حِمّى أَلَا وَإِنَّ حِمَى اللَّهِ مَحَارِمُهُ، أَلَا وَإِنَّ فِي الْجَسَدِ مُضْغَةً إِذَا صَلُحَتْ صَلَحَ الْجُسَدُ كُلُّهُ، وَإِذَا فَسَدَتْ فَسَدَ الْجَسَدُ كُلُّهُ، أَلَا وَهِيَ الْقَلْبُ».&lt;/ar&gt;
+&lt;p&gt;নু'মান ইবনু বাশীর (রাঃ) হতে বর্ণিত, তিনি বলেন, রাসূলুল্লাহ (ﷺ) বলেছেন, 'হালাল এবং হারাম সুস্পষ্ট, আর উভয়ের মধ্যে অনেক সন্দেহজনক বিষয় বা বস্তু আছে। যেগুলো (হালালের অন্তর্ভুক্ত না হারামের অন্তর্ভুক্ত,) সে সম্পর্কে অনেকেই সিদ্ধান্ত নিতে পারে না। এরূপ ক্ষেত্রে যেই ব্যক্তি সন্দেহের বস্তুকে পরিহার করে চলবে, তার দ্বীন এবং আবরু-ইজ্জত, মান-সম্মান পাক-পবিত্র থাকবে। পক্ষান্তরে, যেই ব্যক্তি সন্দেহের কাজে লিপ্ত হবে, সে অচিরেই হারামেও লিপ্ত হয়ে পড়বে। (ফলে তার দ্বীন এবং মান-সম্মান কলুষিত হবে।) যেমন যেই রাখাল তার পশুপালকে নিষিদ্ধ এলাকার সীমার ধারে চরাবে, খুব সম্ভব তার পশু নিষিদ্ধ এলাকার ভিতরেও মুখ ঢুকিয়ে দিবে। তোমরা স্মরণ রেখো প্রত্যেক বাদশাহরই নিজ পশুপালের চারণভূমি (নিষিদ্ধ এলাকা) বানিয়ে রাখেন। তদ্রুপ (সকল বাদশাহর বাদশাহ) আল্লাহ তাআলার চারণভূমি তাঁর হারাম বস্তুসমূহকে নির্ধারিত করে রেখেছেন। মনে রেখো মানুষের দেহের ভিতরে একটি গোশতের টুকরা রয়েছে, যা সঠিক থাকলে সমস্ত দেহই সঠিক থাকে। আর সেই অংশের বিকৃতি ঘটলে সম্পূর্ণ দেহেরই বিকৃতি ঘটে। সেই গোশতের টুকরাটি হলো অন্তর' (ছহীহ বুখারী, হা/৫২; ছহীহ মুসলিম, হা/১৫৯৯; মিশকাত, হা/২৭৬২)।&lt;/p&gt;
+&lt;ar&gt;عَنْ رَافِعِ بْنِ خَدِيجٍ قَالَ : قَالَ رَسُولُ اللهِ : ثَمَنُ الْكَلْبِ خَبِيثُ، وَمَهْرُ الْبَغِيِّ خَبِيتٌ، وَكَسْبُ الْحَجَّامِ خَبِيتٌ .&lt;/ar&gt;
+&lt;p&gt;রাফে' ইবনু খাদীজ (রাঃ) বলেন, রাসূল (ﷺ) বলেছেন, 'কুকুর বিক্রয়ের মূল্য ঘৃণিত বস্তু, ব্যভিচারের বিনিময়ও অতি জঘন্য, সিঙ্গা লাগানোর মূল্যও ঘৃণিত' (ছহীহ মুসলিম, হা/১৫৬৮; মিশকাত, হা/২৭৬৩)।&lt;/p&gt;
+&lt;ar&gt;عَنْ أَبِي مَسْعُودٍ الْأَنْصَارِيِّ : «أَنَّ رَسُولَ اللهِ ﷺ نَهَى عَنْ ثَمَنِ الْكَلْبِ، وَمَهْرِ الْبَغِيِّ وَحُلْوَانِ الْكَاهِنِ» .&lt;/ar&gt;
+&lt;p&gt;আবু মাসউদ আনছারী (রাঃ) বলেন, রাসূল (ﷺ) 'কুকুরের মূল্য, যিনাকারিনীর উপার্জন ও গণকের উপার্জন খেতে নিষেধ করেছেন' (ছহীহ বুখারী, হা/৫৭৬১; ছহীহ মুসলিম, হা/১৫৬৭; মিশকাত, হা/২৭৬৪)।&lt;/p&gt;
+&lt;ar&gt;عَنْ أَبِي جُحَيْفَةَ أَنَّ النَّبِيَّ نَهَى عَنْ ثَمَنِ الدَّمِ، وَثَمَنِ الْكَلْبِ، وَكَسْبِ الْبَغِيِّ، وَلَعَنَ آكِلَ الرِّبَا وَمُوكِلَهُ، وَالْوَاشِمَةَ وَالْمُسْتَوْشِمَةَ، وَالْمُصَوِّرَ .&lt;/ar&gt;
+&lt;p&gt;আবূ জুহায়ফা (রাঃ) হতে বর্ণিত, রাসূল (ﷺ) নিষেধ করেছেন, রক্ত বিক্রয় মূল্য হতে, কুকুর বিক্রয়ের মূল্য হতে, ব্যভিচার বা যেনার বিনিময় হতে এবং তিনি লানত করেছেন সূদ গ্রহীতার প্রতি ও সুদদাতার প্রতি। তিনি আরও লা'নত করেছেন ঐ ব্যক্তির প্রতি যে দেহের কোন অংশ (নাম বা চিত্র ইত্যাদি) উলকী করে এবং যে উলকী করায়। এতদ্ভিন্ন ছবি অংকনকারীর প্রতিও লা'নত করেছেন (ছহীহ বুখারী, হা/৫৯৪৫; মুসনাদে আহমাদ, হা/১৮৭৭৮; মিশকাত, হা/২৭৬৫)।&lt;/p&gt;
+&lt;ar&gt;عَنْ جَابِرٍ قَالَ: قَالَ رَسُولُ اللهِ ﷺ : «لَا يَدْخُلُ الْجَنَّةَ لَحْمُ نَبَتَ مِنْ سُحْتٍ، وَكُلُّ لَحْمٍ نَبَتَ مِنْ سُحْتٍ كَانَتِ النَّارُ أَوْلَى بِهِ» .&lt;/ar&gt;
+&lt;p&gt;জাবের (রাঃ) বলেন, রাসূল (ﷺ) বলেছেন, 'যে দেহের গোশত হারাম মালে গঠিত, তা জান্নাতে প্রবেশ করতে পারবে না। হারাম মালে গঠিত দেহের জন্য জাহান্নামই সমীচীন' (মুসনাদে আহমাদ, হা/১৪৪৮১; বায়হাক্বী, শু'আবুল ঈমান, হা/৯৩৯৯; মিশকাত, হা/২৭৭২)।&lt;/p&gt;
+&lt;ar&gt;عَنِ الْحَسَنِ بْنِ عَلِيَّ قَالَ: حَفِظْتُ مِنْ رَسُولِ اللهِ ﷺ : «دَعْ مَا يَرِيبُكَ إِلَى مَا لَا يُرِيبُكَ، فَإِنَّ الصِّدْقَ طُمَأْنِينَةٌ، وَإِنَّ الْكَذِبَ رِيبَةً .&lt;/ar&gt;
+&lt;p&gt;হাসান ইবনু আলী (রাঃ) বলেন, রাসূল (ﷺ)-এর এই বাণীটি আমি ভালোভাবে স্মরণ রেখেছি যে, যে কাজে মনে খটকা লাগে, সে কাজ পরিহার করে খটকাহীন কাজ অবলম্বন করো। সত্য ও শুদ্ধের ক্ষেত্রে দ্বিধার সৃষ্টি হয় না, মিথ্যা ও অশুদ্ধের ক্ষেত্রেই দ্বিধার সৃষ্টি হয়' (মুসনাদে আহমাদ, হা/১৭২৩; তিরমিযী, হা/২৫১৮; নাসাঈ, হা/৫৭১১; মিশকাত, হা/২৭৭৩)।&lt;/p&gt;
+&lt;ar&gt;عَنْ أَبِي أُمَامة قَالَ: قَالَ رَسُولُ اللهِ ﷺ : «لَا تَبِيعُوا الْقَيْنَاتِ، وَلَا تَشْتَرُوهُنَّ، وَلَا تُعَلِّمُوهُنَّ، وَثَمَنُهُنَّ حَرَامٌ، وَفِي مِثْلِ هَذَا نَزَلَتْ وَمِنَ النَّاسِ مَنْ يَشْتَرِي لَهْوَ الْحَدِيثِ .&lt;/ar&gt;
+&lt;p&gt;আবু উমামা (রাঃ) হতে বর্ণিত, তিনি বলেন, রাসূল (ﷺ) বলেছেন, 'তোমরা গায়িকা ক্রয়-বিক্রয় করো না, তার মূল্য হারাম। তাদের গান শিক্ষা দিও না। এই শ্রেণির কার্য যারা করে তাদের সম্পর্কেই পবিত্র কুরআনের এ আয়াত অবতীর্ণ হয়েছে, 'এক শ্রেণির লোক আছে যারা রং-তামাশার গাথা (তথা গান) ক্রয় করে (তাদের জন্য লাঞ্ছনাময় শাস্তি রয়েছে)' (মুসনাদে আহমাদ, হা/২২৩৩৪; তিরমিযী, হা/১২৮২; মিশকাত, হা/২৭৮০)।&lt;/p&gt;
+&lt;ar&gt;عَنْ عَائِشَةَ قَالَتْ: كَانَ لِأَبِي بَكْرٍ الله غُلَامٌ يُخْرِّجُ لَهُ الْخَرَاجَ، فَكَانَ أَبُو بَكْرٍ يَأْكُلُ مِنْ خَرَاجِهِ، فَجَاءَ يَوْمًا بِشَيْءٍ، يَأْكُلُ مِنْهُ أَبُو بَكْرٍ، فَقَالَ لَهُ الْغُلَامُ: تَدْرِي مَا هَذَا؟ فَقَالَ أَبُو بَكْرٍ: وَمَا هُوَ؟ قَالَ: كُنْتُ تَكَهَّنْتُ لِإِنْسَانٍ فِي الْجَاهِلِيَّةِ، وَمَا أُحْسِنُ الْكَهَانَةَ، إِلَّا أَنِّي خَدَعْتُهُ فَأَدْخَلَ أَبُو بَكْرٍ يَدَهُ، فَقَاءَ كُلَّ شَيْءٍ فِي بَطْنِهِ.&lt;/ar&gt;
+&lt;p&gt;আয়েশা (রাঃ) হতে বর্ণিত, তিনি বলেন, আবু বকর ছিদ্দীক্ব (রাঃ)-এর একজন গোলাম ছিল। তিনি তার জন্য রাজস্ব নির্ধারণ করেছিলেন। তিনি তার রাজস্ব হতে খেতেন। একদিন সে কিছু সম্পদ নিয়ে আসে এবং তিনি সেখান হতে কিছু খান। তখন গোলাম তাঁকে বলল, আপনি এ খাদ্য সম্পর্কে কি জানেন? তিনি বললেন এ কেমন খাদ্য? গোলাম বলল, আমি জাহেলী যুগে গণকী করতাম। আমি মানুষকে ধোঁকা দিতাম। ঐ সময়ের এক লোকের সাথে দেখা হলে সে আমাকে এ খাদ্য প্রদান করে। আয়েশা (রাঃ) বলেন, তখন আবু বকর ছিদ্দীক্ব (রাঃ) মুখের ভিতর হাত ঢুকিয়ে সব বমন করে দিলেন' (ছহীহ বুখারী, হা/৩৮৪২; মিশকাত, হা/২৭৮৬)।&lt;/p&gt;
+&lt;ar&gt;عَنْ أَبِي بَكْرٍ أَنَّ رَسُولَ اللهِ ﷺ قَالَ: «لَا يَدْخُلُ الْجَنَّةَ جَسَدُ غُذِّيَ بِحَرَامٍ».&lt;/ar&gt;
+&lt;p&gt;আবু বকর (রাঃ) হতে বর্ণিত আছে, রাসূল (ﷺ) বলেছেন, 'যে দেহ হারাম দ্বারা প্রতিপালিত, তা জান্নাতে প্রবেশ করবে না' (সিলসিলা ছহীহা, হা/২৬০৯; মিশকাত, হা/২৭৮৭)।&lt;/p&gt;
+&lt;ar&gt;عَنْ أَنَسٍ الله قَالَ مَرَّ النَّبِيُّ اللهِ بِتَمْرَةٍ فِي الطَّرِيقِ فَقَالَ: «لَوْلَا أَنِّي أَخَافُ أَنْ تَكُوْنَ مِنَ الصَّدَقَةِ لَأَكَلْتُهَا».&lt;/ar&gt;
+&lt;p&gt;আনাস (রাঃ) বলেন, রাসূল (ﷺ) রাস্তায় পড়া একটি খেজুরের নিকট দিয়ে যাওয়ার সময় বললেন, 'ছাদাকার খেজুর বলে যদি আমার সন্দেহ না হত, নিশ্চয়ই আমি তা খেতাম' (ছহীহ বুখারী, হা/২৪৩১; ছহীহ মুসলিম, হা/১০৭১; মিশকাত, হা/১৮২১)।&lt;/p&gt;
+&lt;ar&gt;عَنْ أَبِي هُرَيْرَةَ هُ قَالَ: «أَخَذَ الْحَسَنُ بْنُ عَلِيَّ تَمْرَةً مِنْ تَمْرِ الصَّدَقَةِ فَجَعَلَهَا فِي فِيهِ، فَقَالَ النَّبِيُّ : كِنْ كِنْ لِيَطْرَحَهَا ، ثُمَّ قَالَ: أَمَا شَعَرْتَ أَنَّا لَا تَأْكُلُ الصَّدَقَةَ .&lt;/ar&gt;
+&lt;p&gt;আবু হুরায়রা (রাঃ) বলেন, একদা (রাসূলের দৌহিত্র) হাসান ইবনু আলী (রাঃ) যাকাতের একটি খেজুর নিয়ে মুখে দিলেন (এটা দেখে) নবী করীম (ﷺ) বললেন, ক্ষ, ক্ষ, যাতে তা সে ফেলে দেয়। অতঃপর বললেন, নানু তুমি জান না! আমরা যে যাকাত খাই না' (ছহীহ বুখারী, হা/৩০৭২; ছহীহ মুসলিম, হা/১০৬৯; মিশকাত, হা/১৮২২)।&lt;/p&gt;
+&lt;ar&gt;عَنْ عَبْدِ الْمُطَّلِبِ بْنِ رَبِيعَةَ قَالَ: قَالَ رَسُولُ اللهِ ﷺ : " إِنَّ هَذِهِ الصَّدَقَاتِ إِنَّمَا هِيَ أَوْسَاخُ النَّاسِ، وَإِنَّهَا لَا تَحِلُّ لِمُحَمَّدٍ، وَلَا لِآلِ مُحَمَّدٍ».&lt;/ar&gt;
+&lt;p&gt;আব্দুল মুত্ত্বালিব ইবনু রবী'আ (রাঃ) হতে বর্ণিত, তিনি বলেন, রাসূলুল্লাহ (ﷺ) বলেছেন, 'এ ছাদাকা অর্থাৎ যাকাত মানুষের সম্পদের ময়লা ব্যতীত কিছু নয়। তাই এটা মুহাম্মাদ (ﷺ)-এর জন্য এবং তাঁর বংশধরদের জন্যও হালাল নয়' (ছহীহ মুসলিম, হা/১০৭২; মিশকাত, হা/১৮২৩)।&lt;/p&gt;
+&lt;ar&gt;عَنْ أَبِي هُرَيْرَةَ قَالَ: كَانَ رَسُولُ اللهِ اللهِ إِذَا أُتِيَ بِطَعَامٍ سَأَلَ عَنْهُ أَهَدْيَةٌ أَمْ صَدَقَةٌ؟ فَإِنْ قِيلَ: صَدَقَةٌ قَالَ لِأَصْحَابِهِ كُلُوا، وَلَمْ يَأْكُلْ، وَإِنْ قِيلَ: هَدِيَّةٌ ضَرَبَ بِيَدِهِ فَأَكَلَ مَعَهُمْ.&lt;/ar&gt;
+&lt;p&gt;আবু হুরায়রা (রাঃ) হতে বর্ণিত। তিনি বলেন, রাসূলুল্লাহ (ﷺ)-এর নিকট কোনো খাবার এলে তিনি জিজ্ঞাসা করতেন, এটা হাদিয়্যা না ছাদাকা? 'ছাদাকা' বলা হলে তিনি তাঁর সাথীদেরকে বলতেন, তোমরা খাও। তিনি নিজে খেতেন না। আর 'হাদিয়্যা' বলা হলে তিনি তাঁর হাত বাড়াতেন ও ছাহাবীদের সাথে নিয়ে খেতেন (ছহীহ বুখারী, হা/২৫৭৬; মিশকাত, হা/১৮২৩)।&lt;/p&gt;
+&lt;ar&gt;عَنْ أَبِي رَافِع الله أَنَّ رَسُولَ اللهِ ﷺ بَعَثَ رَجُلًا مِنْ بَنِي مَخْزُومٍ عَلَى الصَّدَقَةِ فَقَالَ لِأَبِي رَافِعِ اصْحَبْنِي فِيمَا تُصِيبُ مِنْهَا، فَقَالَ: لَا حَتَّى آتِيَ رَسُولَ اللَّهِ ﷺ فَأَسْأَلَهُ، فَانْطَلَقَ إِلَى النَّبِيِّ ﷺ فَسَأَلَهُ، فَقَالَ: " إِنَّ الصَّدَقَةَ لَا تَحِلُّ لَنَا وَإِنَّ مَوَالِيَ الْقَوْمِ مِنْ أَنْفُسِهِمْ».&lt;/ar&gt;
+&lt;p&gt;আবু রাফে' (রাঃ) হতে বর্ণিত, রাসূলুল্লাহ (ﷺ) বানী মাখযূম-এর এক ব্যক্তিকে যাকাত আদায়কারী করে পাঠালেন। যাবার সময় সে ব্যক্তি আবু রাফে' (রাঃ)-কে বলল, আপনিও আমার সাথে চলুন। এতে কিছু অংশ আপনিও পেয়ে যাবেন।&lt;/p&gt;
+&lt;p&gt;আবু রাফে' (রাঃ) বললেন, না, রাসূলুল্লাহ (ﷺ)-কে জিজ্ঞাসা না করে আমি যেতে পারি না। তাই তিনি তাঁর কাছে গেলেন। তাঁকে তার সাথে যাবার অনুমতি চাইলে রাসূলুল্লাহ (ﷺ) বললেন, 'ছাদাকা আমাদের (বানী হাশেমের) জন্য হালাল নয়। আর কোনো গোত্রের দাস তাদের মধ্যেই গণ্য (তুমি তো আমাদেরই দাস)' (তিরমিযী, হা/৬৫৭; মিশকাত, হা/১৮২৯)।&lt;/p&gt;
+&lt;ar&gt;عَنْ عَبْدِ اللَّهِ بْنِ عَمْرٍو قَالَ: قَالَ رَسُولُ اللهِ ﷺ : " لَا تَحِلُّ الصَّدَقَةُ لِغَنِيٌّ، وَلَا لِذِي مِرَّةٍ سَوِيٌّ».&lt;/ar&gt;
+&lt;p&gt;আব্দুল্লাহ ইবনু আমর (রাঃ) হতে বর্ণিত, তিনি বলেন, রাসূলুল্লাহ (ﷺ) বলেছেন, 'যাকাতের মাল ধনীদের জন্য হালাল নয়, সুস্থ সবলদের (খেটে খেতে সক্ষম) জন্যও নয়' (আবূ দাউদ, হা/১৬৩৪; তিরমিযী, হা/৬৫২; মিশকাত, হা/১৮৩০)।&lt;br&gt;&lt;br&gt;এই হাদীছ প্রমাণ করে, যাদের কাজ করে খাওয়ার সামর্থ্য আছে তাদের জন্য ছাদাকা খাওয়া জায়েয নয়।&lt;/p&gt;
+&lt;ar&gt;عَنْ عُبَيْدِ اللَّهِ بْنِ عَدِيِّ بْنِ الْخِيَارِ قَالَ: «أَخْبَرَنِي رَجُلَانِ أَنَّهُمَا أَتَيَا النَّبِيَّ ﷺ وَهُوَ فِي حَجَّةِ الْوَدَاعِ، وَهُوَ يُقَسِّمُ الصَّدَقَةَ فَسَأَلَاهُ مِنْهَا، فَرَفَعَ فِينَا النَّظَرَ، وَخَفَضَهُ فَرَآنَا جَلْدَيْنِ، فَقَالَ: " إِنْ شِئْتُمَا أَعْطَيْتُكুমَا وَلَا حَظٍّ فِيهَا لِغَنِيٌّ وَلَا لِقَوِيٌّ مُكْتَسِبٍ» ".&lt;/ar&gt;
+&lt;p&gt;উবায়দুল্লাহ ইবনু আদী ইবনু খিয়ার (রাঃ) হতে বর্ণিত, তিনি বলেন, আমাকে দু'ব্যক্তি জানিয়েছেন যে, বিদায় হজ্জে মানুষের মধ্যে যাকাতের মাল বণ্টন করার সময় তারা উভয়ে নবী (ﷺ)-এর কাছে উপস্থিত ছিলেন। তারা এ মালের কিছু অংশ নেবার জন্য আগ্রহ দেখান। দুজন বলেন, রাসূলুল্লাহ (ﷺ) (যাকাত নেবার আগ্রহ দেখে) আমাদের মাথা থেকে পা পর্যন্ত চোখ বুলালেন। আমাদের সুস্থ সবল দেখে বললেন, তোমরা যাকাত নিতে চাইলে আমি দিতে পারি। (কিন্তু মনে রাখবে,) ছাদাকা ও যাকাতের সম্পদে ধনীদের কোনো অংশ নেই। আর সুস্থ সবল এবং পরিশ্রম করতে সক্ষম লোকদের জন্য ছাদাকা ও যাকাত নয়' (আবু দাউদ, হা/১৬৩৩; নাসাঈ, হা/২৫৯৮; মিশকাত, হা/১৮৩২)।&lt;/p&gt;
+&lt;ar&gt;عَنْ قَبِيصَةَ بْنِ مُخَارِقٍ قَالَ: تَحَمَّلْتُ حَمَالَةً، فَأَتَيْتُ رَسُولَ اللَّهِ ﷺ أَسْأَلُهُ فِيهَا، فَقَالَ: " أَقِمْ حَتَّى تَأْتِيَنَا الصَّدَقَةُ، فَنَأْمُرَ لَكَ بِهَا " ، ثُمَّ قَالَ: " يَا قَبِيصَةُ إِنَّ الْمَسْأَلَةَ لَا تَحِلُّ إِلَّا لِأَحَدِ ثَلَاثَةٍ : رَجُلٍ تَحَمَّلَ حَمَالَةٌ فَحَلَّتْ لَهُ الْمَسْأَلَةُ حَتَّى يُصِيبَهَا ثُمَّ يُمْسِكُ، وَرَجُلٍ أَصَابَتْهُ جَائِحَةُ اجْتَاحَتْ مَالَهُ، فَحَلَّتْ لَهُ الْمَسْأَلَةُ حَتَّى يُصِيبَ قِوَامًا مِنْ عَيْشٍ، أَوْ قَالَ سِدَادًا مِنْ عَيْشٍ، وَرَجُلٍ أَصَابَتْهُ فَاقَةٌ حَتَّى يَقُولَ ثَلَاثَةٌ مِنْ ذَوِي الْخِجَا مِنْ قَوْمِهِ: لَقَدْ أَصَابَتْ فُلَانًا فَاقَةٌ&lt;/ar&gt;
+&lt;ar&gt;فَحَلَّتْ لَهُ الْمَسْأَلَةُ حَتَّى يُصِيبَ قِوَامًا مِنْ عَيْشٍ ، أَوْ قَالَ سِدَادًا مِنْ عَيْشٍ، فَمَا سِوَاهُنَّ مِنَ الْمَسْأَلَةِ يَا قَبِيصَةُ سُحْتُ، يَأْكُلُهَا صَاحِبُهَا سُحْتًا».&lt;/ar&gt;
+&lt;p&gt;কবীসা ইবনু মুখারিক্ক (রাঃ) হতে বর্ণিত, তিনি বলেন, আমি ঋণগ্রস্ত হয়ে রাসূলুল্লাহ (ﷺ)-এর কাছে এলাম। তার কাছে ঋণ আদায়ের জন্য কিছু চাইলাম। তিনি বললেন, অপেক্ষা করো। আমার কাছে যাকাতের মাল আসা পর্যন্ত আসলে তোমাকে কিছু দেবার জন্য বলে দেব। তারপর তিনি বললেন, কবীসা! শুধু তিন ধরনের ব্যক্তির জন্য কিছু চাওয়া জায়েয। প্রথমত, যে ব্যক্তি অপরের ঋণের জামিনদার। তবে বেশি চাইতে পারবে না। বরং যতটুকু ঋণ শোধের জন্য প্রয়োজন শুধু ততটুকু চাইবে। এরপর আর চাইবে না। দ্বিতীয়ত, ওই ব্যক্তি যে বিপদগ্রস্ত হয়ে পড়েছে (দুর্ভিক্ষ, প্লাবন ইত্যাদিতে)। তার সব ধন-সম্পদ ধ্বংস হয়েছে। তারও (শুধু খাবার ও পোশাকের জন্য) ততটুকু যাতে প্রয়োজন মিটে যায়। তার জীবনের জন্য অবলম্বন হয়ে যায়। তৃতীয়ত, ওই ব্যক্তি (যে ধনী, কিন্তু তার এমন কোনো কঠিন প্রয়োজন হয়ে পড়েছে যা মহল্লাবাসী জানে। যেমন ঘরের সব মালপত্র চুরি হয়ে গেছে অথবা অন্য কোনো দুর্ঘটনার কারণে মুখাপেক্ষী হয়ে পড়েছে)। (মহল্লার) তিনজন বুদ্ধিমান সচেতন লোক এ ব্যাপারে সাক্ষ্য দিবে যে, সত্যিই এ ব্যক্তি মুখাপেক্ষী। তার জন্যও সেই পরিমাণ (সাহায্য) চাওয়া জায়েয, যাতে তার প্রয়োজন মিটে। অথবা তিনি বলেছেন এর দ্বারা তার মুখাপেক্ষিতা ও অভাব দূর হয়, তার জীবনে একটি অবলম্বন আসে। হে ক্ববীসা! এ তিন প্রকারের 'চাওয়া' ছাড়া হালাল নয়। আর হারাম পন্থায় প্রাপ্ত মাল খাওয়া তার জন্য হারাম (ছহীহ মুসলিম, হা/১০৪৪; মিশকাত, হা/১৮৩৭)।&lt;/p&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr"/>

--- a/output/opodesh-test/book-output.xlsx
+++ b/output/opodesh-test/book-output.xlsx
@@ -507,8 +507,7 @@
 &lt;ar&gt;يَوْمَ تَشْهَدُ عَلَيْهِمْ أَلْسِنَتُهُمْ وَأَيْدِيهِمْ وَأَرْجُلُهُمْ بِمَا كَانُوا يَعْمَلُوْনَ&lt;/ar&gt;
 &lt;p&gt;'যেদিন তাদের বিরুদ্ধে সাক্ষ্য দিবে তাদের যবান, তাদের হাত ও তাদের পা তাদের কৃতকর্ম সম্বন্ধে' (আন-নূর, ২৪/২৪)।&lt;/p&gt;
 &lt;ar&gt;وَيَوْمَ يُحْশَرُ أَعْدَاءُ اللهِ إِلَى النَّارِ فَهُمْ يُوزَعُوْنَ إِذَا مَا جَاءُوهَا شَهِدَ عَلَيْهِمْ سَمْعُكُمْ وَأَبْصَارُكُمْ وَجُلُودُكُمْ بِمَا كَانُوا يَعْمَلُوْনَ وَقَالُوا لِجُلُوْدِهِمْ لِمَ شَهِدْتُمْ عَلَيْنَا قَالُوْا أَنْطَقَنَا اللَّهُ الَّذِي أَنْطَقَ كُلَّ شَيْءٍ وَهُوَ خَلَقَكُمْ أَوَّلَ مَرَّةٍ وَإِلَيْهِ تُرْجَعُوْنَ وَمَا كُنْتُمْ تَسْتَتِرُوْنَ أَنْ يَشْهَدَ عَلَيْكُمْ سَمْعُكُمْ وَلَا أَبْصَارُكُمْ وَلَا جُلُودُكُمْ وَلَكِنْ ظَنَنْتُمْ أَنَّ اللَّهَ لَا يَعْلَمُ كَثِيرًا مِمَّا تَعْمَلُوْনَ&lt;/ar&gt;
-&lt;p&gt;'যেদিন আল্লাহর শত্রুদের জাহান্নাম অভিমুখে সমবেত করা হবে, সেদিন তাদের তাড়িয়ে নিয়ে যাওয়া হবে বিভিন্ন দলে। পরিশেষে যখন তারা জাহান্নামের সন্নিকটে পৌঁছবে তখন তাদের কর্ণ, চক্ষু ও ত্বক (চামড়া) তাদের কৃতকর্ম সম্বন্ধে সাক্ষ্য দিবে। জাহান্নামীরা তাদের ত্বককে জিজ্ঞাসা করবে, তোমরা আমাদের বিরুদ্ধে সাক্ষ্য দিচ্ছ কেন? উত্তরে তারা বলবে, আল্লাহ যিনি সবকিছুকে বাকশক্তি&lt;/p&gt;
-&lt;p&gt;দিয়েছেন তিনি আমাদেরও বাকশক্তি দিয়েছেন। তিনি তোমাদের সৃষ্টি করেছেন প্রথম বার এবং তাঁরই নিকট তোমরা প্রত্যাবর্তিত হবে। তোমরা কিছু গোপন করতে না এই বিশ্বাসে যে, তোমাদের কর্ণ, চক্ষু এবং ত্বক তোমাদের বিরুদ্ধে সাক্ষ্য দিবে না। উপরন্তু তোমরা মনে করতে যে, তোমরা যা করতে তার অনেক কিছুই আল্লাহ জানেন না' (ফুছছিলাত, ৪১/১৯-২২)।&lt;/p&gt;
+&lt;p&gt;'যেদিন আল্লাহর শত্রুদের জাহান্নাম অভিমুখে সমবেত করা হবে, সেদিন তাদের তাড়িয়ে নিয়ে যাওয়া হবে বিভিন্ন দলে। পরিশেষে যখন তারা জাহান্নামের সন্নিকটে পৌঁছবে তখন তাদের কর্ণ, চক্ষু ও ত্বক (চামড়া) তাদের কৃতকর্ম সম্বন্ধে সাক্ষ্য দিবে। জাহান্নামীরা তাদের ত্বককে জিজ্ঞাসা করবে, তোমরা আমাদের বিরুদ্ধে সাক্ষ্য দিচ্ছ কেন? উত্তরে তারা বলবে, আল্লাহ যিনি সবকিছুকে বাকশক্তি দিয়েছেন তিনি আমাদেরও বাকশক্তি দিয়েছেন। তিনি তোমাদের সৃষ্টি করেছেন প্রথম বার এবং তাঁরই নিকট তোমরা প্রত্যাবর্তিত হবে। তোমরা কিছু গোপন করতে না এই বিশ্বাসে যে, তোমাদের কর্ণ, চক্ষু এবং ত্বক তোমাদের বিরুদ্ধে সাক্ষ্য দিবে না। উপরন্তু তোমরা মনে করতে যে, তোমরা যা করতে তার অনেক কিছুই আল্লাহ জানেন না' (ফুছছিলাত, ৪১/১৯-২২)।&lt;/p&gt;
 &lt;p&gt;হাদীছে এসেছে,&lt;/p&gt;
 &lt;ar&gt;عَنِ ابْنِ عُمَرَ قَالَ قَالَ رَسُولُ اللهِ ﷺ إِنَّ اللهَ يُدْنِي الْمُؤْمِنَ فَيَضَعُ عَلَيْهِ كَنَفَهُ، وَيَسْتُرُهُ فَيَقُولُ أَتَعْرِفُ ذَنْبَ كَذَا أَتَعْرِفُ ذَنْبَ كَذَا فَيَقُولُ نَعَمْ أَيْ رَبِّ . حَتَّى إِذَا قَرَّرَهُ بِذُنُوبِهِ وَرَأَى فِي نَفْسِهِ أَنَّهُ هَلَكَ قَالَ سَتَرْتُهَا عَلَيْكَ فِي الدُّنْيَا، وَأَنَا أَغْفِرُهَا لَكَ الْيَوْمَ ، فَيُعْطَى كِتَابَ حَسَنَاتِهِ، وَأَمَّا الْكَافِرُ وَالْمُنَافিقُونَ فَيَقُولُ الْأَشْهَادُ هَؤُلَاءِ الَّذِينَ كَذَبُوا عَلَى رَبِّهِمْ، أَلَا لَعْنَةُ اللَّهِ عَلَى الظَّالِمِينَ » .&lt;/ar&gt;
 &lt;p&gt;ইবনু উমার (রাঃ) বলেন, রাসূলুল্লাহ (ﷺ) বলেছেন, '(কিয়ামতের দিন) আল্লাহ তাআলা মুমিনদের নিজের নিকটবর্তী করবেন এবং আল্লাহ তাআলা নিজ বাজু তার উপরে রেখে তাকে ঢেকে নিবেন। অতঃপর আল্লাহ সেই বান্দাকে বলবেন, আচ্ছা! বলো দেখি, এই গুনাহটি তুমি করেছ কি? এই গুনাহটি সম্পর্কে তুমি অবগত আছ কি? সে বলবে হ্যাঁ, হে আমার রব! আমি অবগত আছি। শেষ পর্যন্ত এক একটি করে তার কৃত সমস্ত গুনাহের স্বীকৃতি আদায় করবেন। এদিকে সে বান্দা মনে মনে এই ধারণা করবে যে, সে এই সমস্ত অপরাধের কারণে নিশ্চিত ধ্বংস হবে। তখন আল্লাহ তাআলা বলবেন, দুনিয়াতে আমি তোমার এই সমস্ত অপরাধ ঢেকে রেখেছিলাম। আর আজ আমি তা মাফ করে দিব। অতঃপর তাকে নেকীর আমলনামা দেওয়া হবে। আর কাফের ও মুনাফেকদের সমস্ত সৃষ্টির সম্মুখে আনয়ন করা হবে এবং উচ্চৈস্বরে এই ঘোষণা দেওয়া হবে- এরা তারা, যারা স্বীয় পরওয়ারদিগারের বিরুদ্ধে মিথ্যারোপ করত। জেনে রাখ, এই সমস্ত জালেমদের উপর আজ আল্লাহর লানত' (ছহীহ বুখারী, হা/২৪৪১; ছহীহ মুসলিম, হা/২৭৬৮; মিশকাত, হা/৫৫৫১)।&lt;/p&gt;
@@ -516,12 +515,10 @@
 &lt;p&gt;আনাস (রাঃ) হতে বর্ণিত, তিনি বলেন, আমরা রাসূলুল্লাহ (ﷺ)-এর কাছে ছিলাম, হঠাৎ তিনি হাসলেন। অতঃপর জিজ্ঞাসা করলেন, তোমরা কি জান আমি কেন হাসছি? আমরা বললাম, আল্লাহ এবং তাঁর রাসূলই ভালো জানেন। তিনি বললেন, কিয়ামতের দিন বান্দা যে তার রবের সাথে সরাসরি কথা বলবে, সেই কথাটি স্মরণ করে হাসছি। বান্দা বলবে, হে রব! তুমি কি আমাকে জুলুম হতে নিরাপত্তা দান করনি? আল্লাহ বলবেন, হ্যাঁ, তখন বান্দা বলবে, আজ আমি আমার সম্পর্কে আপনজন ব্যতীত আমার বিরুদ্ধে অন্য কারো সাক্ষ্য গ্রহণ করব না। তখন আল্লাহ বলবেন, আজ তুমি নিজেই তোমার সাক্ষী হিসাবে এবং কিরামান-কাতেবীনের সাক্ষ্যই তোমার জন্য যথেষ্ট। অতঃপর আল্লাহ তাআলা তার মুখের উপর মোহর লাগিয়ে দিবেন এবং অঙ্গ-প্রত্যঙ্গকে বলা হবে, তোমরা কে কখন কী কী কাজ করেছ বলো। তখন অঙ্গ-প্রত্যঙ্গসমূহ তাদের কৃতকর্মসমূহ প্রকাশ করে দিবে। এরপর তার মুখকে স্বাভাবিক অবস্থায় খুলে দেওয়া হবে। তখন সে স্বীয় অঙ্গসমূহকে লক্ষ্য করে আক্ষেপের সাথে বলবে, হে দুর্ভাগা অঙ্গসমূহ! তোরা দূর হ! তোদের ধ্বংস হৌক! তোদের জন্যই তো আমি আমার রবের সাথে ঝগড়া করেছিলাম' (ছহীহ মুসলিম, হা/২৯৬৯; মিশকাত, হা/৫৫৫৪)।&lt;/p&gt;
 &lt;ar&gt;عَنْ أَبِي هُرَيْرَةَ قَالَ: قَالُوا : يَا رَسُولَ اللهِ! هَلْ نَرَى رَبَّنَا يَوْمَ الْقِيَامَةِ؟ قَالَ: هَلْ تُضَارُّونَ فِي رؤْيَةِ الشَّمْسِ فِي الظَّهِيرَةِ لَيْسَتْ فِي سَحَابَةٍ؟ قَالُوا: لَا ، قَالَ: فَهَلْ تُضَارُّونَ فِي رُؤْيَةِ الْقَمَرِ لَيْلَةَ الْبَدْرِ لَيْسَتْ فِي سَحَابَةٍ؟ قَالُوا : لَا. قَالَ: فَوَالَّذِي نَفْسِي بِيَدِهِ لَا تُضَارُّونَ فِي رُؤْيَةِ رَبِّكُمْ إِلَّا كَمَا تُضَارُّونَ فِي رُؤْيَةِ أَحَدِهِمَا. قَالَ: فَيَلْقَى الْعَبْدَ فَيَقُولُ: أَيْ قُلْ: أَلَمْ أُكْرِمْكَ وَأُسَوَّدْكَ وَأَزَوَّجْكَ، وَأُسَخَّرْ لَكَ الْخَيْلَ وَالْإِبِلَ ، وَأَذَرْكَ تَرْأَسُ وَتَرْبَعُ؟ فَيَقُولُ: بَلَى. قَالَ: فَيَقُولُ: أَفَظَنَنْتَ أَنَّكَ مُلَاقِي؟ فَيَقُولُ لَا فَيَقُولُ: فَإِنِّي قَدْ أَنْسَاكَ كَمَا نَسِيتَنِي. ثُمَّ يَلْقَى الثَّانِي فَذَكَرَ مِثْلَهُ ، ثُمَّ يَلْقَى الثَّالِثَ فَيَقُولُ لَهُ مِثْلَ ذَلِكَ، فَيَقُولُ: يَا رَبِّ آمَنْتُ بِكَ، وَبِكِতَابِكَ وَبِرُسُلِكَ، وَصَلَّيْتُ وَصُمْتُ، وَتَصَدَّقْتُ، وَيُثْنِي بِخَيْرٍ مَا اسْتَطَاعَ، يَقُولُ: هَاهُنَا إِذًا، ثُمَّ يُقَالُ: الْآنَ نَبْعَثُ شَاهِدًا عَلَيْكَ، وَيَتَفَكَّرُ فِي نَفْسِهِ: مَنْ ذَا الَّذِي يَشْهَدُ عَلَيَّ? فَيُخْتَمُ عَلَى فِيهِ وَيُقَالُ لِفَخِذِهِ: انْطِقِي؛ فَتَنْطِقُ فَخِذُهُ وَلَحْمُهُ وَعِظَامُهُ بِعَمَلِهِ، وَذَلِكَ لِيُعْذِرَ مِنْ نَفْسِهِ، وَذَلِكَ الْمُنَافِقُ، وَذَلِكَ الَّذِي سَخِطَ اللهُ عَلَيْهِ» .&lt;/ar&gt;
 &lt;p&gt;আবূ হুরায়রা (রাঃ) হতে বর্ণিত, তিনি বলেন, ছাহাবীগণ (রাঃ) বললেন, হে আল্লাহর রাসূল (ﷺ)! কিয়ামতের দিন কী আমরা আমাদের রবকে দেখতে পাব? তিনি বললেন, দ্বিপ্রহরে মেঘমুক্ত আকাশে সূর্য দেখতে কি তোমাদের মধ্যে পরস্পরে বাধা সৃষ্টি হয়? তারা বললেন, না। তিনি আরও বললেন, মেঘমুক্ত আকাশে পূর্ণিমার রাত্রে পূর্ণ চাঁদ দেখতে কি তোমাদের কোনো প্রকারের অসুবিধা হয়? তারা বললেন, না। অতঃপর তিনি বললেন, সেই মহান সত্তার কসম, যাঁর হাতে আমার প্রাণ! এই দুটির কোনো একটিকে দেখতে তোমাদের যেই পরিমাণ অসুবিধা হয়, সেই দিন তোমাদের রবকে দেখতে সেই পরিমাণ অসুবিধাও হবে না। এরপর রাসূল (ﷺ) বললেন, তখন আল্লাহ তাআলা কোনো এক বান্দাকে লক্ষ্য করে বলবেন, হে অমুক! আমি কি তোমাকে মর্যাদা দান করিনি? আমি কি তোমাকে সর্দারী দান করিনি? আমি কি তোমাকে বিবি দান করিনি? আমি কি তোমার জন্য ঘোড়া ও উটকে অনুগত করে দেয়নি? আমি কি তোমাকে এই সুযোগ দেয়নি যে, তুমি নিজ সম্প্রদায়ের নেতৃত্ব দিবে এবং তাদের নিকট হতে এক-চতুর্থাংশ মাল ভোগ করবে? জবাবে বান্দা বলবে, হ্যাঁ, (হে আমার প্রতিপালক!)। অতঃপর রাসূল (ﷺ) বলেন, তখন আল্লাহ তাআলা বান্দাকে বলবেন, আচ্ছা বলো দেখি, তোমার কি এই ধারণা ছিল যে, তুমি আমার সাক্ষাৎ লাভ করবে? বান্দা বলবে, না। এইবার আল্লাহ বলবেন, (দুনিয়াতে) তুমি যেভাবে আমাকে ভুলে গিয়েছিলে আজ আমিও (আখেরাতে) অনুরূপভাবে তোমাকে ভুলে থাকব। (অর্থাৎ তোমাকে আযাবে লিপ্ত রাখব)। অতঃপর আল্লাহ তাআলা দ্বিতীয় এক ব্যক্তিকে জিজ্ঞাসা করবেন, সেও অনুরূপ বলবে। তারপর তৃতীয় এক ব্যক্তির সাথে সাক্ষাৎ করবেন এবং তাকেও অনুরূপ কথা জিজ্ঞাসা করলে সে বলবে, হে আমার প্রতিপালক! আমি তোমার প্রতি, তোমার কিতাবের প্রতি এবং তোমার সমস্ত নবীগণের প্রতি ঈমান এনেছি, ছালাত আদায় করেছি, ছিয়াম পালন করেছি এবং দান-ছাদাকা করেছি। মোটকথা, সে সাধ্য পরিমাণ নিজের নেক কার্যসমূহের একটি তালিকা আল্লাহর সম্মুখে তুলে ধরবে। তখন আল্লাহ তাআলা বলবেন, আচ্ছা! তুমি তো তোমার কথা বললে, এখন এখানেই দাঁড়াও, এক্ষুণি তোমার ব্যাপারে সাক্ষী উপস্থিত করছি। এই কথা শুনে বান্দা মনে মনে চিন্তা করবে, এমন কে আছে যে, এখানে আমার বিরুদ্ধে সাক্ষ্য দিবে? অতঃপর তার মুখে মোহর লাগিয়ে দেওয়া হবে এবং তার রানকে বলা হবে, তুমি বলো, তখন তার রান, হাড়, মাংস প্রভৃতি এক একটি করে বলে ফেলবে, এরা যা যা করেছিল। তার মুখে মোহর লাগিয়ে অঙ্গ-প্রত্যঙ্গ হতে এই জন্য সাক্ষী গ্রহণ করা হবে, যেন সেই বান্দা কোনো ওযর-আপত্তি পেশ করতে না পারে। বস্তুত যেই বান্দার কথা আলোচনা করা হয়েছে, সে হলো মুনাফেক এবং এই কারণেই আল্লাহ তার প্রতি অত্যন্ত ক্ষুব্ধ হবেন (ছহীহ মুসলিম, হা/২৯৬৮; মিশকাত, হা/৫৫৫৫)।&lt;/p&gt;
-&lt;ar&gt;عَنْ عَبْدِ اللَّهِ بْنِ عَمْرٍو قَالَ: قَالَ رَسُولُ اللهِ ﷺ : «إِنَّ اللَّهَ سَيُخَلَّصُ رَجُلًا مِنْ أُمَّتِي عَلَى رُءُوسِ الْخَلَائِقِ يَوْمَ الْقِيَامَةِ، فَيَنْشُرُ عَلَيْهِ تِسْعَةً وَتِسْعِينَ سِجِلًا، كُلُّ سِجِلٌ مِثْلَ مَدَّ الْبَصَرِ ، ثُمَّ يَقُولُ أَتُنْكِرُ مِنْ هَذَا شَيْئًا أَظْلَمَكَ كَتَبَتِي الْحَافِظُونَ؟ فَيَقُولُ: لَا يَا رَبِّ فَيَقُولُ: أَفَلَكَ عُذْرُ؟ قَالَ: لَا يَا رَبِّ فَيَقُولُ : بَلَى؛ إِنَّ لَكَ عِنْدَنَا حَسَنَةً، وَإِنَّهُ لَا ظُلْمَ عَلَيْكَ الْيَوْمَ، فَتُخْرَجُ بِطَاقَةٌ فِيهَا: أَشْهَدُ أَنْ لَا إِلَهَ إِلَّا اللهُ، وَأَنَّ مُحَمَّدًا عَبْدُهُ وَرَسُولُهُ، فَيَقُولُ: احْضُرْ&lt;/ar&gt;
-&lt;ar&gt;وَزْنَكَ، فَيَقُولُ: يَا رَبِّ مَا هَذِهِ الْبِطَاقَةُ مَعَ هَذِهِ السِّجِلَّاتِ؟ فَيَقُولُ: إِنَّكَ لَا تُظْلَمُ، قَالَ: فَتُوضَعُ السِّجِلَّاتُ فِي كِفَّةٍ، وَالْبِطَاقَةُ فِي كِفَّةٍ، فَطَاشَتِ السِّجِلَّاتُ وَثَقُلَتِ الْبِطَاقَةُ؛ فَلَا يَثْقُلُ مَعَ اسْمِ اللهِ شَيْءٌ .&lt;/ar&gt;
+&lt;ar&gt;عَنْ عَبْدِ اللَّهِ بْنِ عَمْرٍو قَالَ: قَالَ رَسُولُ اللهِ ﷺ : «إِنَّ اللَّهَ سَيُخَلَّصُ رَجُلًا مِنْ أُمَّتِي عَلَى رُءُوسِ الْخَلَائِقِ يَوْمَ الْقِيَامَةِ، فَيَنْشُرُ عَلَيْهِ تِسْعَةً وَتِسْعِينَ سِجِلًا، كُلُّ سِجِلٌ مِثْلَ مَدَّ الْبَصَرِ ، ثُمَّ يَقُولُ أَتُنْكِرُ مِنْ هَذَا شَيْئًا أَظْلَمَكَ كَتَبَتِي الْحَافِظُونَ؟ فَيَقُولُ: لَا يَا رَبِّ فَيَقُولُ: أَفَلَكَ عُذْرُ؟ قَالَ: لَا يَا رَبِّ فَيَقُولُ : بَلَى؛ إِنَّ لَكَ عِنْدَنَا حَسَنَةً، وَإِنَّهُ لَا ظُلْمَ عَلَيْكَ الْيَوْمَ، فَتُخْرَجُ بِطَاقَةٌ فِيهَا: أَشْهَدُ أَنْ لَا إِلَهَ إِلَّا اللهُ، وَأَنَّ مُحَمَّدًا عَبْدُهُ وَرَسُولُهُ، فَيَقُولُ: احْضُرْ وَزْنَكَ، فَيَقُولُ: يَا رَبِّ مَا هَذِهِ الْبِطَاقَةُ مَعَ هَذِهِ السِّجِلَّاتِ؟ فَيَقُولُ: إِنَّكَ لَا تُظْلَمُ، قَالَ: فَتُوضَعُ السِّجِلَّاتُ فِي كِفَّةٍ، وَالْبِطَاقَةُ فِي كِفَّةٍ، فَطَاشَتِ السِّجِلَّاتُ وَثَقُلَتِ الْبِطَاقَةُ؛ فَلَا يَثْقُلُ مَعَ اسْمِ اللهِ شَيْءٌ .&lt;/ar&gt;
 &lt;p&gt;আব্দুল্লাহ ইবনু আমর (রাঃ) বলেন, রাসূলুল্লাহ (ﷺ) বলেছেন, 'কিয়ামতের দিন এমন এক ব্যক্তিকে জনসম্মুখে উপস্থিত করা হবে, যার আমলনামা খোলা হবে নিরানব্বই ভলিয়মে এবং প্রতি ভলিয়ম বিস্তীর্ণ হবে দৃষ্টিসীমা পর্যন্ত। অতঃপর আল্লাহ তাআলা তাকে জিজ্ঞাসা করবেন, আচ্ছা বলো দেখি, তুমি এর কোনো একটিকে অস্বীকার করতে পারবে? অথবা আমার লিখক ফেরেশতাগণ কি তোমার প্রতি জুলুম করেছে? সে বলবে, না। হে আমার রব! আল্লাহ তাআলা জিজ্ঞাসা করবেন, তবে কি তোমার পক্ষ হতে কোনো ওযর পেশ করার আছে? সে বলবে, না; হে আমার রব! তখন আল্লাহ বলবেন, হ্যাঁ, তোমার একটি নেকী আমার নিকট রক্ষিত আছে। তুমি নিশ্চিত জেনে রাখ, আজ তোমার প্রতি কোনো জুলুম বা অবিচার করা হবে না। এরপর এক টুকরা কাগজ বের করা হবে, যাতে লিখা আছে, &lt;ar&gt;أَشْهَدُ أَنْ لَا إِلَهَ إِلَّا اللَّهُ وَأَنَّ مُحَمَّدًا رَّسُوْلُ اللَّهِ&lt;/ar&gt; [অর্থাৎ আমি সাক্ষ্য দিচ্ছি যে, আল্লাহ ছাড়া কোনো ইলাহ, (মা'বুদ) নেই এবং মুহাম্মাদ (ﷺ) তাঁর বান্দা ও রাসূল]। অতঃপর আল্লাহ তাকে বলবেন, তোমার আমলের ওজন দেখার জন্য উপস্থিত হও। তখন সে বলবে, হে আমার রব! ঐ সমস্ত বিরাট বিরাট দফতরের মুকাবিলায় এই এক টুকরা কাগজের মূল্যই বা কী আছে? তখন আল্লাহ বলবেন, তোমার উপর কোনো অবিচার করা হবে না। নবী করীম (ﷺ) বলেন, অতঃপর ঐ সমস্ত দফতরগুলো এক পাল্লায় এবং এই কাগজের টুকরাখানি আরেক পাল্লায় থাকবে। কাগজের টুকরা যে পাল্লায় থাকবে তা ভারী হয়ে নিচের দিকে ঝুঁকে থাকবে। মোটকথা, আল্লাহর নামের সাথে অন্য কোনো জিনিস ওজনই হতে পারবে না' (তিরমিযী, হা/২৬৩৯; ইবনু হিব্বান, হা/২২৫; মিশকাত, হা/৫৫৫৯)।&lt;/p&gt;
 &lt;ar&gt;عَنْ عَدِيِّ بْنِ حَاتِمٍ قَالَ : قَالَ رَسُولُ اللهِ ﷺ : «مَا مِنْكُمْ مِنْ أَحَدٍ إِلَّا سَيُكَلِّمُهُ رَبُّهُ، لَيْسَ بَيْنَهُ وَبَيْنَهُ تُرْجُمَانُ وَلَا حِجَابٌ يَحْجُبُهُ، فَيَنْظُرُ أَيْمَنَ مِنْهُ، فَلَا يَرَى إِلَّا مَا قَدَّمَ مِنْ عَمَلِهِ، وَيَنْظُرُ أَشْأَمَ مِنْهُ فَلَا يَرَى إِلَّا مَا قَدَّمَ، وَيَنْظُرُ بَيْنَ يَدَيْهِ فَلَا يَرَى إِلَّا النَّارَ تِلْقَاءَ وَجْهِهِ، فَاتَّقُوا النَّارَ وَلَوْ بِشِقِّ تَمْرَةٍ».&lt;/ar&gt;
-&lt;p&gt;আদী ইবনু হাতেম (রাঃ) হতে বর্ণিত, তিনি বলেন, রাসূলুল্লাহ (ﷺ) বলেছেন, তোমাদের মধ্যে এমন কেউ নেই, যার সাথে তার রব কথাবার্তা&lt;/p&gt;
-&lt;p&gt;বলবেন না। তার ও তার রবের মধ্যে কোনো দোভাষী এবং এমন কোনো পর্দা থাকবে না, যা তাকে আড়াল করে রাখবে। সে তার ডানে তাকাবে, তখনও পূর্বে প্রেরিত আমল ছাড়া আর কিছুই দেখতে পাবে না। আবার বামে তাকাবে, তখনও পূর্ব প্রেরিত আমল ছাড়া আর কিছুই দেখতে পাবে না। আর সম্মুখের দিকে তাকালে জাহান্নাম ছাড়া আর কিছুই দেখতে পাবে না। যা একেবারে চেহারার সম্মুখে অবস্থিত। সুতরাং খেজুর ছালের বিনিময়ে হলেও জাহান্নাম হতে বাঁচতে চেষ্টা করো' (ছহীহ বুখারী, হা/৭৫১২; মিশকাত, হা/৫৫৫০)।&lt;/p&gt;
+&lt;p&gt;আদী ইবনু হাতেম (রাঃ) হতে বর্ণিত, তিনি বলেন, রাসূলুল্লাহ (ﷺ) বলেছেন, তোমাদের মধ্যে এমন কেউ নেই, যার সাথে তার রব কথাবার্তা বলবেন না। তার ও তার রবের মধ্যে কোনো দোভাষী এবং এমন কোনো পর্দা থাকবে না, যা তাকে আড়াল করে রাখবে। সে তার ডানে তাকাবে, তখনও পূর্বে প্রেরিত আমল ছাড়া আর কিছুই দেখতে পাবে না। আবার বামে তাকাবে, তখনও পূর্ব প্রেরিত আমল ছাড়া আর কিছুই দেখতে পাবে না। আর সম্মুখের দিকে তাকালে জাহান্নাম ছাড়া আর কিছুই দেখতে পাবে না। যা একেবারে চেহারার সম্মুখে অবস্থিত। সুতরাং খেজুর ছালের বিনিময়ে হলেও জাহান্নাম হতে বাঁচতে চেষ্টা করো' (ছহীহ বুখারী, হা/৭৫১২; মিশকাত, হা/৫৫৫০)।&lt;/p&gt;
 &lt;ar&gt;عَنْ أَبِي سَعِيدٍ الْخُدْرِي  قَالَ قَالَ رَسُولُ اللهِ   ( وَالَّذِي نَفْسِي بِيَدِهِ لَا تَقُومُ السَّاعَةُ حَتَّى تُكَلِّمَ السَّاعَةُ حَتَّى تُكَلِّمَ السَّبَاعُ الإِنْسَ وَحَتَّى تُكَلِّمَ الرَّجُلَ عَذَبَةُ سَوْطِهِ وَشِرَاكُ نَعْلِهِ وَتُخْبِرَهُ فَخِذْهُ بِمَا أَحْدَثَ أَهْلُهُ مِنْ بَعْدِهِ ».&lt;/ar&gt;
 &lt;p&gt;আবু সাঈদ খুদরী (রাঃ) বলেন, রাসূলুল্লাহ (ﷺ) বলেছেন, 'সেই মহান সত্তার কসম, যার হাতে আমার প্রাণ! সেই সময় পর্যন্ত কিয়ামত কায়েম হবে না যে পর্যন্ত না হিংস্র পশু মানুষের সাথে কথা বলবে এবং যে পর্যন্ত না কারও চাবুক তার সাথে কথা বলবে, তার জুতার ফিতা তার সাথে কথা বলবে। আর তার উরু তাকে জানিয়ে দিবে যে, তার অনুপস্থিতিতে তার স্ত্রী কী করেছে' (তিরমিযী, হা/২১৮১; মিশকাত, হা/৫৪৫৯)।&lt;/p&gt;
 &lt;ar&gt;عَنْ بَهِزِ بْنِ حَكِيمٍ عَنْ أَبِيْهِ عَنْ جَدِّهِ عَنِ النَّبِيِّ ﷺ قَالَ: «إِنَّكُمْ تُدْعَوْنَ مُقَدَّمُ عَلَى أَفْوَاهِكُمْ بِالْقِدَامِ، فَأَوَّلُ مَا يُسْأَلُ عَنْ أَحَدِكُمْ فَخِدْهُ وَكَفُهُ».&lt;/ar&gt;
@@ -585,8 +582,7 @@
 &lt;ar&gt;عَنْ خَوْلَةَ بِنْتِ قَيْسٍ له قَالَتْ: سَمِعْتُ رَسُولَ اللهِ ﷺ يَقُولُ: «إِنَّ هَذِهِ الْمَالَ خَضِرَةٌ حُلْوَةٌ، فَمَنْ أَصَابَهُ بِحَقِّهِ بُورِكَ لَهُ فِيهِ، وَرُبَّ مُتَخَوِّضٍ فِيمَا شَاءَتْ بِهِ نَفْسُهُ مِنْ مَالِ اللَّهِ وَرَسُولِهِ لَيْسَ لَهُ يَوْمَ الْقِيَامَةِ إِلَّا النَّارُ».&lt;/ar&gt;
 &lt;p&gt;খাওলা বিনতে কায়স (রাঃ) হতে বর্ণিত, তিনি বলেন, আমি রাসূল (ﷺ)-কে বলতে শুনেছি, তিনি বলেন, 'নিশ্চয়ই এই পার্থিব সম্পদ শ্যামল ও সুমিষ্ট (অর্থাৎ আকর্ষণীয়) তবে যেই ব্যক্তি ন্যায়ভাবে প্রাপ্ত হয় তাতে তার বরকত হয়। আবার বহু লোক এমনও আছে, যে আল্লাহ ও তাঁর রাসূলের সম্পদে (অর্থাৎ গনীমতের মালে) যথেচ্ছা তসরূপ করে, তার জন্য কিয়ামতের দিন জাহান্নামের আগুন ব্যতীত আর কিছুই না' (তিরমিযী, হা/২৩৭৭; মিশকাত, হা/৪০১৭)।&lt;/p&gt;
 &lt;ar&gt;عَنْ أَبِي هُرَيْرَةَ هُ قَالَ: قَامَ فِينَا رَسُولُ اللهِ ﷺ ذَاتَ يَوْمٍ، فَذَكَرَ الْغُلُولَ، فَعَظَّمَهُ وَعَظَّمَ أَمْرَهُ، ثُمَّ قَالَ: «لَا أُلْفِيَنَّ أَحَدَكُمْ يَجِيءُ يَوْمَ الْقِيَامَةِ عَلَى رَقَبَتِهِ بَعِيرٌ لَهُ رُغَاءُ يَقُولُ: يَا رَسُولَ اللَّهِ! أَغِثْنِي، فَأَقُولُ لَا أَمْلِكُ لَكَ شَيْئًا، قَدْ أَبْلَغْتُكَ. لَا أُلْفِيَنَّ أَحَدَكُمْ يَجِيءُ يَوْমَ الْقِيَامَةِ عَلَى رَقَبَتِهِ فُرْسُ لَهُ حَمْحَمَةٌ، فَيَقُولُ: يَا رَسُولَ اللهِ أَغِثْنِي، فَأَقُولُ: لَا أَمْلِكُ لَكَ شَيْئًا، قَدْ أَبْلَغْتُكَ، لَا أُلْفِيَنَّ أَحَدَكُمْ يَجِيءُ يَوْমَ الْقِيَامَةِ عَلَى رَقَبَتِهِ شَاةٌ لَهَا ثُغَاءُ يَقُولُ: يَا رَسُولَ اللَّهِ أَغِثْنِي، فَأَقُولُ: لَا أَمْلِكُ لَكَ شَيْئًا قَدْ أَبْلَগْتُكَ. لَا أُلْفِيَنَّ أَحَدَكُمْ يَجِيءُ الْقِيَامَةِ عَلَى رَقَبَتِهِ نَفْسٌ لَهَا صِيَاحٌ، فَيَقُولُ : يَا رَسُولَ اللهِ أَغِثْنِي، فَأَقُولُ: لَا أَمْلِكُ لَكَ شَيْئًا، قَدْ أَبْلَغْتُكَ. لَا أُلْفِيَنَّ أَحَدَكُمْ يَجِيءُ يَوْমَ الْقِيَامَةِ عَلَى رَقَبَتِهِ رِقَاعٌ تَخْفُقُ، فَيَقُولُ: يَا رَسُولَ اللَّهِ أَغِثْنِي، فَأَقُولُ : لَا أَمْلِكُ لَكَ شَيْئًا، قَدْ أَبْلَغْتُكَ. لَا أُلْفِيَنَّ أَحَدَكُمْ يَجِيءُ يَوْمَ الْقِيَامَةِ عَلَى رَقَبَتِهِ صَامِتُ، فَيَقُولُ: يَا رَسُولَ اللهِ أَغِثْنِي، فَأَقُولُ: لَا أَمْلِكُ لَكَ شَيْئًا، قَدْ أَبْلَغْتُكَ»&lt;/ar&gt;
-&lt;p&gt;আবূ হুরায়রা (রাঃ) হতে বর্ণিত, তিনি বলেন, একদা নবী (ﷺ) আমাদের মাঝে বক্তব্য দেওয়ার জন্য দাঁড়ালেন, তিনি খিয়ানত সম্পর্কে বক্তব্য দিলেন এবং খিয়ানতের বিষয়টি খুব বড় করে পেশ করলেন। তারপর তিনি বললেন, 'কিয়ামতের দিন তোমাদের কাউকে আমি এমন অবস্থায় পাব যে, তার কাঁধের উপর উট চিৎকার করতে থাকবে। সে বলবে, হে আল্লাহর রাসূল! আমাকে রক্ষা&lt;/p&gt;
-&lt;p&gt;করুন। আমি বলব, আজ আল্লাহর সামনে তোমার জন্য সামান্য কিছু করার ক্ষমতা আমি রাখি না, যা পূর্বেই বলেছি। কিয়ামতের দিন আমি তোমাদের কাউকে এমন অবস্থায় পাব যে, তার কাঁধের উপর ঘোড়া চিৎকার করতে থাকবে। সে বলবে, হে আল্লাহর রাসূল! আমাকে রক্ষা করুন, আমি বলব, আজ আল্লাহর সামনে তোমার জন্য সামান্য কিছু করার ক্ষমতা আমার নেই, যা আমি পূর্বেই বলেছি। কিয়ামতের দিন আমি যেন তোমাদের কাউকে এই অবস্থায় দেখতে না পাই যে, সে কাঁধের উপর একটি ছাগল বহন করছে এবং আমাকে বলবে, আল্লাহর রাসূল আমাকে সাহায্য করুন। আর আমি বলব, আমি কিছুই করতে পারব না। আমি তো তোমাকে আল্লাহর বিধান পূর্বেই জানিয়ে দিয়েছি। কিয়ামতের দিন আমি যেন তোমাদের কাউকে এমন অবস্থায় দেখতে না পাই যে, সে নিজের কাঁধের উপর চিৎকাররত একটি মানুষ বহন করে নিয়ে আসবে আর আমাকে বলবে, হে আল্লাহর রাসূল! আমাকে সাহায্য করুন। আর আমি বলব, আজ আমি তোমার জন্য কিছুই করতে পারব না। আমি আল্লাহর বিধান তোমাকে পূর্বেই জানিয়ে দিয়েছি। কিয়ামতের দিন আমি যেন তোমাদের কাউকে এ অবস্থায় দেখতে না পাই যে, সে নিজের কাঁধের উপর কাপড় ইত্যাদির এক খণ্ড বহন করে নিয়ে আসছে। আর তা ভীষণভাবে তার কাঁধের উপর দুলছে, তখন সে আমাকে বলবে, হে আল্লাহর রাসূল! আমাকে সাহায্য করুন, আর আমি বলব, আমি তোমার জন্য কিছুই করতে পারব না। কিয়ামতে আমি যেন তোমাদের কাউকে এমন অবস্থায় না দেখতে পাই যে, সে নিজের কাঁধের উপর অচেতন সম্পদ (সোনা-চাঁদি) বহন করে নিয়ে আসছে। আর আমাকে বলবে, হে আল্লাহর রাসূল! আমাকে সাহায্য করুন। আর আমি বলব, আজ আমি তোমাকে কোনো সাহায্য করতে পারব না। আমি তো তোমাকে আল্লাহর বিধান পূর্বেই জানিয়ে দিয়েছি' (ছহীহ মুসলিম, হা/১৮৩১; মিশকাত, হা/৩৯৯৬)।&lt;/p&gt;
+&lt;p&gt;আবূ হুরায়রা (রাঃ) হতে বর্ণিত, তিনি বলেন, একদা নবী (ﷺ) আমাদের মাঝে বক্তব্য দেওয়ার জন্য দাঁড়ালেন, তিনি খিয়ানত সম্পর্কে বক্তব্য দিলেন এবং খিয়ানতের বিষয়টি খুব বড় করে পেশ করলেন। তারপর তিনি বললেন, 'কিয়ামতের দিন তোমাদের কাউকে আমি এমন অবস্থায় পাব যে, তার কাঁধের উপর উট চিৎকার করতে থাকবে। সে বলবে, হে আল্লাহর রাসূল! আমাকে রক্ষা করুন। আমি বলব, আজ আল্লাহর সামনে তোমার জন্য সামান্য কিছু করার ক্ষমতা আমি রাখি না, যা পূর্বেই বলেছি। কিয়ামতের দিন আমি তোমাদের কাউকে এমন অবস্থায় পাব যে, তার কাঁধের উপর ঘোড়া চিৎকার করতে থাকবে। সে বলবে, হে আল্লাহর রাসূল! আমাকে রক্ষা করুন, আমি বলব, আজ আল্লাহর সামনে তোমার জন্য সামান্য কিছু করার ক্ষমতা আমার নেই, যা আমি পূর্বেই বলেছি। কিয়ামতের দিন আমি যেন তোমাদের কাউকে এই অবস্থায় দেখতে না পাই যে, সে কাঁধের উপর একটি ছাগল বহন করছে এবং আমাকে বলবে, আল্লাহর রাসূল আমাকে সাহায্য করুন। আর আমি বলব, আমি কিছুই করতে পারব না। আমি তো তোমাকে আল্লাহর বিধান পূর্বেই জানিয়ে দিয়েছি। কিয়ামতের দিন আমি যেন তোমাদের কাউকে এমন অবস্থায় দেখতে না পাই যে, সে নিজের কাঁধের উপর চিৎকাররত একটি মানুষ বহন করে নিয়ে আসবে আর আমাকে বলবে, হে আল্লাহর রাসূল! আমাকে সাহায্য করুন। আর আমি বলব, আজ আমি তোমার জন্য কিছুই করতে পারব না। আমি আল্লাহর বিধান তোমাকে পূর্বেই জানিয়ে দিয়েছি। কিয়ামতের দিন আমি যেন তোমাদের কাউকে এ অবস্থায় দেখতে না পাই যে, সে নিজের কাঁধের উপর কাপড় ইত্যাদির এক খণ্ড বহন করে নিয়ে আসছে। আর তা ভীষণভাবে তার কাঁধের উপর দুলছে, তখন সে আমাকে বলবে, হে আল্লাহর রাসূল! আমাকে সাহায্য করুন, আর আমি বলব, আমি তোমার জন্য কিছুই করতে পারব না। কিয়ামতে আমি যেন তোমাদের কাউকে এমন অবস্থায় না দেখতে পাই যে, সে নিজের কাঁধের উপর অচেতন সম্পদ (সোনা-চাঁদি) বহন করে নিয়ে আসছে। আর আমাকে বলবে, হে আল্লাহর রাসূল! আমাকে সাহায্য করুন। আর আমি বলব, আজ আমি তোমাকে কোনো সাহায্য করতে পারব না। আমি তো তোমাকে আল্লাহর বিধান পূর্বেই জানিয়ে দিয়েছি' (ছহীহ মুসলিম, হা/১৮৩১; মিশকাত, হা/৩৯৯৬)।&lt;/p&gt;
 &lt;ar&gt;عَنْ أَبِي هُرَيْرَةَ قَالَ: «أَهْدَى رَجُلٌ لِرَسُولِ اللهِ ﷺ غُلَامًا يُقَالُ لَهُ: مِدْعَمُ فَبَيْنَمَا مِدْعَمُ يَحُطُّ رَحْلًا لِرَسُولِ اللهِ ﷺ إِذْ أَصَابَهُ سَهْمُ عَائِرٌ فَقَتَلَهُ، فَقَالَ النَّاسُ: هَنِيئًا لَهُ الْجَنَّةُ، فَقَالَ رَسُولُ اللهِ ﷺ : كَلَّا ، وَالَّذِي نَفْسِي بِيَدِهِ إِنَّ الشَّمْلَةَ الَّتِي أَخَذَهَا يَوْمَ خَيْبَرَ مِنَ الْمَغَانِمِ لَمْ تُصِبْهَا الْمَقَاسِمُ، لَتَشْتَعِلُ عَلَيْهِ نَارًا فَلَمَّا سَمِعَ ذَلِكَ النَّاسُ جَاءَ رَجُلٌ بِشِرَاكٍ، أَوْ شِرَاكَيْنِ إِلَى النَّبِيِّ ﷺ فَقَالَ: شِرَاكَ مِنْ نَارٍ، أَوْ شِرَاكَانِ مِنْ نَارٍ» .&lt;/ar&gt;
 &lt;p&gt;আবূ হুরায়রা (রাঃ) বলেন, মিদআম নামে একটি গোলাম রাসূল (ﷺ)-কে হাদিয়া দিয়েছিল। মিদআম এক সময় রাসূল (ﷺ)-এর উটের পিঠের হাওদা নামাচ্ছিল এমতাবস্থায় একটি তীর এসে তাকে লাগে এবং সে মারা যায়। ছাহাবীগণ বলেন, তার জন্য জান্নাত। রাসূল (ﷺ) বললেন, কখনই নয়।&lt;/p&gt;
 &lt;p&gt;আল্লাহর কসম, নিশ্চয়ই ঐ চাদরটি যেটি সে 'খায়বার'-এর গনীমত বণ্টন করার পূর্বে আত্মসাৎ করেছিল সে চাদরটি জাহান্নামের আগুন তার উপর উত্তেজিত করছে। এ কথা শুনে একজন লোক একটি জুতার ফিতা বা দুটি জুতার ফিতা রাসূল (ﷺ)-এর নিকট নিয়ে আসল। রাসূল (ﷺ) বললেন, একটি বা দুটি জুতার ফিতা আত্মসাৎ করলেও জাহান্নামে যাবে (ছহীহ বুখারী, হা/৬৭০৭; ছহীহ মুসলিম, হা/১১৫; মিশকাত, হা/৩৯৯৭)।&lt;br&gt;&lt;br&gt;এই হাদীছসমূহ দ্বারা প্রমাণিত হয় যে, আত্মসাৎকৃত বস্তু ক্ষুদ্র হলেও তার পরিণাম জাহান্নাম।&lt;/p&gt;
@@ -626,8 +622,7 @@
 &lt;ar&gt;يَا أَيُّهَا الرُّسُلُ كُلُوا مِنَ الطَّيِّبَاتِ وَاعْمَلُوا صَالِحًا إِنِّي بِمَا تَعْمَلُوْنَ عَلِيمٌ)&lt;/ar&gt;
 &lt;p&gt;'হে রাসূলগণ! তোমরা পবিত্র বস্তু হতে আহার করো ও সৎকর্ম করো; তোমরা যা কর সে সম্বন্ধে আমি অবগত' (আল-মুমিনূন, ২৩/৫১)।&lt;/p&gt;
 &lt;ar&gt;عَنْ أَبِي هُرَيْرَةَ هُ قَالَ: «قَالَ رَسُولُ اللهِ اللهِ : إِنَّ اللهَ طَيِّبُ لَا يَقْبَلُ إِلَّا طَيِّبًا، وَأَنَّ اللَّهَ أَمَرَ الْمُؤْمِنِينَ بِمَا أَمَرَ بِهِ الْمُرْسَلِينَ ثُمَّ ذَكَرَ الرَّجُلَ يُطِيلُ السَّفَرَ، أَشْعَثَ، أَغْبَرَ، يَمُدُّ يَدَيْهِ إِلَى السَّمَاءِ: يَا رَبِّ يَا رَبِّ وَمَطْعَمُهُ حَرَامٌ ، وَمَشْرَبُهُ حَرَامٌ ، وَمَلْبَسُهُ حَرَামٌ، وَغُذَّيَ بِالْحَرَامِ، فَأَنَّى يُسْتَجَابُ لِذَلِكَ؟».&lt;/ar&gt;
-&lt;p&gt;আবু হুরায়রা (রাঃ) বলেন, রাসূল (ﷺ) বলেছেন, 'নিশ্চয়ই আল্লাহ পবিত্র, তিনি পবিত্র ছাড়া গ্রহণ করেন না। (এবং সর্বক্ষেত্রে পাক-পবিত্রতার আদেশই তিনি করেছেন। সেই সম্পর্কে) আল্লাহ রাসূলগণকে যে আদেশ করেছেন, মুমিনগণকেও সেই আদেশই করেছেন। অতঃপর রাসূল (ﷺ) উল্লেখ করলেন, এক ব্যক্তি দূর-দূরান্তের সফর করছে। তার মাথার চুল এলোমেলো, শরীরে ধূলা-বালি। এমতাবস্থায় ঐ ব্যক্তি উভয় হস্ত আসমানের দিকে উঠিয়ে কাতর&lt;/p&gt;
-&lt;p&gt;স্বরে হে প্রভু! হে প্রভু! বলে ডাকছে। কিন্তু তার খাদ্য হারাম, তার পানীয় হারাম, তার পোশাক হারাম, তার জীবিকা নির্বাহ হারাম, কীভাবে তার দু'আ কবুল হবে' (ছহীহ মুসলিম, হা/১০১৫; তিরমিযী, হা/২৯৮৯; মিশকাত হা/২৭৬০)।&lt;/p&gt;
+&lt;p&gt;আবু হুরায়রা (রাঃ) বলেন, রাসূল (ﷺ) বলেছেন, 'নিশ্চয়ই আল্লাহ পবিত্র, তিনি পবিত্র ছাড়া গ্রহণ করেন না। (এবং সর্বক্ষেত্রে পাক-পবিত্রতার আদেশই তিনি করেছেন। সেই সম্পর্কে) আল্লাহ রাসূলগণকে যে আদেশ করেছেন, মুমিনগণকেও সেই আদেশই করেছেন। অতঃপর রাসূল (ﷺ) উল্লেখ করলেন, এক ব্যক্তি দূর-দূরান্তের সফর করছে। তার মাথার চুল এলোমেলো, শরীরে ধূলা-বালি। এমতাবস্থায় ঐ ব্যক্তি উভয় হস্ত আসমানের দিকে উঠিয়ে কাতর স্বরে হে প্রভু! হে প্রভু! বলে ডাকছে। কিন্তু তার খাদ্য হারাম, তার পানীয় হারাম, তার পোশাক হারাম, তার জীবিকা নির্বাহ হারাম, কীভাবে তার দু'আ কবুল হবে' (ছহীহ মুসলিম, হা/১০১৫; তিরমিযী, হা/২৯৮৯; মিশকাত হা/২৭৬০)।&lt;/p&gt;
 &lt;ar&gt;عَنْ أَبِي هُرَيْرَةَ الله قَالَ: قَالَ رَسُولُ اللهِ ﷺ : يَأْتِي عَلَى الْمَرْءِ زَمَانٌ لَا يُبَالِي الْمَرْءُ مَا أَخَذَ مِنْهُ، أَمِنَ الْحَلَالِ أَمْ مِنَ الْحَرَامِ».&lt;/ar&gt;
 &lt;p&gt;আবু হুরায়রা (রাঃ) বলেন, রাসূল (ﷺ) বলেছেন, 'মানুষের সম্মুখে এমন এক যুগ আসবে যে, কেউ পরওয়া করবে না কী উপায়ে মাল অর্জন করল; হারাম না হালাল উপায়ে' (ছহীহ বুখারী, হা/২০৫৯; মিশকাত, হা/২৭৬১)।&lt;/p&gt;
 &lt;ar&gt;وَعَنِ النُّعْمَانِ بْنِ بَشِيرٍ قَالَ: قَالَ رَسُولُ اللهِ ﷺ : الْحَلَالُ بَيِّنُ وَالْحَرَامُ بَيِّنٌ، وَبَيْنَهُمَا مُشْتَبِهَاتٌ لَا يَعْلَمُهُنَّ كَثِيرٌ مِنَ النَّاسِ، فَمَنِ اتَّقَى الشُّبَهَاتِ اسْتَبْرَأَ لِدِينِهِ وَعِرْضِهِ، وَمَنْ وَقَعَ فِي الْحَرَامِ كَالرَّاعِي يَرْعَى حَوْلَ الْحِمَى يُوشِكُ أَنْ يَرْتَعَ فِيهِ، أَلَا وَإِنَّ لِكُلِّ مَلِكٍ حِمّى أَلَا وَإِنَّ حِمَى اللَّهِ مَحَارِمُهُ، أَلَا وَإِنَّ فِي الْجَسَدِ مُضْغَةً إِذَا صَلُحَتْ صَلَحَ الْجُسَدُ كُلُّهُ، وَإِذَا فَسَدَتْ فَسَدَ الْجَسَدُ كُلُّهُ، أَلَا وَهِيَ الْقَلْبُ».&lt;/ar&gt;
@@ -663,8 +658,7 @@
 &lt;p&gt;আব্দুল্লাহ ইবনু আমর (রাঃ) হতে বর্ণিত, তিনি বলেন, রাসূলুল্লাহ (ﷺ) বলেছেন, 'যাকাতের মাল ধনীদের জন্য হালাল নয়, সুস্থ সবলদের (খেটে খেতে সক্ষম) জন্যও নয়' (আবূ দাউদ, হা/১৬৩৪; তিরমিযী, হা/৬৫২; মিশকাত, হা/১৮৩০)।&lt;br&gt;&lt;br&gt;এই হাদীছ প্রমাণ করে, যাদের কাজ করে খাওয়ার সামর্থ্য আছে তাদের জন্য ছাদাকা খাওয়া জায়েয নয়।&lt;/p&gt;
 &lt;ar&gt;عَنْ عُبَيْدِ اللَّهِ بْنِ عَدِيِّ بْنِ الْخِيَارِ قَالَ: «أَخْبَرَنِي رَجُلَانِ أَنَّهُمَا أَتَيَا النَّبِيَّ ﷺ وَهُوَ فِي حَجَّةِ الْوَدَاعِ، وَهُوَ يُقَسِّمُ الصَّدَقَةَ فَسَأَلَاهُ مِنْهَا، فَرَفَعَ فِينَا النَّظَرَ، وَخَفَضَهُ فَرَآنَا جَلْدَيْنِ، فَقَالَ: " إِنْ شِئْتُمَا أَعْطَيْتُكুমَا وَلَا حَظٍّ فِيهَا لِغَنِيٌّ وَلَا لِقَوِيٌّ مُكْتَسِبٍ» ".&lt;/ar&gt;
 &lt;p&gt;উবায়দুল্লাহ ইবনু আদী ইবনু খিয়ার (রাঃ) হতে বর্ণিত, তিনি বলেন, আমাকে দু'ব্যক্তি জানিয়েছেন যে, বিদায় হজ্জে মানুষের মধ্যে যাকাতের মাল বণ্টন করার সময় তারা উভয়ে নবী (ﷺ)-এর কাছে উপস্থিত ছিলেন। তারা এ মালের কিছু অংশ নেবার জন্য আগ্রহ দেখান। দুজন বলেন, রাসূলুল্লাহ (ﷺ) (যাকাত নেবার আগ্রহ দেখে) আমাদের মাথা থেকে পা পর্যন্ত চোখ বুলালেন। আমাদের সুস্থ সবল দেখে বললেন, তোমরা যাকাত নিতে চাইলে আমি দিতে পারি। (কিন্তু মনে রাখবে,) ছাদাকা ও যাকাতের সম্পদে ধনীদের কোনো অংশ নেই। আর সুস্থ সবল এবং পরিশ্রম করতে সক্ষম লোকদের জন্য ছাদাকা ও যাকাত নয়' (আবু দাউদ, হা/১৬৩৩; নাসাঈ, হা/২৫৯৮; মিশকাত, হা/১৮৩২)।&lt;/p&gt;
-&lt;ar&gt;عَنْ قَبِيصَةَ بْنِ مُخَارِقٍ قَالَ: تَحَمَّلْتُ حَمَالَةً، فَأَتَيْتُ رَسُولَ اللَّهِ ﷺ أَسْأَلُهُ فِيهَا، فَقَالَ: " أَقِمْ حَتَّى تَأْتِيَنَا الصَّدَقَةُ، فَنَأْمُرَ لَكَ بِهَا " ، ثُمَّ قَالَ: " يَا قَبِيصَةُ إِنَّ الْمَسْأَلَةَ لَا تَحِلُّ إِلَّا لِأَحَدِ ثَلَاثَةٍ : رَجُلٍ تَحَمَّلَ حَمَالَةٌ فَحَلَّتْ لَهُ الْمَسْأَلَةُ حَتَّى يُصِيبَهَا ثُمَّ يُمْسِكُ، وَرَجُلٍ أَصَابَتْهُ جَائِحَةُ اجْتَاحَتْ مَالَهُ، فَحَلَّتْ لَهُ الْمَسْأَلَةُ حَتَّى يُصِيبَ قِوَامًا مِنْ عَيْشٍ، أَوْ قَالَ سِدَادًا مِنْ عَيْشٍ، وَرَجُلٍ أَصَابَتْهُ فَاقَةٌ حَتَّى يَقُولَ ثَلَاثَةٌ مِنْ ذَوِي الْخِجَا مِنْ قَوْمِهِ: لَقَدْ أَصَابَتْ فُلَانًا فَاقَةٌ&lt;/ar&gt;
-&lt;ar&gt;فَحَلَّتْ لَهُ الْمَسْأَلَةُ حَتَّى يُصِيبَ قِوَامًا مِنْ عَيْشٍ ، أَوْ قَالَ سِدَادًا مِنْ عَيْشٍ، فَمَا سِوَاهُنَّ مِنَ الْمَسْأَلَةِ يَا قَبِيصَةُ سُحْتُ، يَأْكُلُهَا صَاحِبُهَا سُحْتًا».&lt;/ar&gt;
+&lt;ar&gt;عَنْ قَبِيصَةَ بْنِ مُخَارِقٍ قَالَ: تَحَمَّلْتُ حَمَالَةً، فَأَتَيْتُ رَسُولَ اللَّهِ ﷺ أَسْأَلُهُ فِيهَا، فَقَالَ: " أَقِمْ حَتَّى تَأْتِيَنَا الصَّدَقَةُ، فَنَأْمُرَ لَكَ بِهَا " ، ثُمَّ قَالَ: " يَا قَبِيصَةُ إِنَّ الْمَسْأَلَةَ لَا تَحِلُّ إِلَّا لِأَحَدِ ثَلَاثَةٍ : رَجُلٍ تَحَمَّلَ حَمَالَةٌ فَحَلَّتْ لَهُ الْمَسْأَلَةُ حَتَّى يُصِيبَهَا ثُمَّ يُمْسِكُ، وَرَجُلٍ أَصَابَتْهُ جَائِحَةُ اجْتَاحَتْ مَالَهُ، فَحَلَّتْ لَهُ الْمَسْأَلَةُ حَتَّى يُصِيبَ قِوَامًا مِنْ عَيْشٍ، أَوْ قَالَ سِدَادًا مِنْ عَيْشٍ، وَرَجُلٍ أَصَابَتْهُ فَاقَةٌ حَتَّى يَقُولَ ثَلَاثَةٌ مِنْ ذَوِي الْخِجَا مِنْ قَوْمِهِ: لَقَدْ أَصَابَتْ فُلَانًا فَاقَةٌ فَحَلَّتْ لَهُ الْمَسْأَلَةُ حَتَّى يُصِيبَ قِوَامًا مِنْ عَيْشٍ ، أَوْ قَالَ سِدَادًا مِنْ عَيْشٍ، فَمَا سِوَاهُنَّ مِنَ الْمَسْأَلَةِ يَا قَبِيصَةُ سُحْتُ، يَأْكُلُهَا صَاحِبُهَا سُحْتًا».&lt;/ar&gt;
 &lt;p&gt;কবীসা ইবনু মুখারিক্ক (রাঃ) হতে বর্ণিত, তিনি বলেন, আমি ঋণগ্রস্ত হয়ে রাসূলুল্লাহ (ﷺ)-এর কাছে এলাম। তার কাছে ঋণ আদায়ের জন্য কিছু চাইলাম। তিনি বললেন, অপেক্ষা করো। আমার কাছে যাকাতের মাল আসা পর্যন্ত আসলে তোমাকে কিছু দেবার জন্য বলে দেব। তারপর তিনি বললেন, কবীসা! শুধু তিন ধরনের ব্যক্তির জন্য কিছু চাওয়া জায়েয। প্রথমত, যে ব্যক্তি অপরের ঋণের জামিনদার। তবে বেশি চাইতে পারবে না। বরং যতটুকু ঋণ শোধের জন্য প্রয়োজন শুধু ততটুকু চাইবে। এরপর আর চাইবে না। দ্বিতীয়ত, ওই ব্যক্তি যে বিপদগ্রস্ত হয়ে পড়েছে (দুর্ভিক্ষ, প্লাবন ইত্যাদিতে)। তার সব ধন-সম্পদ ধ্বংস হয়েছে। তারও (শুধু খাবার ও পোশাকের জন্য) ততটুকু যাতে প্রয়োজন মিটে যায়। তার জীবনের জন্য অবলম্বন হয়ে যায়। তৃতীয়ত, ওই ব্যক্তি (যে ধনী, কিন্তু তার এমন কোনো কঠিন প্রয়োজন হয়ে পড়েছে যা মহল্লাবাসী জানে। যেমন ঘরের সব মালপত্র চুরি হয়ে গেছে অথবা অন্য কোনো দুর্ঘটনার কারণে মুখাপেক্ষী হয়ে পড়েছে)। (মহল্লার) তিনজন বুদ্ধিমান সচেতন লোক এ ব্যাপারে সাক্ষ্য দিবে যে, সত্যিই এ ব্যক্তি মুখাপেক্ষী। তার জন্যও সেই পরিমাণ (সাহায্য) চাওয়া জায়েয, যাতে তার প্রয়োজন মিটে। অথবা তিনি বলেছেন এর দ্বারা তার মুখাপেক্ষিতা ও অভাব দূর হয়, তার জীবনে একটি অবলম্বন আসে। হে ক্ববীসা! এ তিন প্রকারের 'চাওয়া' ছাড়া হালাল নয়। আর হারাম পন্থায় প্রাপ্ত মাল খাওয়া তার জন্য হারাম (ছহীহ মুসলিম, হা/১০৪৪; মিশকাত, হা/১৮৩৭)।&lt;/p&gt;&lt;/div&gt;</t>
         </is>
       </c>

--- a/output/opodesh-test/book-output.xlsx
+++ b/output/opodesh-test/book-output.xlsx
@@ -7,7 +7,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Book Content" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="chapter" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="section" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="content" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,15 +439,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="35" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="60" customWidth="1" min="5" max="5"/>
-    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -459,26 +457,6 @@
           <t>chapter_name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>section_id</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>section_name</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>content</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>notes</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
@@ -489,15 +467,161 @@
           <t>অবিচ্ছেদ্য সাক্ষী হতে সাবধান</t>
         </is>
       </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>আত্মসাৎ</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>হালাল ও হারাম</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>section_id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>section_name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>chapter_id</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>অবিচ্ছেদ্য সাক্ষী হতে সাবধান</t>
+        </is>
+      </c>
       <c r="C2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>অবিচ্ছেদ্য সাক্ষী হতে সাবধান</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>আত্মসাৎ</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>হালাল ও হারাম</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>content_id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>chapter_id</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>section_id</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>content</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>&lt;div class="page-text"&gt;&lt;p&gt;অবিচ্ছেদ্য সাক্ষী এমন সাক্ষীকে বলা হয়, যা ব্যক্তি হতে পৃথক হয় না।&lt;/p&gt;
 &lt;p&gt;কিয়ামতের মাঠে আল্লাহ অবিচ্ছেদ্য সাক্ষীর মাধ্যমে মানুষকে অপরাধী প্রমাণ করবেন। আর তা হবে মানুষের হাত, পা, শরীর ইত্যাদি।&lt;/p&gt;
@@ -527,26 +651,19 @@
 &lt;p&gt;উক্ববা ইবনু আমের (রাঃ) হতে বর্ণিত, তিনি রাসূলুল্লাহ (ﷺ)-কে বলতে শুনেছেন, 'কিয়ামতের দিন মানুষের যখন মুখ বন্ধ থাকবে, তখন তার বাম উরুর হাড় সর্বপ্রথম কথা বলবে' (মুসনাদে আহমাদ, হা/১৭৪১২; সিলসিলা ছহীহা, হা/২৭১৩)।&lt;/p&gt;&lt;/div&gt;</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr"/>
+      <c r="E2" s="3" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>আত্মসাৎ</t>
-        </is>
+      <c r="B3" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>আত্মসাৎ</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>&lt;div class="page-text"&gt;&lt;p&gt;কারো কোনো সম্পদ আত্মসাৎ করা বড় গুনাহ। এর পরিণতি ভয়াবহ। যেমন আল্লাহ তাআলা বলেন,&lt;/p&gt;
 &lt;ar&gt;وَمَا كَانَ لِنَبِيَّ أَنْ يَয়ُلَّ وَمَنْ يَয়ْلُلْ يَأْتِ بِمَا غَلَّ يَوْمَ الْقِيَامَةِ ثُمَّ تُوَفَّى كُلُّ نَفْسٍ مَا كَسَبَتْ وَهُمْ لَا يُظْلَمُوْنَ&lt;/ar&gt;
@@ -594,26 +711,19 @@
 &lt;p&gt;খাওলা আনছারী (রাঃ) হতে বর্ণিত, তিনি বলেন, আমি রাসূল (ﷺ)-কে বলতে শুনেছি, 'নিশ্চয়ই যে ব্যক্তি অন্যায়ভাবে সম্পদ দখল করবে। কিয়ামতের দিন তার জন্য জাহান্নাম রয়েছে' (ছহীহ বুখারী, হা/৩১১৮; মিশকাত, হা/৩৯৯৫)।&lt;/p&gt;&lt;/div&gt;</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr"/>
+      <c r="E3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>হালাল ও হারাম</t>
-        </is>
+      <c r="B4" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>হালাল ও হারাম</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>&lt;div class="page-text"&gt;&lt;ar&gt;يَا أَيُّهَا النَّاسُ كُلُوا مِمَّا فِي الْأَرْضِ حَلَالًا طَيِّبًا وَلَا تَتَّبِعُوا خُطُوَاتِ الشَّيْطَانِ إِنَّهُ لَكُمْ عَدُوٌّ مُبِينٌ)&lt;/ar&gt;
 &lt;p&gt;'হে মানবগণ! পৃথিবীর মধ্যে যা বৈধ-পবিত্র, তা হতে ভক্ষণ করো এবং শয়তানের পদঙ্ক অনুসরণ করো না, নিশ্চয়ই সে তোমাদের প্রকাশ্য শত্রু' (আল-বাকারা, ২/১৬৮)।&lt;/p&gt;
@@ -662,7 +772,7 @@
 &lt;p&gt;কবীসা ইবনু মুখারিক্ক (রাঃ) হতে বর্ণিত, তিনি বলেন, আমি ঋণগ্রস্ত হয়ে রাসূলুল্লাহ (ﷺ)-এর কাছে এলাম। তার কাছে ঋণ আদায়ের জন্য কিছু চাইলাম। তিনি বললেন, অপেক্ষা করো। আমার কাছে যাকাতের মাল আসা পর্যন্ত আসলে তোমাকে কিছু দেবার জন্য বলে দেব। তারপর তিনি বললেন, কবীসা! শুধু তিন ধরনের ব্যক্তির জন্য কিছু চাওয়া জায়েয। প্রথমত, যে ব্যক্তি অপরের ঋণের জামিনদার। তবে বেশি চাইতে পারবে না। বরং যতটুকু ঋণ শোধের জন্য প্রয়োজন শুধু ততটুকু চাইবে। এরপর আর চাইবে না। দ্বিতীয়ত, ওই ব্যক্তি যে বিপদগ্রস্ত হয়ে পড়েছে (দুর্ভিক্ষ, প্লাবন ইত্যাদিতে)। তার সব ধন-সম্পদ ধ্বংস হয়েছে। তারও (শুধু খাবার ও পোশাকের জন্য) ততটুকু যাতে প্রয়োজন মিটে যায়। তার জীবনের জন্য অবলম্বন হয়ে যায়। তৃতীয়ত, ওই ব্যক্তি (যে ধনী, কিন্তু তার এমন কোনো কঠিন প্রয়োজন হয়ে পড়েছে যা মহল্লাবাসী জানে। যেমন ঘরের সব মালপত্র চুরি হয়ে গেছে অথবা অন্য কোনো দুর্ঘটনার কারণে মুখাপেক্ষী হয়ে পড়েছে)। (মহল্লার) তিনজন বুদ্ধিমান সচেতন লোক এ ব্যাপারে সাক্ষ্য দিবে যে, সত্যিই এ ব্যক্তি মুখাপেক্ষী। তার জন্যও সেই পরিমাণ (সাহায্য) চাওয়া জায়েয, যাতে তার প্রয়োজন মিটে। অথবা তিনি বলেছেন এর দ্বারা তার মুখাপেক্ষিতা ও অভাব দূর হয়, তার জীবনে একটি অবলম্বন আসে। হে ক্ববীসা! এ তিন প্রকারের 'চাওয়া' ছাড়া হালাল নয়। আর হারাম পন্থায় প্রাপ্ত মাল খাওয়া তার জন্য হারাম (ছহীহ মুসলিম, হা/১০৪৪; মিশকাত, হা/১৮৩৭)।&lt;/p&gt;&lt;/div&gt;</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr"/>
+      <c r="E4" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
